--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-286.5500000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.52874e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.753</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2696636606650077</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9458056496175236</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.975931199999464</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.382345947683587</v>
+      </c>
+      <c r="J2" t="n">
+        <v>41.26996032494195</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.2343794523108</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 32.441x + -16105.915</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>419.2326892825938</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7283.020815301395</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.208497343607827e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8723576743306077</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-229.497</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.51864e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-86.194</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.229347628314319</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9524649153600583</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.096320048765808</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.785509851517824</v>
+      </c>
+      <c r="J3" t="n">
+        <v>53.16962857414322</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.51704152719303</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 38.628x + -18438.480</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>415.8312423507439</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3537.425526003954</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.058952545786878e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8375002269239821</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-200.145</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.51232e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.414</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1240006760837866</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6636793936162532</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.984553600201311</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.693141499371841</v>
+      </c>
+      <c r="J4" t="n">
+        <v>62.43819918072323</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.63173771670471</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 41.867x + -19638.793</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>426.9358447869628</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>174689281.998233</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.81308952672996e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9718976251082175</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-180.649</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.50798e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.556</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3380097135004396</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.056556217023782</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.158548300650653</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.870069208000045</v>
+      </c>
+      <c r="J5" t="n">
+        <v>70.01049461869066</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.75344427271543</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 45.956x + -21341.593</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>407.5001834965634</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3459.085167738524</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.970744449809594e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7772845170568609</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-168.091</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.50537e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.657</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2100806654701562</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.026511182952121</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.26223883386594</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.18793284944645</v>
+      </c>
+      <c r="J6" t="n">
+        <v>76.6313612243556</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.82438455887657</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 48.730x + -22379.847</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>416.2955460959788</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5373.300659411513</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8.886465498890387e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8853846798524502</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-158.6559999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5037e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.748</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1833774597281363</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7778709796599224</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.03883812893056</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.697095144141651</v>
+      </c>
+      <c r="J7" t="n">
+        <v>81.24013916264497</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.81374997364514</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 48.293x + -21849.680</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>413.4572111420966</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6825.418772768077</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.361469973584559e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.877804163304986</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-150.795</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.50231e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.812</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2614877646672792</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.113166877173368</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.280960377016453</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30.74926624145304</v>
+      </c>
+      <c r="J8" t="n">
+        <v>87.27206229238766</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.91345318528198</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 52.726x + -23681.335</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>398.6739443155888</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3354.608012709333</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.236408422876814e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6688279065846658</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-142.993</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.50176e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.881</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3206493379548573</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.015220060371274</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.084853166688043</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.43408753814591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>91.42927357425376</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.92842992015298</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 53.463x + -23736.442</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>396.0362382921331</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3322.582231403105</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.439434287426658e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6700199123941255</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-140.446</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.50105e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.923</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2978506581875404</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.044156552647077</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.121535501014364</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24.61629948078551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>94.9368022083093</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.9251467226117</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 53.299x + -23408.920</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>393.4370342247838</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3294.122405107289</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.849900843905989e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6845499496079346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-135.631</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.50078e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.97199999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2137437464084619</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.037070547304311</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.162719463258724</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20.2050340351472</v>
+      </c>
+      <c r="J11" t="n">
+        <v>98.81668570612396</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.95413911794064</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 54.777x + -23837.615</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>391.0632391930403</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3264.069938753463</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.724265934223685e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.630846086608007</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-131.0170000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.50054e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-87.015</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1988034368267566</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.132717307688328</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.23356486320051</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20.52677283187985</v>
+      </c>
+      <c r="J12" t="n">
+        <v>101.60450815865</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.97330415228687</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 55.800x + -24053.498</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>394.0977679144297</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6519.887508174598</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9.549030011595242e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.835028137467054</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-126.0149999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.50039e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-87.054</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.670079027072413</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.249726827230075</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.512717680857185</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.753610657823997</v>
+      </c>
+      <c r="J13" t="n">
+        <v>104.7355091822837</v>
+      </c>
+      <c r="K13" t="n">
+        <v>89.05634127267498</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 60.711x + -26034.306</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>392.8430672948829</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>855128219.2084062</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.712016493363925e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.979474372054447</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-125.866</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.50045e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-87.084</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2502710190124335</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8986334283192537</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.869112672557594</v>
+      </c>
+      <c r="I14" t="n">
+        <v>17.08394057978147</v>
+      </c>
+      <c r="J14" t="n">
+        <v>104.8937579522922</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.98416076772514</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 56.396x + -23863.414</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>389.695358208202</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>321334355.8278245</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.708134112227292e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9798302819661022</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-121.0189999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.5005e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-87.127</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3648011505785648</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.162540493258979</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.289031284553619</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.61590745313985</v>
+      </c>
+      <c r="J15" t="n">
+        <v>111.1543498405293</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89.03575403470118</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 59.415x + -24961.219</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>386.6341236401993</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>105628032.5617058</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.702302874103545e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9803626081801807</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-120.169</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.50046e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-87.158</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1596009830547203</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8772304227963224</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.99464212323835</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.530132835311278</v>
+      </c>
+      <c r="J16" t="n">
+        <v>112.8762218567926</v>
+      </c>
+      <c r="K16" t="n">
+        <v>89.00221894496224</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 57.417x + -23863.700</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>383.5601705167197</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>209024500.0176502</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.698854366435733e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9806699975155032</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-117.5959999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.50041e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-87.187</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3281822149982813</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9912454880045429</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.064203467877868</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>112.4437319603085</v>
+      </c>
+      <c r="K17" t="n">
+        <v>89.03097801498369</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 59.122x + -24377.925</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>380.5290257264724</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>207300632.6712884</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.695154011482158e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9810036091747164</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-115.3820000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.50048e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-87.211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4441947042709506</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.255803127973852</v>
+      </c>
+      <c r="H18" t="n">
+        <v>55.00818467122109</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.67962964093946</v>
+      </c>
+      <c r="J18" t="n">
+        <v>114.7526237705915</v>
+      </c>
+      <c r="K18" t="n">
+        <v>89.10550813941626</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 64.049x + -26268.556</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>377.5196203385924</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>117820159.098676</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.692053420978269e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9812947421950817</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-111.521</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.50077e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-87.254</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4747856971071805</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.042027925832634</v>
+      </c>
+      <c r="H19" t="n">
+        <v>42.78042843151687</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.891717298405903</v>
+      </c>
+      <c r="J19" t="n">
+        <v>119.9015352564753</v>
+      </c>
+      <c r="K19" t="n">
+        <v>89.08940839896985</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 62.916x + -25535.822</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>374.4969979867185</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>156466484.3031162</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.687436587151995e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9817441611408338</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-111.873</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.50097e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-87.276</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2040193429260758</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9919577877974927</v>
+      </c>
+      <c r="H20" t="n">
+        <v>36.1502654965991</v>
+      </c>
+      <c r="I20" t="n">
+        <v>66.19346428790335</v>
+      </c>
+      <c r="J20" t="n">
+        <v>122.6586426665235</v>
+      </c>
+      <c r="K20" t="n">
+        <v>89.05474568298867</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 60.609x + -24340.325</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>371.4986777876879</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>222024150.6506714</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.68509893582668e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9819777562874118</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-106.295</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.50091e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-87.315</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5260021767871218</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.330083738778998</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.401578942904233</v>
+      </c>
+      <c r="I21" t="n">
+        <v>39.04956925063428</v>
+      </c>
+      <c r="J21" t="n">
+        <v>128.5799767080835</v>
+      </c>
+      <c r="K21" t="n">
+        <v>89.1488362482192</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 67.310x + -26900.502</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>368.4761277387811</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>327113719.9689867</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.680504414924477e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9823926097935577</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-107.269</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.50118e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-87.33199999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4389141470815144</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8739192901444751</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.011982921052152</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60.23869870532217</v>
+      </c>
+      <c r="J22" t="n">
+        <v>126.3151734182323</v>
+      </c>
+      <c r="K22" t="n">
+        <v>89.10539835048284</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 64.041x + -25303.807</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>365.4780612686336</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>298274177.4419369</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.67870213672396e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.982590067376848</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-516.1890000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.44567e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.624</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1932201611715378</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8282660769631874</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.50892068625401</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.110258333208687</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.99935931064937</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.19793351182348</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 20.431x + -10804.473</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>454.5794073840062</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>736737071.9532801</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.003872975957584e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9500380180101933</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-424.239</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.46029e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.343</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04681824688339607</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6514626612367653</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.866814762570976</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.659625920032692</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.30058811349939</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.68962738094933</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 24.786x + -11630.288</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>408.9207503450474</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3489.288174957848</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.324373287264978e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.728300516904037</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-359.397</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.45557e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.767</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3148555314555037</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8217435698194462</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.925040907165875</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.810523464519012</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.51110441032063</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.03664702988991</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 29.171x + -13296.596</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>417.4499877467158</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>966855033.5855224</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.828363463551726e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9648940954335234</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-312.485</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.44921e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.07299999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1347412486345415</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8639631439455213</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.941048867293506</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.878700243864679</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.95561996195787</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.28014656513224</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 33.304x + -14939.030</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>411.9548059643218</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>112876492.8521605</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.778603561807484e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9684066534420489</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-277.463</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.44382e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.297</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4642302347336944</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.034733779351052</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.302090190429891</v>
+      </c>
+      <c r="I6" t="n">
+        <v>42.50426549670706</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.59100676048639</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.46697743725498</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 37.365x + -16558.876</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>396.160984841526</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3331.650565335081</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.884789522626573e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6771610163355278</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-251.1650000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.43966e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.476</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3484248521515291</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.272318903749826</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.073765109404044</v>
+      </c>
+      <c r="I7" t="n">
+        <v>51.70685708765008</v>
+      </c>
+      <c r="J7" t="n">
+        <v>48.58758612244542</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.60767135371988</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 41.143x + -17995.618</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>392.7280518508706</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3287.27072288689</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.521316533480897e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6870961214067036</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-229.595</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.43633e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.624</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.430249316114006</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.179586645343728</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.438375833633839</v>
+      </c>
+      <c r="I8" t="n">
+        <v>34.47260734172169</v>
+      </c>
+      <c r="J8" t="n">
+        <v>53.83833662679709</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.72244516517623</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 44.841x + -19367.250</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>389.3162630114839</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3246.866204574776</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.448483453491044e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6669684330727591</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-213.3079999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.43368e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.754</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1211278767167347</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8575363153693312</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.248319701926778</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24.59997745335877</v>
+      </c>
+      <c r="J9" t="n">
+        <v>58.84212245370388</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.77241592232483</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 46.666x + -19817.192</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>385.959650966054</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3207.657416673737</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.600902006448315e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6349211170253005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-198.412</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.43162e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.863</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1603822997649117</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8848762452763849</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.062226087585731</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14.39674161085175</v>
+      </c>
+      <c r="J10" t="n">
+        <v>63.65532405535298</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.84041693729746</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 49.404x + -20694.792</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>387.3450379457233</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6379.659292308062</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.122412543331055e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7933009686804277</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-184.275</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43006e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.955</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6452256822340328</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.443121094046478</v>
+      </c>
+      <c r="H11" t="n">
+        <v>39.68419032078065</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>68.5835508410199</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.95390704849997</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 54.765x + -22756.507</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>383.2532454365163</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>312966827.1727201</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.644941800157093e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9782682150218491</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-411.295</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.46314e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.242</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2059864383734093</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.86868901378242</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.845211220641163</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.428998334951572</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.17510476110219</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.76498880630163</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 25.623x + -12826.701</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>445.5217413763704</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>364301404.1346943</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.91923481557885e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9583470646485271</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-325.431</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.45624e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.831</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1533933466527184</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6183815582476688</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.782174170631141</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.463221784909456</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36.23805081436807</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.19650747490451</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 31.759x + -15183.470</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>427.9261418923682</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>15303.38066629657</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.88800024798695e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9999977050154838</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-269.539</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.44916e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.179</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2705555679152608</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.01210002301506</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.482200100315166</v>
+      </c>
+      <c r="I4" t="n">
+        <v>30.82422203876305</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.94538629382376</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.49949242872881</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 38.176x + -17996.417</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>428.6542212651177</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>116762374.6555094</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.765931770364124e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9694633329565993</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-233.819</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.44353e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.414</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2707273831914636</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8999759155717224</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.184741674272713</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22.6341276390077</v>
+      </c>
+      <c r="J5" t="n">
+        <v>52.87542163232857</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.6738344489425</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 43.196x + -20102.819</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>423.9464700506286</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>173605973.5623363</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.728458101141928e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9721247177853118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-208.241</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.43943e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.58499999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2448698978735633</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9297276202254495</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.083110923611488</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.680965533797732</v>
+      </c>
+      <c r="J6" t="n">
+        <v>59.9148325463306</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.80615247011848</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 47.986x + -22072.289</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>409.4762507523336</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6634.489808736175</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.474904544031344e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9104443705026902</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-188.177</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.43615e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.726</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3219977293189288</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.178421286101475</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.47936003148988</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>67.64333315961575</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.89680133452164</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 51.930x + -23590.427</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>414.7822903069173</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>464361701.3064986</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.679803956322664e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9756979943363299</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-171.5380000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.43417e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.84399999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2192921871439489</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.063379702293585</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.282844245367996</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>75.15281033102391</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.96059567111276</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 55.118x + -24738.503</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>410.6263840299802</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>224219218.8157094</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.662751648033464e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9770406258276019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-159.1630000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.43228e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.944</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05118988029425977</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.969596873840784</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.839921183871087</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>82.0414138919255</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.97844311556345</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 56.081x + -24829.512</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>396.9008938885154</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3330.061449918616</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.344437710028993e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6681430773683831</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-148.453</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.43116e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-87.02</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1742507461667912</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.062165249780565</v>
+      </c>
+      <c r="H10" t="n">
+        <v>42.60515217841277</v>
+      </c>
+      <c r="I10" t="n">
+        <v>16.85627625961427</v>
+      </c>
+      <c r="J10" t="n">
+        <v>89.14077185931664</v>
+      </c>
+      <c r="K10" t="n">
+        <v>89.04388766450577</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 59.920x + -26313.311</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>394.4043571083006</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3299.951747559794</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.67483432733058e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6795188648528611</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-140.0120000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43021e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-87.07899999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5395662438290054</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.236436662336845</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4296171345155942</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.253989809740849</v>
+      </c>
+      <c r="J11" t="n">
+        <v>93.30280411486554</v>
+      </c>
+      <c r="K11" t="n">
+        <v>89.12237823926489</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 65.280x + -28470.458</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>392.0388811811654</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3273.180475907599</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.128354893777338e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6249177268667451</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-130.943</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.42966e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-87.14700000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4541478536429603</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.260172077986908</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>63.21899903588657</v>
+      </c>
+      <c r="J12" t="n">
+        <v>103.7831074796338</v>
+      </c>
+      <c r="K12" t="n">
+        <v>89.14996582156013</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 67.399x + -29121.175</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>389.7561682247307</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3245.541536701804</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.700437883643665e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.6325172106567057</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-126.54</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.42903e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-87.19499999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3018321585745657</v>
+      </c>
+      <c r="G13" t="n">
+        <v>82.32831890833661</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.005005775968096</v>
+      </c>
+      <c r="I13" t="n">
+        <v>77.14292714228635</v>
+      </c>
+      <c r="J13" t="n">
+        <v>108.0719001161687</v>
+      </c>
+      <c r="K13" t="n">
+        <v>89.16134179986844</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 68.314x + -29230.219</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>387.4442877909653</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3218.404699776368</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.583406276037654e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6366755061964129</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-118.631</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.42868e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-87.249</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5066352048371567</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15.94403999700256</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57.07998708018266</v>
+      </c>
+      <c r="J14" t="n">
+        <v>114.7237880779391</v>
+      </c>
+      <c r="K14" t="n">
+        <v>89.20508838239715</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 72.074x + -30606.603</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>389.7406547608484</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6428.329509532081</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.404332381958741e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7603143428010402</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-114.64</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.42845e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-87.29300000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4212676031016663</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>121.5435319611368</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89.1878417462287</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 70.543x + -29635.204</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>387.2330232416897</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1685873676.812895</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.602149282356551e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9821131271518025</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-111.169</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.42846e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-87.334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2648942239331119</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.112252316526112</v>
+      </c>
+      <c r="J16" t="n">
+        <v>125.6699085567055</v>
+      </c>
+      <c r="K16" t="n">
+        <v>89.18097761505307</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 69.952x + -29097.288</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>384.180802477226</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>32699356.54622534</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.595471982436994e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9827547239918457</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-106.103</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.42851e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-87.374</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3114374268644638</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>27.13985504973357</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>132.9781427317299</v>
+      </c>
+      <c r="K17" t="n">
+        <v>89.20381774901686</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 71.959x + -29700.810</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>381.1678759208106</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>156745896.91315</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.592581634940034e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9830424839695814</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-101.91</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.42865e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-87.40900000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.99454425808437</v>
+      </c>
+      <c r="G18" t="n">
+        <v>23.18359254647</v>
+      </c>
+      <c r="H18" t="n">
+        <v>27.52088045515272</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>137.7744023930748</v>
+      </c>
+      <c r="K18" t="n">
+        <v>89.24646638241214</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 76.032x + -31154.694</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>378.1684127705454</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>824277120.1782154</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.589103556328105e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9833912377264868</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-99.745</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.42879e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-87.43899999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21.59470286553895</v>
+      </c>
+      <c r="H19" t="n">
+        <v>24.56384967748641</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>140.8590334000464</v>
+      </c>
+      <c r="K19" t="n">
+        <v>89.24863645460839</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 76.251x + -30964.859</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>375.2080221451005</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>204741793.2675469</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.585612533663524e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9837469604722237</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-97.34300000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.42897e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-87.476</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12.44478804006545</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.73351564673546</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.30098360183226</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>147.9102010569628</v>
+      </c>
+      <c r="K20" t="n">
+        <v>89.20082965421912</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 71.689x + -28783.942</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>372.271572841044</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>102338665.8058016</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.581391330094839e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9841762427238474</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-94.233</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.42901e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-87.506</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>119.1564960831399</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.90623181058468</v>
+      </c>
+      <c r="J21" t="n">
+        <v>151.2264079338039</v>
+      </c>
+      <c r="K21" t="n">
+        <v>89.22789773890457</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 74.203x + -29563.860</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>369.2783700430094</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>167282172.5652885</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.578380550462287e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9844766365161687</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-90.32999999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.42914e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-87.544</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1176760841413539</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23.42304300595208</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.807477104156312</v>
+      </c>
+      <c r="J22" t="n">
+        <v>162.4989948078652</v>
+      </c>
+      <c r="K22" t="n">
+        <v>89.24567236948779</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 75.952x + -30011.966</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>366.3474447787102</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>199545158.8411019</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.574402716137631e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9848776475961103</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-698.2180000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.46552e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.50700000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1925491804141725</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8744031192422377</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.061046529614885</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.66126614381116</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.10449652226727</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.686x + -7984.235</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>465.9385210326996</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>125944830.0616441</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.217924434706812e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9369197037901673</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-536.298</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.48235e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.629</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2284996415826582</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7266619909554093</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.761101557097582</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.369580172889659</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.91215541130907</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.07975860361393</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 19.603x + -9314.389</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>429.6809189207714</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>235133123.0002992</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.027784351602589e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9520877344335995</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-432.936</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.47334e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.30800000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2143156944160017</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8092714297959385</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.792694903214924</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.434349116589851</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.3283097717079</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.63522719125206</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 24.215x + -11088.536</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>419.1457457201915</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>114473230.6109785</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.912782323924476e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9599419137558218</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-358.3320000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.46346e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.771</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2925773793764858</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.08152617807323</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.313638347615063</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.027492724142349</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32.2230618559198</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.04764426360474</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.336x + -13231.085</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>412.8967978783018</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>119797743.5511172</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.835494335189894e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9651419885269856</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-303.413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.45553e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.116</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5493934765802965</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.410188971512364</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.34181537244983</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.872209861731851</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.54666385935315</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.35315008012894</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 34.782x + -15489.980</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>395.9831167167076</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3336.055198839147</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.05322933536866e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7126686329610542</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-266.626</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.44965e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.36499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5074132763959316</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.155739487157557</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.290057272069526</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.62736838107926</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44.84446357357221</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.52520479587945</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 38.841x + -17009.142</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>392.2258068671704</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3287.626786119543</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.265270617677732e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6695571729866691</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-237.98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.44513e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.56100000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4537020212548949</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.051677884267775</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.403075732523242</v>
+      </c>
+      <c r="I8" t="n">
+        <v>52.71086676115873</v>
+      </c>
+      <c r="J8" t="n">
+        <v>51.25480753216245</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.65921782205136</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 42.725x + -18422.555</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>388.5763487116285</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3241.865783801222</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.159831949522686e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6242997012247486</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-216.23</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.44184e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.729</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02545865638593039</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6785801560275218</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.063260045783374</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30.70849064733947</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57.90919636980156</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.72436859326332</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 44.908x + -19002.983</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>385.0824326971173</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3198.838064944804</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.578920216903476e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6356469724392596</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-198.86</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.43944e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.839</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5841831652325623</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.113043009863059</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.411604419681786</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.28070185496962</v>
+      </c>
+      <c r="J10" t="n">
+        <v>62.64111663167108</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.85729932848511</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 50.134x + -21035.600</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>386.4806172968474</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6365.913405262596</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.397234723466366e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7610592166744905</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-185.408</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43775e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.94799999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2279369343337856</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.162545917706498</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.331421121767884</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>68.69587973279077</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.89963523684352</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 52.063x + -21517.563</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>382.3158348878899</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>416139392.9200711</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.654709682333789e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9781914278896926</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-509.7910000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.48966e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.602</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1950795110801365</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8832796669262837</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.83941065869744</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.575998979197658</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.1678380711639</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.18653222989532</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 20.348x + -10250.959</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>447.743774507379</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>30778583.24879043</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.052089358659983e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9509693409218157</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-342.783</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.46983e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.67700000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3243019859946038</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9867661453656977</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.268661707157932</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.531952404968413</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.95171831545183</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.10521808608657</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 30.228x + -14561.042</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>435.21944108829</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>475366282.7591516</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.86397735280607e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9634121185905193</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-273.986</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.45814e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.13500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04973484883749691</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7417335734405835</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.212154208197443</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.993358272928293</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.15111167618797</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.42475046954964</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 36.363x + -17150.115</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>412.6806406451644</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3522.630093569946</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.578283406252619e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7431792652140136</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-231.005</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.4504e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.407</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1765171855787109</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8173243094259266</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.033987566480522</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.145366021340354</v>
+      </c>
+      <c r="J5" t="n">
+        <v>53.41866753661562</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.64437714473877</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 42.257x + -19714.397</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>425.0270033480434</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>231840496.8403437</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.740383282684285e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9717846255995866</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-201.1249999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.44557e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.59699999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5134047949762769</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.249166310547523</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.500535000286332</v>
+      </c>
+      <c r="I6" t="n">
+        <v>28.87007287994195</v>
+      </c>
+      <c r="J6" t="n">
+        <v>63.05085311496209</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.82450896285805</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 48.735x + -22545.273</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>422.7110849134795</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10926.48629287233</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.44331616981372e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9996051177293487</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-184.603</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.44212e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.72799999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2714925078547025</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.967604981890549</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.038417045439191</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50.89110683042671</v>
+      </c>
+      <c r="J7" t="n">
+        <v>70.0346869879685</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.85921148358472</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 50.218x + -22886.242</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>416.3709010465464</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>227030833.2324212</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.689034763179671e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9754734755785102</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-171.938</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.43979e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.825</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2852091473322986</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9413860218299669</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.934828154734594</v>
+      </c>
+      <c r="I8" t="n">
+        <v>43.40849476679223</v>
+      </c>
+      <c r="J8" t="n">
+        <v>75.8719893605862</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.91292527282339</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 52.700x + -23744.987</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>413.121377527487</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6683.192422803645</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.106353207470936e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7816812558426494</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-159.488</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.43841e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.91200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2687994240041698</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9695587177550111</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.967428379470031</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30.42269536762668</v>
+      </c>
+      <c r="J9" t="n">
+        <v>82.30315231334518</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.9661537017887</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 55.414x + -24730.506</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>409.2460785515499</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5466.576901333721</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.727846956299995e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8478032682312012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-148.47</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.43722e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.982</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5642957837302314</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.537330056319824</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.765818925248256</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>89.3369242063621</v>
+      </c>
+      <c r="K10" t="n">
+        <v>89.06871706157064</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 61.518x + -27316.270</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>395.8910871285624</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3320.625198204999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.574161057298543e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6863964127987041</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-145.249</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43611e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-87.035</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08347917902598105</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8886899371652173</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.983320566520368</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.513208850372214</v>
+      </c>
+      <c r="J11" t="n">
+        <v>92.31452673024421</v>
+      </c>
+      <c r="K11" t="n">
+        <v>89.00823369920913</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 57.766x + -25295.647</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>393.8316717896972</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3293.769767612086</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.578325690877909e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6819802183137279</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-139.0890000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.43544e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-87.08199999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3333113356562042</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.08970173429023</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.213284585796286</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>97.46096450505657</v>
+      </c>
+      <c r="K12" t="n">
+        <v>89.05655104008662</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 60.725x + -26418.907</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>391.8424530579769</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3270.317355555084</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.066630005625109e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.6254732877058276</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-131.6079999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.4353e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-87.131</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5597341464822598</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.381217285494777</v>
+      </c>
+      <c r="H13" t="n">
+        <v>57.70506455825574</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.410382448788007</v>
+      </c>
+      <c r="J13" t="n">
+        <v>102.4531845583565</v>
+      </c>
+      <c r="K13" t="n">
+        <v>89.1296181681449</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 65.823x + -28499.843</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>389.8289478579588</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3246.622202714017</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.708662111489181e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6318400119149941</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-128.303</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.43474e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-87.16800000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.419576051462992</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.275070550830177</v>
+      </c>
+      <c r="H14" t="n">
+        <v>43.1558444238731</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>105.7101513331248</v>
+      </c>
+      <c r="K14" t="n">
+        <v>89.13147266081205</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 65.964x + -28311.090</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>387.8941981626574</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3225.342151708438</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.619389206315173e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.6352034107546096</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-122.366</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.43446e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-87.214</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5356623742648906</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.280961405844801</v>
+      </c>
+      <c r="H15" t="n">
+        <v>44.6081907936746</v>
+      </c>
+      <c r="I15" t="n">
+        <v>16.84501800489797</v>
+      </c>
+      <c r="J15" t="n">
+        <v>111.4458634800138</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89.15968101814754</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 68.178x + -29049.599</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>391.1532336160193</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6451.145522897522</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.050197949507803e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8119579070368823</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-120.816</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.43442e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-87.246</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3413539175300419</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.055185355829462</v>
+      </c>
+      <c r="H16" t="n">
+        <v>29.57353170918867</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>112.8557175783032</v>
+      </c>
+      <c r="K16" t="n">
+        <v>89.11445303669798</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 64.696x + -27259.194</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>388.8264473583125</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>159832079.2250715</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.615536210353232e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9814689125112368</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-116.407</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.43441e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-87.28100000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4591734488888983</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.084635221674765</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.432010133908</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>116.8060187004285</v>
+      </c>
+      <c r="K17" t="n">
+        <v>89.16896176629569</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 68.940x + -28880.545</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>386.034710055192</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>420412153.1588411</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.611705287351e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9818357171934463</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-113.7910000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.43414e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-87.315</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4211131216884566</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.144760675858397</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24.13379308222178</v>
+      </c>
+      <c r="I18" t="n">
+        <v>87.14393014824773</v>
+      </c>
+      <c r="J18" t="n">
+        <v>123.3406603157688</v>
+      </c>
+      <c r="K18" t="n">
+        <v>89.16317318030586</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 68.463x + -28425.147</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>383.2136317446345</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>313980803.5212577</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.607471483106774e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9822118464404277</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-110.864</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.43426e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-87.34399999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3520642412077271</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.185567329385985</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>95.06359465549689</v>
+      </c>
+      <c r="J19" t="n">
+        <v>124.8685987512335</v>
+      </c>
+      <c r="K19" t="n">
+        <v>89.19079324006958</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 70.800x + -29184.068</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>380.3232093163263</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>310644615.4314929</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.604137434342052e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9825472664208442</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-107.718</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.43445e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-87.377</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.303949794740728</v>
+      </c>
+      <c r="G20" t="n">
+        <v>77.00186893994545</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.53686433003766</v>
+      </c>
+      <c r="I20" t="n">
+        <v>69.51125562032557</v>
+      </c>
+      <c r="J20" t="n">
+        <v>130.9732848146434</v>
+      </c>
+      <c r="K20" t="n">
+        <v>89.19279528563034</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 70.976x + -28988.997</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>377.3952586420104</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>206279049.5861789</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.60055151696587e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9829095447455423</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-104.699</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.43491e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-87.40300000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6120557306531654</v>
+      </c>
+      <c r="G21" t="n">
+        <v>28.17592677371058</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>66.41478437562661</v>
+      </c>
+      <c r="J21" t="n">
+        <v>132.0586861027249</v>
+      </c>
+      <c r="K21" t="n">
+        <v>89.25410106462239</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 76.810x + -31198.966</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>374.4372449724538</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>319226464.8156897</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.598147789401788e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.983191267320505</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-103.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.43515e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-87.43300000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5888094392421295</v>
+      </c>
+      <c r="G22" t="n">
+        <v>32.85695096432471</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.17967565383666</v>
+      </c>
+      <c r="J22" t="n">
+        <v>137.8713027085747</v>
+      </c>
+      <c r="K22" t="n">
+        <v>89.21795392947773</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 73.259x + -29436.657</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>371.479829090248</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>606907419.4105353</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.595275182660601e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9834955641109866</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-916.8920000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.57293e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.94</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1458071414842707</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5894388043392587</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.332665507107203</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.731630894249228</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.25412374512587</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.69387133424055</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.767x + -5387.806</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>439.5821624890179</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>179437612.1642645</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.656262698550957e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9206783514761252</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-624.9380000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.55133e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3297100366831963</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9001482719099967</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.946329377916797</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.760178550018705</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.92208242469651</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.45393516384725</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.137x + -7388.070</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>400.8704822541768</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3419.239551428888</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.532936774713646e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7370591481815131</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-458.975</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.52503e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.056</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2578768724022593</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9800379232129497</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.097206780106089</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.968178675168363</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.90934423252638</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.41118647874454</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 22.117x + -9881.900</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>409.407617747873</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>181930353.206481</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.018214439935201e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9570432031100142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-360.698</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.50662e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.69799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1978888461933131</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7397775158056628</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.079130682926888</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.543063266820791</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.45434620358342</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.94948734474607</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 27.930x + -12292.182</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>392.2942363708429</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3311.443666203407</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.426062328510996e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6946169540452056</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-295.8559999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.49432e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.10899999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6726147200026024</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.258241451334412</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.240244151311418</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.200094581817688</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39.15809653791465</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.31136112682967</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 33.920x + -14767.628</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>389.1104300571027</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3266.097246308253</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.625341197155095e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6865098081672082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-252.701</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.48639e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.399</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3182167828106994</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.158970684605528</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.257108827089283</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.329277694670078</v>
+      </c>
+      <c r="J7" t="n">
+        <v>46.83510260689462</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.52341347472644</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 38.794x + -16633.027</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>385.7990518375054</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3219.360410303704</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.694982343220032e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6302576555915422</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-224.205</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.48072e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2569360457607195</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9909652539684836</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.197119503204801</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.242127832209206</v>
+      </c>
+      <c r="J8" t="n">
+        <v>53.87317226550037</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.64962108815162</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 42.422x + -17889.926</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>387.7873766025926</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6402.446348565064</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.583818891856134e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.835353369684867</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-199.7330000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.47724e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3719344938100666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.302471527137695</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.140956709185947</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.29657807805067</v>
+      </c>
+      <c r="J9" t="n">
+        <v>61.21485024353517</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.7830010822081</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 47.072x + -19597.341</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>383.7743960295181</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>313346146.0761515</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.723040403138065e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9761513105903162</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-184.455</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.475e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.896</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09361332141376247</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7860254070705663</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.801789865981753</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.633897319915755</v>
+      </c>
+      <c r="J10" t="n">
+        <v>67.01401299143372</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.82390532328188</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 48.710x + -19947.208</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>379.1208119834776</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>206565007.5045739</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.704464585334878e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9775685726083856</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-168.986</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.47335e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3920894475119457</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.147704848237603</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.072365186816426</v>
+      </c>
+      <c r="I11" t="n">
+        <v>38.68604571496671</v>
+      </c>
+      <c r="J11" t="n">
+        <v>74.33755334938022</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.92454085184558</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 53.269x + -21601.165</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>374.8848460024854</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>229459817.9932854</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.689847293904402e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9787166590237585</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-371.904</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.51399e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2292053978879659</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8759101704768288</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.868902380930953</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.334426381536433</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.19174442467736</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.82290876471947</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 26.305x + -13183.646</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>445.2107445227359</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>484757949.2143062</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.985003324268114e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9583532847736836</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-270.399</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.49834e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-86.002</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4069915713887124</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.382722875312195</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.086461376278661</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.678044039904082</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43.98562631472151</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.4011402363483</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 35.826x + -17219.712</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>414.0888565555738</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3551.88036038065</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.824848398905355e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7294442315509895</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-223.461</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.48879e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.319</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6832747166325229</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.309178561605427</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.301456991374557</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.253608215286931</v>
+      </c>
+      <c r="J4" t="n">
+        <v>54.5446183790102</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.65591714947475</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 42.620x + -20167.683</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>427.8187709455693</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>240267045.2171544</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.799402542672796e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9706712931760222</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-196.9239999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.48296e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3377967277484958</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8685864998310625</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.087956972862759</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.967804344001123</v>
+      </c>
+      <c r="J5" t="n">
+        <v>63.8596371918139</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.7299404691602</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 45.105x + -20992.341</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>423.4845522674789</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>230711883.3746552</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.764613456250841e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9730451771880099</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-180.642</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.47905e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.64400000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2056940400910255</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9785322360228204</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.160506119185388</v>
+      </c>
+      <c r="I6" t="n">
+        <v>29.58168384987797</v>
+      </c>
+      <c r="J6" t="n">
+        <v>70.96386325177357</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.80509088880189</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 47.943x + -22050.598</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>419.3363685423765</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>114431946.7009747</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.742469253335535e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9745720067180582</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-167.714</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.47673e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.745</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1228651537141657</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.829782113657682</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.87546524546391</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.428990491449566</v>
+      </c>
+      <c r="J7" t="n">
+        <v>76.3039613099418</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.85215892479286</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 49.909x + -22692.498</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>415.069877870661</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6699.275184442167</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.432145177788463e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8402983123840755</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-158.921</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.47524e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.827</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1360267418209382</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7268598203902856</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.67278878622605</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.398334593052569</v>
+      </c>
+      <c r="J8" t="n">
+        <v>81.56281243102093</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.8574131229344</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 50.139x + -22513.854</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>411.7900922825735</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6788.468379783648</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.638363161511533e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8741868035379186</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-147.3020000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.47422e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.898</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3673627027089082</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.215447472850204</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.506819302244316</v>
+      </c>
+      <c r="I9" t="n">
+        <v>38.39684851266294</v>
+      </c>
+      <c r="J9" t="n">
+        <v>89.32171975412756</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.99057701950217</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 56.755x + -25371.295</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>397.3939176713774</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3339.040714941274</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.251818003045368e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.6695653512320575</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-142.7090000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.47345e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.95</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3410251925219966</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.397413500147951</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.266369216354575</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.430005299430585</v>
+      </c>
+      <c r="J10" t="n">
+        <v>93.7724216068379</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.99394217515265</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 56.945x + -25198.542</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>394.9405005528467</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3312.978033132198</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.572980120354203e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6805896875607824</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-138.268</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.47276e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.997</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4065955793458744</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9820423473630473</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.923855963719443</v>
+      </c>
+      <c r="I11" t="n">
+        <v>36.10224791246267</v>
+      </c>
+      <c r="J11" t="n">
+        <v>95.83319170819763</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.99417310334179</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 56.958x + -24938.719</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>392.6520746059164</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3285.306692972217</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.877486350574464e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6526092727617582</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-134.1199999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.47245e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-87.041</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2279642236486098</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.03879488990274</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.054022985831914</v>
+      </c>
+      <c r="I12" t="n">
+        <v>29.5582845439287</v>
+      </c>
+      <c r="J12" t="n">
+        <v>99.35020959134143</v>
+      </c>
+      <c r="K12" t="n">
+        <v>89.0113552010319</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 57.948x + -25150.243</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>390.4070269839705</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3257.477024161224</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.730720833761005e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.6307817034250055</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-128.152</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.47247e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-87.08499999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3891483258136423</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.340505896964026</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.449927819187408</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4957955112764292</v>
+      </c>
+      <c r="J13" t="n">
+        <v>105.021041843762</v>
+      </c>
+      <c r="K13" t="n">
+        <v>89.06915122590496</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 61.547x + -26531.690</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>388.1213415078581</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3232.569053716101</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.629135381785853e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6346006875393772</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-123.9520000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.47216e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-87.134</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2617647120249922</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9509140517004793</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.01633400268642</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.007675167515963</v>
+      </c>
+      <c r="J14" t="n">
+        <v>109.5307017111447</v>
+      </c>
+      <c r="K14" t="n">
+        <v>89.03403213158484</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 59.309x + -25280.494</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>390.583764969574</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6458.350086340269</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.23462095952067e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7741013293075699</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-122.354</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.47205e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-87.161</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.239777436988743</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9633272914733254</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.975382731945476</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.523147131837248</v>
+      </c>
+      <c r="J15" t="n">
+        <v>110.7282543408883</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89.04748147753429</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 60.146x + -25419.839</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>389.2140831090402</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>212123666.6558876</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.667756367745261e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9805657373557194</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-119.337</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.47199e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-87.191</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5105954516420155</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.16399332589215</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.206331608491171</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>112.6208813698807</v>
+      </c>
+      <c r="K16" t="n">
+        <v>89.09557239948225</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 63.345x + -26595.582</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>386.1619194211478</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>630147973.6149029</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.664281427213033e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9808823324143803</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-110.985</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.47301e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-87.252</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3633071108191505</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.243313126023183</v>
+      </c>
+      <c r="H17" t="n">
+        <v>46.77429937829264</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.558191734369867</v>
+      </c>
+      <c r="J17" t="n">
+        <v>123.5526502796577</v>
+      </c>
+      <c r="K17" t="n">
+        <v>89.1260787236988</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 65.557x + -27301.216</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>383.1139822365346</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>235037887.056922</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.658346229963305e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9815290895776586</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-113.409</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.47247e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-87.259</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5018124156540074</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.11493532627462</v>
+      </c>
+      <c r="H18" t="n">
+        <v>36.52464859101643</v>
+      </c>
+      <c r="I18" t="n">
+        <v>61.37418987871618</v>
+      </c>
+      <c r="J18" t="n">
+        <v>122.2383678319495</v>
+      </c>
+      <c r="K18" t="n">
+        <v>89.11289757595712</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 64.582x + -26639.038</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>380.0618972010561</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1033766805.194658</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.656828516500103e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9816209907570435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-110.349</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.47271e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-87.291</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4116587596975646</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.218825373800666</v>
+      </c>
+      <c r="H19" t="n">
+        <v>32.0943230244362</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.015664136821234</v>
+      </c>
+      <c r="J19" t="n">
+        <v>121.8892906166401</v>
+      </c>
+      <c r="K19" t="n">
+        <v>89.14182050853864</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 66.759x + -27314.911</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>376.961918160021</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>309418650.2319997</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.653061657371997e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9820010834511069</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-108.847</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.47275e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-87.322</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4066497606996921</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.088027152078596</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11.41361968853344</v>
+      </c>
+      <c r="I20" t="n">
+        <v>51.45684682116918</v>
+      </c>
+      <c r="J20" t="n">
+        <v>128.0449417670068</v>
+      </c>
+      <c r="K20" t="n">
+        <v>89.13020675648549</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 65.868x + -26689.192</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>373.938434749889</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>205348113.3277394</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.649336675343289e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9823539224522917</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-109.006</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.47295e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-87.345</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2760811216853171</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9130168825225143</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.30310778615464</v>
+      </c>
+      <c r="I21" t="n">
+        <v>61.73107249312272</v>
+      </c>
+      <c r="J21" t="n">
+        <v>127.0583295218604</v>
+      </c>
+      <c r="K21" t="n">
+        <v>89.09339115417504</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 63.193x + -25320.881</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>370.903070994451</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>38637295.74779098</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.645484748636624e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9827367452978</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-106.333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.47365e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-87.369</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6714070932454794</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.131874686963183</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>42.88351096776944</v>
+      </c>
+      <c r="J22" t="n">
+        <v>129.0660872073018</v>
+      </c>
+      <c r="K22" t="n">
+        <v>89.16389312927488</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 68.522x + -27301.233</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>367.7975938516235</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>800821460.7859757</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.645206086526355e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9828374030987175</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-754.7139999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.55372e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.039</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04738333586731697</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3206346233204299</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.034171585156763</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.148366429471708</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.316667755847</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.59107526851361</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.970x + -6441.186</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>431.8804385697641</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>236325911.4878342</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.421535611000204e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9325885994459102</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-497.308</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.54859e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.804</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1385832825640608</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7841302783169236</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.871968014347045</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.056646001154741</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.7712597562457</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.13674553142994</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 19.994x + -8801.431</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>388.8880946342742</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3286.19399190833</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.320028754645425e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8835133387878162</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-361.8100000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.53088e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.688</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3841822320281821</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.112043713403548</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.035832029625437</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.977970272417165</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.83619877757449</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.91102970620548</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 27.416x + -11727.899</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>383.6039142069445</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3210.996368504371</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.203063429814494e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.6724951138049746</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-284.087</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.51792e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.191</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3824815865688868</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.343763967973147</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.279785239723245</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.37593002576943</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.48580457419422</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.32852274969719</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 34.269x + -14433.980</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>386.2083336826761</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6380.724393138067</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.038272625164862e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.859611520136535</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-238.5700000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.50988e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.506</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04114586801431521</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7574590820279299</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.879624447070336</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.789237764879073</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49.85538818688924</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.51560631152049</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 38.590x + -15955.651</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>382.4736754823203</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>209185431.4402277</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.794745490306424e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9732745673122102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-206.832</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.50524e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.724</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1982195727913589</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.000100437336305</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.959561973003111</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.810803984085168</v>
+      </c>
+      <c r="J7" t="n">
+        <v>58.74190409315504</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.65957793641439</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 42.737x + -17405.514</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>377.2917233827275</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>307775388.5564924</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.761317038744865e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9756615362415106</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-184.732</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.50224e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.877</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2569265832587139</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.008061290595036</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.970472738356537</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.601342300409536</v>
+      </c>
+      <c r="J8" t="n">
+        <v>66.32953090142806</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.78294966683336</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 47.070x + -18921.753</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>372.3037068619515</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>304006294.589339</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.73812905593134e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.977381857124623</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-169.393</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.50088e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.99299999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5275591011210629</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.230899185061016</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.145109127991847</v>
+      </c>
+      <c r="I9" t="n">
+        <v>37.18397857259151</v>
+      </c>
+      <c r="J9" t="n">
+        <v>74.42598544950813</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.87275466523322</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 50.822x + -20167.596</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>367.5314693890718</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>38393525.61343922</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.720479364240339e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9788022244373353</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-156.482</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.50031e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-87.089</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5394665844542564</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.35767389866034</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.362572431479899</v>
+      </c>
+      <c r="I10" t="n">
+        <v>29.91690095219927</v>
+      </c>
+      <c r="J10" t="n">
+        <v>81.0801175697478</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.93311863277523</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 53.698x + -21028.191</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>363.1266844353947</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>148258672.0502665</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.709239146154232e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9797430798266125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-147.681</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.50046e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-87.16200000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4734379631402365</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.316103757860133</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.232374486206331</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26.57226962424973</v>
+      </c>
+      <c r="J11" t="n">
+        <v>86.60120843249781</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.9737992355857</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 55.827x + -21600.451</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>351.5106155674105</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5898.008891584643</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.235512271654899e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7930270991523264</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-608.6600000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.5369e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.914</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2785191139918084</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8892966623409297</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.899770046115609</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.545052544910743</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.59692457140864</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.56603481257713</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 16.665x + -8204.892</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8204.891919915419</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>445.0244163987439</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>608.6600000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.228960720397941e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9431952925240271</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-487.385</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.50123e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.77500000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1975051182707226</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9346805205780346</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.752465745704763</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.497089253516159</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22.82244741267145</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.30161957723325</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 21.218x + -10274.914</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10274.91400160013</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>438.7994999563107</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>487.385</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.03784965291014e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9531298208429709</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-416.6139999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.48329e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.27200000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.08309429603688401</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6385647022010473</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.780933521589282</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.698020984226417</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27.40069509148915</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.68508427257339</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 24.737x + -11761.524</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11761.52385783254</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>432.8256052678489</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>416.6139999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.938977506697763e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9588141492459019</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-361.974</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.47135e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.61799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7439905342003544</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.719694749076641</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.565945310021589</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.125897675567046</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.59376441137767</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.03375180799974</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 29.128x + -13739.046</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13739.04637824691</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>411.3187824562365</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>361.974</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.630400549407319e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7387540163156397</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-325.338</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.46258e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6228190897135595</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.173026524571004</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.235963805513922</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.128728747136414</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.76462183950861</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.22545674805478</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 32.277x + -14992.525</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14992.52478000839</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>421.866699372222</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>325.338</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.824509949546205e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9658957504319755</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-294.284</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.45626e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.108</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3137097772139661</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.820794075833813</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.408307774974133</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.825903441310532</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40.31971103848736</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.3652592097021</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 35.039x + -16004.119</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16004.11879585791</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>413.3690171197563</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>294.284</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.370851338602851e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9632196828583551</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-269.049</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.45096e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.283</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2476589464368071</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8629026124045522</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.255831732782069</v>
+      </c>
+      <c r="I8" t="n">
+        <v>41.27828465846257</v>
+      </c>
+      <c r="J8" t="n">
+        <v>45.09585069468846</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.48841713881001</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 37.896x + -17093.425</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17093.42473464095</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>412.9992153348903</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>269.049</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.756077495807179e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9704915414757052</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-248.641</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.44661e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.429</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2578187686538379</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9907504140241142</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.087084290957009</v>
+      </c>
+      <c r="I9" t="n">
+        <v>37.67098400262385</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49.33138541099138</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.5885531646659</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 40.585x + -18100.591</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18100.59079228311</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>397.4850624089426</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>248.641</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.088510335412902e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7118209399384114</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-225.139</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.44317e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.574</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4573048808325964</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.195093895634331</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.344799995336352</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.40769635172419</v>
+      </c>
+      <c r="J10" t="n">
+        <v>54.72323278274322</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.73948548702943</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 45.447x + -20143.103</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20143.10255451971</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>406.4658718266165</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>225.139</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.027691994699986e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8544745903309675</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-212.641</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43999e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.676</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2825786075686996</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.016218396030067</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.104335840771005</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26.1678314033804</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.98666517192155</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.77140104859826</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 46.628x + -20407.899</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20407.89935235872</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>392.7309796848951</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>212.641</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.521469716471364e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6877219055020486</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>88.2343794523108</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 32.441x + -16105.915</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-16105.91496641924</v>
       </c>
       <c r="Y2" t="n">
         <v>419.2326892825938</v>
       </c>
       <c r="Z2" t="n">
-        <v>7283.020815301395</v>
+        <v>286.5500000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>7.208497343607827e-07</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>88.51704152719303</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 38.628x + -18438.480</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-18438.47981940698</v>
       </c>
       <c r="Y3" t="n">
         <v>415.8312423507439</v>
       </c>
       <c r="Z3" t="n">
-        <v>3537.425526003954</v>
+        <v>229.497</v>
       </c>
       <c r="AA3" t="n">
         <v>1.058952545786878e-06</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>88.63173771670471</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 41.867x + -19638.793</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-19638.79252253433</v>
       </c>
       <c r="Y4" t="n">
         <v>426.9358447869628</v>
       </c>
       <c r="Z4" t="n">
-        <v>174689281.998233</v>
+        <v>200.145</v>
       </c>
       <c r="AA4" t="n">
         <v>1.81308952672996e-07</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>88.75344427271543</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 45.956x + -21341.593</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21341.5930482217</v>
       </c>
       <c r="Y5" t="n">
         <v>407.5001834965634</v>
       </c>
       <c r="Z5" t="n">
-        <v>3459.085167738524</v>
+        <v>180.649</v>
       </c>
       <c r="AA5" t="n">
         <v>1.970744449809594e-06</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>88.82438455887657</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 48.730x + -22379.847</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22379.84733407621</v>
       </c>
       <c r="Y6" t="n">
         <v>416.2955460959788</v>
       </c>
       <c r="Z6" t="n">
-        <v>5373.300659411513</v>
+        <v>168.091</v>
       </c>
       <c r="AA6" t="n">
         <v>8.886465498890387e-07</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>88.81374997364514</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 48.293x + -21849.680</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21849.67980895728</v>
       </c>
       <c r="Y7" t="n">
         <v>413.4572111420966</v>
       </c>
       <c r="Z7" t="n">
-        <v>6825.418772768077</v>
+        <v>158.6559999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>6.361469973584559e-07</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>88.91345318528198</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 52.726x + -23681.335</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23681.33456379035</v>
       </c>
       <c r="Y8" t="n">
         <v>398.6739443155888</v>
       </c>
       <c r="Z8" t="n">
-        <v>3354.608012709333</v>
+        <v>150.795</v>
       </c>
       <c r="AA8" t="n">
         <v>4.236408422876814e-06</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>88.92842992015298</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 53.463x + -23736.442</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-23736.44190164505</v>
       </c>
       <c r="Y9" t="n">
         <v>396.0362382921331</v>
       </c>
       <c r="Z9" t="n">
-        <v>3322.582231403105</v>
+        <v>142.993</v>
       </c>
       <c r="AA9" t="n">
         <v>4.439434287426658e-06</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>88.9251467226117</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 53.299x + -23408.920</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-23408.91966239561</v>
       </c>
       <c r="Y10" t="n">
         <v>393.4370342247838</v>
       </c>
       <c r="Z10" t="n">
-        <v>3294.122405107289</v>
+        <v>140.446</v>
       </c>
       <c r="AA10" t="n">
         <v>3.849900843905989e-06</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>88.95413911794064</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 54.777x + -23837.615</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-23837.61526272434</v>
       </c>
       <c r="Y11" t="n">
         <v>391.0632391930403</v>
       </c>
       <c r="Z11" t="n">
-        <v>3264.069938753463</v>
+        <v>135.631</v>
       </c>
       <c r="AA11" t="n">
         <v>5.724265934223685e-06</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>88.97330415228687</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 55.800x + -24053.498</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-24053.49785526302</v>
       </c>
       <c r="Y12" t="n">
         <v>394.0977679144297</v>
       </c>
       <c r="Z12" t="n">
-        <v>6519.887508174598</v>
+        <v>131.0170000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>9.549030011595242e-07</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>89.05634127267498</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 60.711x + -26034.306</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-26034.30608589084</v>
       </c>
       <c r="Y13" t="n">
         <v>392.8430672948829</v>
       </c>
       <c r="Z13" t="n">
-        <v>855128219.2084062</v>
+        <v>126.0149999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.712016493363925e-07</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>88.98416076772514</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 56.396x + -23863.414</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-23863.41449898794</v>
       </c>
       <c r="Y14" t="n">
         <v>389.695358208202</v>
       </c>
       <c r="Z14" t="n">
-        <v>321334355.8278245</v>
+        <v>125.866</v>
       </c>
       <c r="AA14" t="n">
         <v>1.708134112227292e-07</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>89.03575403470118</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 59.415x + -24961.219</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-24961.21932336222</v>
       </c>
       <c r="Y15" t="n">
         <v>386.6341236401993</v>
       </c>
       <c r="Z15" t="n">
-        <v>105628032.5617058</v>
+        <v>121.0189999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.702302874103545e-07</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>89.00221894496224</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 57.417x + -23863.700</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-23863.70018466999</v>
       </c>
       <c r="Y16" t="n">
         <v>383.5601705167197</v>
       </c>
       <c r="Z16" t="n">
-        <v>209024500.0176502</v>
+        <v>120.169</v>
       </c>
       <c r="AA16" t="n">
         <v>1.698854366435733e-07</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>89.03097801498369</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 59.122x + -24377.925</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-24377.9248764107</v>
       </c>
       <c r="Y17" t="n">
         <v>380.5290257264724</v>
       </c>
       <c r="Z17" t="n">
-        <v>207300632.6712884</v>
+        <v>117.5959999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.695154011482158e-07</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>89.10550813941626</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 64.049x + -26268.556</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-26268.55606877112</v>
       </c>
       <c r="Y18" t="n">
         <v>377.5196203385924</v>
       </c>
       <c r="Z18" t="n">
-        <v>117820159.098676</v>
+        <v>115.3820000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.692053420978269e-07</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>89.08940839896985</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 62.916x + -25535.822</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-25535.82191588283</v>
       </c>
       <c r="Y19" t="n">
         <v>374.4969979867185</v>
       </c>
       <c r="Z19" t="n">
-        <v>156466484.3031162</v>
+        <v>111.521</v>
       </c>
       <c r="AA19" t="n">
         <v>1.687436587151995e-07</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>89.05474568298867</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 60.609x + -24340.325</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-24340.3247656731</v>
       </c>
       <c r="Y20" t="n">
         <v>371.4986777876879</v>
       </c>
       <c r="Z20" t="n">
-        <v>222024150.6506714</v>
+        <v>111.873</v>
       </c>
       <c r="AA20" t="n">
         <v>1.68509893582668e-07</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>89.1488362482192</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 67.310x + -26900.502</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-26900.50165895274</v>
       </c>
       <c r="Y21" t="n">
         <v>368.4761277387811</v>
       </c>
       <c r="Z21" t="n">
-        <v>327113719.9689867</v>
+        <v>106.295</v>
       </c>
       <c r="AA21" t="n">
         <v>1.680504414924477e-07</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>89.10539835048284</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 64.041x + -25303.807</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-25303.80680019316</v>
       </c>
       <c r="Y22" t="n">
         <v>365.4780612686336</v>
       </c>
       <c r="Z22" t="n">
-        <v>298274177.4419369</v>
+        <v>107.269</v>
       </c>
       <c r="AA22" t="n">
         <v>1.67870213672396e-07</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-326.13</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.4458e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.70699999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3607406132644139</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.03234437970366</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.082609677607008</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.249067598662565</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37.26974350700457</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.18517492560989</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 31.560x + -16088.814</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-16088.81420677342</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>450.4684834829814</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>326.13</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.837048170211643e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9630781018369076</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-278.083</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.44701e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-86.08</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3606668270657946</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.014285812524864</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.160191964629171</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.151778607673752</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43.56101720680282</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.43713032555434</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 36.652x + -17721.496</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-17721.49634677437</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>436.945861412715</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>278.083</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.782556758605042e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9677668587007904</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-249.624</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.44392e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.297</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07433704226585361</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5154553816086164</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.644026512101666</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.371633975759122</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49.59152434380715</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.53373275930893</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 39.067x + -18470.522</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-18470.5222536253</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>414.3112736839394</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>249.624</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.562502442294363e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.744252698759901</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-224.401</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.44064e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.446</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3879423674139348</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.321138573306015</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.484484522982701</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.02126843830591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>55.78664500530981</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.72532217965134</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 44.942x + -21133.161</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21133.16091644632</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>427.0585486463653</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>224.401</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.723974774484817e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9721783028520264</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-207.116</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.438e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.58199999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09471439571052782</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9432058198692791</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.054031358628662</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30.98208550230149</v>
+      </c>
+      <c r="J6" t="n">
+        <v>61.06147280806506</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.76879421157902</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 46.529x + -21547.561</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-21547.56147767845</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>422.7493752504539</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>207.116</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.702798754841155e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9737834879306907</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-192.922</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.43573e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.68300000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1428568968535594</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8993657744343769</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.994454079773701</v>
+      </c>
+      <c r="I7" t="n">
+        <v>37.66387194752814</v>
+      </c>
+      <c r="J7" t="n">
+        <v>66.2705917233327</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.84376734030843</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 49.547x + -22702.574</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-22702.57419919123</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>418.6153878666947</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>192.922</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.686923980205979e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9749735352325676</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-180.4830000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.43369e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.782</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2142710672691781</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9156098085717993</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.043763660906011</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19.46081359100852</v>
+      </c>
+      <c r="J8" t="n">
+        <v>72.02293229990379</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.88027298043149</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 51.163x + -23160.916</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23160.91605284272</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>414.8066137859243</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>180.4830000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.671914608872588e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9761205730851896</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-170.912</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.43237e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.855</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2230673548169933</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9928664383075485</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.431619955252782</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.403966145058472</v>
+      </c>
+      <c r="J9" t="n">
+        <v>76.83572165323311</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.9374410821389</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 53.916x + -24186.023</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-24186.02289824299</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>411.1964330576128</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>170.912</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.660903334854821e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9769925866196439</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-159.095</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.43113e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.93300000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4718952694591041</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.099263689411906</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.407490499757435</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>82.43393516974481</v>
+      </c>
+      <c r="K10" t="n">
+        <v>89.02204433206558</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 58.582x + -26103.312</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-26103.31153531824</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>397.6480759034161</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>159.095</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.398185265419246e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6659332817379022</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-152.358</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.43053e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.997</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2366661892358034</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9800102674151965</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.219615326585745</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>87.50521049502312</v>
+      </c>
+      <c r="K11" t="n">
+        <v>89.00696568856972</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 57.692x + -25393.939</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-25393.93913333458</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>395.385174804119</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>152.358</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.86398736120781e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6824926402563017</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-144.2209999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.42966e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-87.053</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4483214437894611</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.233166158226024</v>
+      </c>
+      <c r="H12" t="n">
+        <v>34.83031508077826</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.318654377395548</v>
+      </c>
+      <c r="J12" t="n">
+        <v>92.70791309757264</v>
+      </c>
+      <c r="K12" t="n">
+        <v>89.08710479955295</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 62.757x + -27463.065</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-27463.06474505195</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>393.1439615832914</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>144.2209999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.640301048061864e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.6630492364665539</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-136.078</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.42916e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-87.11499999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4451871291190626</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.263405927147861</v>
+      </c>
+      <c r="H13" t="n">
+        <v>48.85694213831647</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.323086967196212</v>
+      </c>
+      <c r="J13" t="n">
+        <v>98.75776030446136</v>
+      </c>
+      <c r="K13" t="n">
+        <v>89.12278836452018</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 65.311x + -28329.992</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-28329.992125253</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>390.838525250868</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>136.078</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.755749929442009e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6304905883100571</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-131.7619999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.42854e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-87.161</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4296553433693044</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.095843051671861</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16.38514662091575</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>103.1579367081166</v>
+      </c>
+      <c r="K14" t="n">
+        <v>89.11322531876897</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 64.606x + -27727.522</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-27727.52163474765</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>388.5851151114368</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>131.7619999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.634747470496693e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.63465178739948</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-127.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.42828e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-87.197</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5464686076555584</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.291373861205821</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.63488624931479</v>
+      </c>
+      <c r="J15" t="n">
+        <v>105.5865994965467</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89.1650016430421</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 68.613x + -29245.628</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-29245.62761920104</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>391.327822567147</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.643917021953699e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9352514479345544</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-125.127</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.42802e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-87.23699999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2617129184509353</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.106646789018974</v>
+      </c>
+      <c r="H16" t="n">
+        <v>30.95825897632223</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.410231164184812</v>
+      </c>
+      <c r="J16" t="n">
+        <v>108.3046587895985</v>
+      </c>
+      <c r="K16" t="n">
+        <v>89.12779420332863</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 65.686x + -27662.537</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-27662.5367367368</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>388.7695746202324</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>125.127</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.609519091912995e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9813443311117686</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-119.9429999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.42778e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-87.282</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2187397352297945</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.071962052064052</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13.56497065075459</v>
+      </c>
+      <c r="J17" t="n">
+        <v>113.2701893536862</v>
+      </c>
+      <c r="K17" t="n">
+        <v>89.14943303210345</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 67.357x + -28123.082</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-28123.08245496312</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>385.7283556142595</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>119.9429999999999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.603503911150147e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9818962755714378</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-114.354</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.42772e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-87.325</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3581881191898013</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.250298229896885</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.491851142777003</v>
+      </c>
+      <c r="J18" t="n">
+        <v>118.6683724647427</v>
+      </c>
+      <c r="K18" t="n">
+        <v>89.19919001883319</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 71.543x + -29665.815</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-29665.81517515678</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>382.7288031680701</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>114.354</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.598774880315277e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9823446757609035</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.42793e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-87.371</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4640323302785433</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42.75605392963757</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>73.94917913957804</v>
+      </c>
+      <c r="J19" t="n">
+        <v>129.1541052059849</v>
+      </c>
+      <c r="K19" t="n">
+        <v>89.23578150019959</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 74.969x + -30852.623</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-30852.6232540144</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>379.7377611207317</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>108.39</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.594107282117107e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9828120929642581</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-108.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.42774e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-87.401</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>55.55029812630103</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>64.83841105431515</v>
+      </c>
+      <c r="J20" t="n">
+        <v>131.1443200943292</v>
+      </c>
+      <c r="K20" t="n">
+        <v>89.14549169996715</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 67.046x + -27211.056</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-27211.05566833534</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>376.8309540999307</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.590356800892361e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.983157983607033</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-104.229</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.42781e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-87.428</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4271466358948189</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15.67132988896301</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.82036928695099</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.75334142518138</v>
+      </c>
+      <c r="J21" t="n">
+        <v>135.2538130901161</v>
+      </c>
+      <c r="K21" t="n">
+        <v>89.24036593942184</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 75.421x + -30491.363</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-30491.36332095984</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>373.9924789566734</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>104.229</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.587205510494637e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9834744355635867</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-100.227</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.42815e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-87.461</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.615237403643917</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>39.36634948581876</v>
+      </c>
+      <c r="I22" t="n">
+        <v>40.41685682396033</v>
+      </c>
+      <c r="J22" t="n">
+        <v>138.396966705116</v>
+      </c>
+      <c r="K22" t="n">
+        <v>89.2594148876689</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 77.361x + -31030.122</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-31030.1220791261</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>371.1337623225913</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>100.227</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.583705252172225e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9838515278440514</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>87.19793351182348</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 20.431x + -10804.473</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10804.47260449541</v>
       </c>
       <c r="Y2" t="n">
         <v>454.5794073840062</v>
       </c>
       <c r="Z2" t="n">
-        <v>736737071.9532801</v>
+        <v>516.1890000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.003872975957584e-07</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>87.68962738094933</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.786x + -11630.288</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11630.28770275351</v>
       </c>
       <c r="Y3" t="n">
         <v>408.9207503450474</v>
       </c>
       <c r="Z3" t="n">
-        <v>3489.288174957848</v>
+        <v>424.239</v>
       </c>
       <c r="AA3" t="n">
         <v>2.324373287264978e-06</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>88.03664702988991</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 29.171x + -13296.596</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13296.59635142475</v>
       </c>
       <c r="Y4" t="n">
         <v>417.4499877467158</v>
       </c>
       <c r="Z4" t="n">
-        <v>966855033.5855224</v>
+        <v>359.397</v>
       </c>
       <c r="AA4" t="n">
         <v>1.828363463551726e-07</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>88.28014656513224</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 33.304x + -14939.030</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14939.02966586925</v>
       </c>
       <c r="Y5" t="n">
         <v>411.9548059643218</v>
       </c>
       <c r="Z5" t="n">
-        <v>112876492.8521605</v>
+        <v>312.485</v>
       </c>
       <c r="AA5" t="n">
         <v>1.778603561807484e-07</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>88.46697743725498</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 37.365x + -16558.876</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-16558.87633341621</v>
       </c>
       <c r="Y6" t="n">
         <v>396.160984841526</v>
       </c>
       <c r="Z6" t="n">
-        <v>3331.650565335081</v>
+        <v>277.463</v>
       </c>
       <c r="AA6" t="n">
         <v>3.884789522626573e-06</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>88.60767135371988</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 41.143x + -17995.618</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17995.61827354145</v>
       </c>
       <c r="Y7" t="n">
         <v>392.7280518508706</v>
       </c>
       <c r="Z7" t="n">
-        <v>3287.27072288689</v>
+        <v>251.1650000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>4.521316533480897e-06</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>88.72244516517623</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 44.841x + -19367.250</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-19367.25000866836</v>
       </c>
       <c r="Y8" t="n">
         <v>389.3162630114839</v>
       </c>
       <c r="Z8" t="n">
-        <v>3246.866204574776</v>
+        <v>229.595</v>
       </c>
       <c r="AA8" t="n">
         <v>4.448483453491044e-06</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>88.77241592232483</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 46.666x + -19817.192</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19817.1919479509</v>
       </c>
       <c r="Y9" t="n">
         <v>385.959650966054</v>
       </c>
       <c r="Z9" t="n">
-        <v>3207.657416673737</v>
+        <v>213.3079999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>5.600902006448315e-06</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>88.84041693729746</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 49.404x + -20694.792</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20694.79226048642</v>
       </c>
       <c r="Y10" t="n">
         <v>387.3450379457233</v>
       </c>
       <c r="Z10" t="n">
-        <v>6379.659292308062</v>
+        <v>198.412</v>
       </c>
       <c r="AA10" t="n">
         <v>1.122412543331055e-06</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>88.95390704849997</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 54.765x + -22756.507</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-22756.50704360376</v>
       </c>
       <c r="Y11" t="n">
         <v>383.2532454365163</v>
       </c>
       <c r="Z11" t="n">
-        <v>312966827.1727201</v>
+        <v>184.275</v>
       </c>
       <c r="AA11" t="n">
         <v>1.644941800157093e-07</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>87.76498880630163</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 25.623x + -12826.701</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12826.70080709606</v>
       </c>
       <c r="Y2" t="n">
         <v>445.5217413763704</v>
       </c>
       <c r="Z2" t="n">
-        <v>364301404.1346943</v>
+        <v>411.295</v>
       </c>
       <c r="AA2" t="n">
         <v>1.91923481557885e-07</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>88.19650747490451</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 31.759x + -15183.470</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15183.47037551354</v>
       </c>
       <c r="Y3" t="n">
         <v>427.9261418923682</v>
       </c>
       <c r="Z3" t="n">
-        <v>15303.38066629657</v>
+        <v>325.431</v>
       </c>
       <c r="AA3" t="n">
         <v>1.88800024798695e-07</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>88.49949242872881</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 38.176x + -17996.417</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-17996.41734846085</v>
       </c>
       <c r="Y4" t="n">
         <v>428.6542212651177</v>
       </c>
       <c r="Z4" t="n">
-        <v>116762374.6555094</v>
+        <v>269.539</v>
       </c>
       <c r="AA4" t="n">
         <v>1.765931770364124e-07</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>88.6738344489425</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 43.196x + -20102.819</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20102.8191344386</v>
       </c>
       <c r="Y5" t="n">
         <v>423.9464700506286</v>
       </c>
       <c r="Z5" t="n">
-        <v>173605973.5623363</v>
+        <v>233.819</v>
       </c>
       <c r="AA5" t="n">
         <v>1.728458101141928e-07</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>88.80615247011848</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 47.986x + -22072.289</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22072.28940661754</v>
       </c>
       <c r="Y6" t="n">
         <v>409.4762507523336</v>
       </c>
       <c r="Z6" t="n">
-        <v>6634.489808736175</v>
+        <v>208.241</v>
       </c>
       <c r="AA6" t="n">
         <v>4.474904544031344e-07</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>88.89680133452164</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 51.930x + -23590.427</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-23590.42694492583</v>
       </c>
       <c r="Y7" t="n">
         <v>414.7822903069173</v>
       </c>
       <c r="Z7" t="n">
-        <v>464361701.3064986</v>
+        <v>188.177</v>
       </c>
       <c r="AA7" t="n">
         <v>1.679803956322664e-07</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>88.96059567111276</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 55.118x + -24738.503</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-24738.50326950821</v>
       </c>
       <c r="Y8" t="n">
         <v>410.6263840299802</v>
       </c>
       <c r="Z8" t="n">
-        <v>224219218.8157094</v>
+        <v>171.5380000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.662751648033464e-07</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>88.97844311556345</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 56.081x + -24829.512</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-24829.51235185706</v>
       </c>
       <c r="Y9" t="n">
         <v>396.9008938885154</v>
       </c>
       <c r="Z9" t="n">
-        <v>3330.061449918616</v>
+        <v>159.1630000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>4.344437710028993e-06</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>89.04388766450577</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 59.920x + -26313.311</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-26313.31105928323</v>
       </c>
       <c r="Y10" t="n">
         <v>394.4043571083006</v>
       </c>
       <c r="Z10" t="n">
-        <v>3299.951747559794</v>
+        <v>148.453</v>
       </c>
       <c r="AA10" t="n">
         <v>3.67483432733058e-06</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>89.12237823926489</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 65.280x + -28470.458</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-28470.45822842</v>
       </c>
       <c r="Y11" t="n">
         <v>392.0388811811654</v>
       </c>
       <c r="Z11" t="n">
-        <v>3273.180475907599</v>
+        <v>140.0120000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>6.128354893777338e-06</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>89.14996582156013</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 67.399x + -29121.175</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-29121.17547699118</v>
       </c>
       <c r="Y12" t="n">
         <v>389.7561682247307</v>
       </c>
       <c r="Z12" t="n">
-        <v>3245.541536701804</v>
+        <v>130.943</v>
       </c>
       <c r="AA12" t="n">
         <v>5.700437883643665e-06</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>89.16134179986844</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 68.314x + -29230.219</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-29230.2190850054</v>
       </c>
       <c r="Y13" t="n">
         <v>387.4442877909653</v>
       </c>
       <c r="Z13" t="n">
-        <v>3218.404699776368</v>
+        <v>126.54</v>
       </c>
       <c r="AA13" t="n">
         <v>5.583406276037654e-06</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>89.20508838239715</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 72.074x + -30606.603</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-30606.60289461131</v>
       </c>
       <c r="Y14" t="n">
         <v>389.7406547608484</v>
       </c>
       <c r="Z14" t="n">
-        <v>6428.329509532081</v>
+        <v>118.631</v>
       </c>
       <c r="AA14" t="n">
         <v>1.404332381958741e-06</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>89.1878417462287</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 70.543x + -29635.204</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-29635.20413203444</v>
       </c>
       <c r="Y15" t="n">
         <v>387.2330232416897</v>
       </c>
       <c r="Z15" t="n">
-        <v>1685873676.812895</v>
+        <v>114.64</v>
       </c>
       <c r="AA15" t="n">
         <v>1.602149282356551e-07</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>89.18097761505307</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 69.952x + -29097.288</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-29097.28831433077</v>
       </c>
       <c r="Y16" t="n">
         <v>384.180802477226</v>
       </c>
       <c r="Z16" t="n">
-        <v>32699356.54622534</v>
+        <v>111.169</v>
       </c>
       <c r="AA16" t="n">
         <v>1.595471982436994e-07</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>89.20381774901686</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 71.959x + -29700.810</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-29700.81025677378</v>
       </c>
       <c r="Y17" t="n">
         <v>381.1678759208106</v>
       </c>
       <c r="Z17" t="n">
-        <v>156745896.91315</v>
+        <v>106.103</v>
       </c>
       <c r="AA17" t="n">
         <v>1.592581634940034e-07</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>89.24646638241214</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 76.032x + -31154.694</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-31154.69381519698</v>
       </c>
       <c r="Y18" t="n">
         <v>378.1684127705454</v>
       </c>
       <c r="Z18" t="n">
-        <v>824277120.1782154</v>
+        <v>101.91</v>
       </c>
       <c r="AA18" t="n">
         <v>1.589103556328105e-07</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>89.24863645460839</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 76.251x + -30964.859</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-30964.85902371214</v>
       </c>
       <c r="Y19" t="n">
         <v>375.2080221451005</v>
       </c>
       <c r="Z19" t="n">
-        <v>204741793.2675469</v>
+        <v>99.745</v>
       </c>
       <c r="AA19" t="n">
         <v>1.585612533663524e-07</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>89.20082965421912</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 71.689x + -28783.942</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-28783.94244058224</v>
       </c>
       <c r="Y20" t="n">
         <v>372.271572841044</v>
       </c>
       <c r="Z20" t="n">
-        <v>102338665.8058016</v>
+        <v>97.34300000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.581391330094839e-07</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>89.22789773890457</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 74.203x + -29563.860</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-29563.8603020616</v>
       </c>
       <c r="Y21" t="n">
         <v>369.2783700430094</v>
       </c>
       <c r="Z21" t="n">
-        <v>167282172.5652885</v>
+        <v>94.233</v>
       </c>
       <c r="AA21" t="n">
         <v>1.578380550462287e-07</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>89.24567236948779</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 75.952x + -30011.966</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-30011.96598531417</v>
       </c>
       <c r="Y22" t="n">
         <v>366.3474447787102</v>
       </c>
       <c r="Z22" t="n">
-        <v>199545158.8411019</v>
+        <v>90.32999999999998</v>
       </c>
       <c r="AA22" t="n">
         <v>1.574402716137631e-07</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>86.10449652226727</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.686x + -7984.235</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7984.234650369973</v>
       </c>
       <c r="Y2" t="n">
         <v>465.9385210326996</v>
       </c>
       <c r="Z2" t="n">
-        <v>125944830.0616441</v>
+        <v>698.2180000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.217924434706812e-07</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>87.07975860361393</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 19.603x + -9314.389</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9314.38895203223</v>
       </c>
       <c r="Y3" t="n">
         <v>429.6809189207714</v>
       </c>
       <c r="Z3" t="n">
-        <v>235133123.0002992</v>
+        <v>536.298</v>
       </c>
       <c r="AA3" t="n">
         <v>2.027784351602589e-07</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>87.63522719125206</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 24.215x + -11088.536</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11088.53596514757</v>
       </c>
       <c r="Y4" t="n">
         <v>419.1457457201915</v>
       </c>
       <c r="Z4" t="n">
-        <v>114473230.6109785</v>
+        <v>432.936</v>
       </c>
       <c r="AA4" t="n">
         <v>1.912782323924476e-07</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>88.04764426360474</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.336x + -13231.085</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13231.08512810853</v>
       </c>
       <c r="Y5" t="n">
         <v>412.8967978783018</v>
       </c>
       <c r="Z5" t="n">
-        <v>119797743.5511172</v>
+        <v>358.3320000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.835494335189894e-07</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>88.35315008012894</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 34.782x + -15489.980</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15489.98017282409</v>
       </c>
       <c r="Y6" t="n">
         <v>395.9831167167076</v>
       </c>
       <c r="Z6" t="n">
-        <v>3336.055198839147</v>
+        <v>303.413</v>
       </c>
       <c r="AA6" t="n">
         <v>3.05322933536866e-06</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>88.52520479587945</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 38.841x + -17009.142</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17009.14249155791</v>
       </c>
       <c r="Y7" t="n">
         <v>392.2258068671704</v>
       </c>
       <c r="Z7" t="n">
-        <v>3287.626786119543</v>
+        <v>266.626</v>
       </c>
       <c r="AA7" t="n">
         <v>4.265270617677732e-06</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>88.65921782205136</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 42.725x + -18422.555</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-18422.55495118479</v>
       </c>
       <c r="Y8" t="n">
         <v>388.5763487116285</v>
       </c>
       <c r="Z8" t="n">
-        <v>3241.865783801222</v>
+        <v>237.98</v>
       </c>
       <c r="AA8" t="n">
         <v>6.159831949522686e-06</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>88.72436859326332</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 44.908x + -19002.983</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19002.98295864273</v>
       </c>
       <c r="Y9" t="n">
         <v>385.0824326971173</v>
       </c>
       <c r="Z9" t="n">
-        <v>3198.838064944804</v>
+        <v>216.23</v>
       </c>
       <c r="AA9" t="n">
         <v>5.578920216903476e-06</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>88.85729932848511</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 50.134x + -21035.600</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21035.60011296409</v>
       </c>
       <c r="Y10" t="n">
         <v>386.4806172968474</v>
       </c>
       <c r="Z10" t="n">
-        <v>6365.913405262596</v>
+        <v>198.86</v>
       </c>
       <c r="AA10" t="n">
         <v>1.397234723466366e-06</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>88.89963523684352</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 52.063x + -21517.563</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-21517.56347801927</v>
       </c>
       <c r="Y11" t="n">
         <v>382.3158348878899</v>
       </c>
       <c r="Z11" t="n">
-        <v>416139392.9200711</v>
+        <v>185.408</v>
       </c>
       <c r="AA11" t="n">
         <v>1.654709682333789e-07</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>87.18653222989532</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 20.348x + -10250.959</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10250.95867513279</v>
       </c>
       <c r="Y2" t="n">
         <v>447.743774507379</v>
       </c>
       <c r="Z2" t="n">
-        <v>30778583.24879043</v>
+        <v>509.7910000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.052089358659983e-07</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>88.10521808608657</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 30.228x + -14561.042</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14561.04227016276</v>
       </c>
       <c r="Y3" t="n">
         <v>435.21944108829</v>
       </c>
       <c r="Z3" t="n">
-        <v>475366282.7591516</v>
+        <v>342.783</v>
       </c>
       <c r="AA3" t="n">
         <v>1.86397735280607e-07</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>88.42475046954964</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 36.363x + -17150.115</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-17150.11455124067</v>
       </c>
       <c r="Y4" t="n">
         <v>412.6806406451644</v>
       </c>
       <c r="Z4" t="n">
-        <v>3522.630093569946</v>
+        <v>273.986</v>
       </c>
       <c r="AA4" t="n">
         <v>2.578283406252619e-06</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>88.64437714473877</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 42.257x + -19714.397</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-19714.39747457574</v>
       </c>
       <c r="Y5" t="n">
         <v>425.0270033480434</v>
       </c>
       <c r="Z5" t="n">
-        <v>231840496.8403437</v>
+        <v>231.005</v>
       </c>
       <c r="AA5" t="n">
         <v>1.740383282684285e-07</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>88.82450896285805</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 48.735x + -22545.273</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22545.27319824054</v>
       </c>
       <c r="Y6" t="n">
         <v>422.7110849134795</v>
       </c>
       <c r="Z6" t="n">
-        <v>10926.48629287233</v>
+        <v>201.1249999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>2.44331616981372e-07</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>88.85921148358472</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 50.218x + -22886.242</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-22886.24164235841</v>
       </c>
       <c r="Y7" t="n">
         <v>416.3709010465464</v>
       </c>
       <c r="Z7" t="n">
-        <v>227030833.2324212</v>
+        <v>184.603</v>
       </c>
       <c r="AA7" t="n">
         <v>1.689034763179671e-07</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>88.91292527282339</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 52.700x + -23744.987</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23744.98673057721</v>
       </c>
       <c r="Y8" t="n">
         <v>413.121377527487</v>
       </c>
       <c r="Z8" t="n">
-        <v>6683.192422803645</v>
+        <v>171.938</v>
       </c>
       <c r="AA8" t="n">
         <v>1.106353207470936e-06</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>88.9661537017887</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 55.414x + -24730.506</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-24730.50644335342</v>
       </c>
       <c r="Y9" t="n">
         <v>409.2460785515499</v>
       </c>
       <c r="Z9" t="n">
-        <v>5466.576901333721</v>
+        <v>159.488</v>
       </c>
       <c r="AA9" t="n">
         <v>7.727846956299995e-07</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>89.06871706157064</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 61.518x + -27316.270</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-27316.27022963938</v>
       </c>
       <c r="Y10" t="n">
         <v>395.8910871285624</v>
       </c>
       <c r="Z10" t="n">
-        <v>3320.625198204999</v>
+        <v>148.47</v>
       </c>
       <c r="AA10" t="n">
         <v>4.574161057298543e-06</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>89.00823369920913</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 57.766x + -25295.647</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-25295.6471690317</v>
       </c>
       <c r="Y11" t="n">
         <v>393.8316717896972</v>
       </c>
       <c r="Z11" t="n">
-        <v>3293.769767612086</v>
+        <v>145.249</v>
       </c>
       <c r="AA11" t="n">
         <v>3.578325690877909e-06</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>89.05655104008662</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 60.725x + -26418.907</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-26418.90728981206</v>
       </c>
       <c r="Y12" t="n">
         <v>391.8424530579769</v>
       </c>
       <c r="Z12" t="n">
-        <v>3270.317355555084</v>
+        <v>139.0890000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>6.066630005625109e-06</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>89.1296181681449</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 65.823x + -28499.843</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-28499.84257358155</v>
       </c>
       <c r="Y13" t="n">
         <v>389.8289478579588</v>
       </c>
       <c r="Z13" t="n">
-        <v>3246.622202714017</v>
+        <v>131.6079999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>5.708662111489181e-06</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>89.13147266081205</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 65.964x + -28311.090</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-28311.08958908441</v>
       </c>
       <c r="Y14" t="n">
         <v>387.8941981626574</v>
       </c>
       <c r="Z14" t="n">
-        <v>3225.342151708438</v>
+        <v>128.303</v>
       </c>
       <c r="AA14" t="n">
         <v>5.619389206315173e-06</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>89.15968101814754</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 68.178x + -29049.599</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-29049.59931635962</v>
       </c>
       <c r="Y15" t="n">
         <v>391.1532336160193</v>
       </c>
       <c r="Z15" t="n">
-        <v>6451.145522897522</v>
+        <v>122.366</v>
       </c>
       <c r="AA15" t="n">
         <v>1.050197949507803e-06</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>89.11445303669798</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 64.696x + -27259.194</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-27259.19356633699</v>
       </c>
       <c r="Y16" t="n">
         <v>388.8264473583125</v>
       </c>
       <c r="Z16" t="n">
-        <v>159832079.2250715</v>
+        <v>120.816</v>
       </c>
       <c r="AA16" t="n">
         <v>1.615536210353232e-07</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>89.16896176629569</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 68.940x + -28880.545</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-28880.54549330903</v>
       </c>
       <c r="Y17" t="n">
         <v>386.034710055192</v>
       </c>
       <c r="Z17" t="n">
-        <v>420412153.1588411</v>
+        <v>116.407</v>
       </c>
       <c r="AA17" t="n">
         <v>1.611705287351e-07</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>89.16317318030586</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 68.463x + -28425.147</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-28425.14716559185</v>
       </c>
       <c r="Y18" t="n">
         <v>383.2136317446345</v>
       </c>
       <c r="Z18" t="n">
-        <v>313980803.5212577</v>
+        <v>113.7910000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.607471483106774e-07</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>89.19079324006958</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 70.800x + -29184.068</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-29184.06750991363</v>
       </c>
       <c r="Y19" t="n">
         <v>380.3232093163263</v>
       </c>
       <c r="Z19" t="n">
-        <v>310644615.4314929</v>
+        <v>110.864</v>
       </c>
       <c r="AA19" t="n">
         <v>1.604137434342052e-07</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>89.19279528563034</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 70.976x + -28988.997</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-28988.99657579932</v>
       </c>
       <c r="Y20" t="n">
         <v>377.3952586420104</v>
       </c>
       <c r="Z20" t="n">
-        <v>206279049.5861789</v>
+        <v>107.718</v>
       </c>
       <c r="AA20" t="n">
         <v>1.60055151696587e-07</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>89.25410106462239</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 76.810x + -31198.966</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-31198.96571073774</v>
       </c>
       <c r="Y21" t="n">
         <v>374.4372449724538</v>
       </c>
       <c r="Z21" t="n">
-        <v>319226464.8156897</v>
+        <v>104.699</v>
       </c>
       <c r="AA21" t="n">
         <v>1.598147789401788e-07</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>89.21795392947773</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 73.259x + -29436.657</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-29436.65716876552</v>
       </c>
       <c r="Y22" t="n">
         <v>371.479829090248</v>
       </c>
       <c r="Z22" t="n">
-        <v>606907419.4105353</v>
+        <v>103.25</v>
       </c>
       <c r="AA22" t="n">
         <v>1.595275182660601e-07</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.69387133424055</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.767x + -5387.806</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5387.805928715256</v>
       </c>
       <c r="Y2" t="n">
         <v>439.5821624890179</v>
       </c>
       <c r="Z2" t="n">
-        <v>179437612.1642645</v>
+        <v>916.8920000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.656262698550957e-07</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>86.45393516384725</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.137x + -7388.070</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7388.069706441625</v>
       </c>
       <c r="Y3" t="n">
         <v>400.8704822541768</v>
       </c>
       <c r="Z3" t="n">
-        <v>3419.239551428888</v>
+        <v>624.9380000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>2.532936774713646e-06</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>87.41118647874454</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 22.117x + -9881.900</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9881.900400862911</v>
       </c>
       <c r="Y4" t="n">
         <v>409.407617747873</v>
       </c>
       <c r="Z4" t="n">
-        <v>181930353.206481</v>
+        <v>458.975</v>
       </c>
       <c r="AA4" t="n">
         <v>2.018214439935201e-07</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>87.94948734474607</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 27.930x + -12292.182</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12292.18184384115</v>
       </c>
       <c r="Y5" t="n">
         <v>392.2942363708429</v>
       </c>
       <c r="Z5" t="n">
-        <v>3311.443666203407</v>
+        <v>360.698</v>
       </c>
       <c r="AA5" t="n">
         <v>3.426062328510996e-06</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>88.31136112682967</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 33.920x + -14767.628</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14767.62845276563</v>
       </c>
       <c r="Y6" t="n">
         <v>389.1104300571027</v>
       </c>
       <c r="Z6" t="n">
-        <v>3266.097246308253</v>
+        <v>295.8559999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>3.625341197155095e-06</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>88.52341347472644</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 38.794x + -16633.027</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16633.02655156043</v>
       </c>
       <c r="Y7" t="n">
         <v>385.7990518375054</v>
       </c>
       <c r="Z7" t="n">
-        <v>3219.360410303704</v>
+        <v>252.701</v>
       </c>
       <c r="AA7" t="n">
         <v>5.694982343220032e-06</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>88.64962108815162</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 42.422x + -17889.926</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17889.92606714007</v>
       </c>
       <c r="Y8" t="n">
         <v>387.7873766025926</v>
       </c>
       <c r="Z8" t="n">
-        <v>6402.446348565064</v>
+        <v>224.205</v>
       </c>
       <c r="AA8" t="n">
         <v>9.583818891856134e-07</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>88.7830010822081</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 47.072x + -19597.341</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19597.34089013432</v>
       </c>
       <c r="Y9" t="n">
         <v>383.7743960295181</v>
       </c>
       <c r="Z9" t="n">
-        <v>313346146.0761515</v>
+        <v>199.7330000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.723040403138065e-07</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>88.82390532328188</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 48.710x + -19947.208</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19947.20813040185</v>
       </c>
       <c r="Y10" t="n">
         <v>379.1208119834776</v>
       </c>
       <c r="Z10" t="n">
-        <v>206565007.5045739</v>
+        <v>184.455</v>
       </c>
       <c r="AA10" t="n">
         <v>1.704464585334878e-07</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>88.92454085184558</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 53.269x + -21601.165</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-21601.1652768092</v>
       </c>
       <c r="Y11" t="n">
         <v>374.8848460024854</v>
       </c>
       <c r="Z11" t="n">
-        <v>229459817.9932854</v>
+        <v>168.986</v>
       </c>
       <c r="AA11" t="n">
         <v>1.689847293904402e-07</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>87.82290876471947</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 26.305x + -13183.646</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-13183.64591278973</v>
       </c>
       <c r="Y2" t="n">
         <v>445.2107445227359</v>
       </c>
       <c r="Z2" t="n">
-        <v>484757949.2143062</v>
+        <v>371.904</v>
       </c>
       <c r="AA2" t="n">
         <v>1.985003324268114e-07</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>88.4011402363483</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 35.826x + -17219.712</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-17219.7122207606</v>
       </c>
       <c r="Y3" t="n">
         <v>414.0888565555738</v>
       </c>
       <c r="Z3" t="n">
-        <v>3551.88036038065</v>
+        <v>270.399</v>
       </c>
       <c r="AA3" t="n">
         <v>2.824848398905355e-06</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>88.65591714947475</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 42.620x + -20167.683</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20167.68347234795</v>
       </c>
       <c r="Y4" t="n">
         <v>427.8187709455693</v>
       </c>
       <c r="Z4" t="n">
-        <v>240267045.2171544</v>
+        <v>223.461</v>
       </c>
       <c r="AA4" t="n">
         <v>1.799402542672796e-07</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>88.7299404691602</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 45.105x + -20992.341</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20992.34145579227</v>
       </c>
       <c r="Y5" t="n">
         <v>423.4845522674789</v>
       </c>
       <c r="Z5" t="n">
-        <v>230711883.3746552</v>
+        <v>196.9239999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.764613456250841e-07</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>88.80509088880189</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 47.943x + -22050.598</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22050.59842642148</v>
       </c>
       <c r="Y6" t="n">
         <v>419.3363685423765</v>
       </c>
       <c r="Z6" t="n">
-        <v>114431946.7009747</v>
+        <v>180.642</v>
       </c>
       <c r="AA6" t="n">
         <v>1.742469253335535e-07</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>88.85215892479286</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 49.909x + -22692.498</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-22692.49838129308</v>
       </c>
       <c r="Y7" t="n">
         <v>415.069877870661</v>
       </c>
       <c r="Z7" t="n">
-        <v>6699.275184442167</v>
+        <v>167.714</v>
       </c>
       <c r="AA7" t="n">
         <v>8.432145177788463e-07</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>88.8574131229344</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 50.139x + -22513.854</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-22513.85403880199</v>
       </c>
       <c r="Y8" t="n">
         <v>411.7900922825735</v>
       </c>
       <c r="Z8" t="n">
-        <v>6788.468379783648</v>
+        <v>158.921</v>
       </c>
       <c r="AA8" t="n">
         <v>6.638363161511533e-07</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>88.99057701950217</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 56.755x + -25371.295</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25371.29466502148</v>
       </c>
       <c r="Y9" t="n">
         <v>397.3939176713774</v>
       </c>
       <c r="Z9" t="n">
-        <v>3339.040714941274</v>
+        <v>147.3020000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>4.251818003045368e-06</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>88.99394217515265</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 56.945x + -25198.542</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-25198.54161031957</v>
       </c>
       <c r="Y10" t="n">
         <v>394.9405005528467</v>
       </c>
       <c r="Z10" t="n">
-        <v>3312.978033132198</v>
+        <v>142.7090000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>3.572980120354203e-06</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>88.99417310334179</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 56.958x + -24938.719</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-24938.71876990232</v>
       </c>
       <c r="Y11" t="n">
         <v>392.6520746059164</v>
       </c>
       <c r="Z11" t="n">
-        <v>3285.306692972217</v>
+        <v>138.268</v>
       </c>
       <c r="AA11" t="n">
         <v>4.877486350574464e-06</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>89.0113552010319</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 57.948x + -25150.243</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-25150.24252877807</v>
       </c>
       <c r="Y12" t="n">
         <v>390.4070269839705</v>
       </c>
       <c r="Z12" t="n">
-        <v>3257.477024161224</v>
+        <v>134.1199999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>5.730720833761005e-06</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>89.06915122590496</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 61.547x + -26531.690</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-26531.69042211393</v>
       </c>
       <c r="Y13" t="n">
         <v>388.1213415078581</v>
       </c>
       <c r="Z13" t="n">
-        <v>3232.569053716101</v>
+        <v>128.152</v>
       </c>
       <c r="AA13" t="n">
         <v>5.629135381785853e-06</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>89.03403213158484</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 59.309x + -25280.494</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-25280.49402069625</v>
       </c>
       <c r="Y14" t="n">
         <v>390.583764969574</v>
       </c>
       <c r="Z14" t="n">
-        <v>6458.350086340269</v>
+        <v>123.9520000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.23462095952067e-06</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>89.04748147753429</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 60.146x + -25419.839</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-25419.83934485272</v>
       </c>
       <c r="Y15" t="n">
         <v>389.2140831090402</v>
       </c>
       <c r="Z15" t="n">
-        <v>212123666.6558876</v>
+        <v>122.354</v>
       </c>
       <c r="AA15" t="n">
         <v>1.667756367745261e-07</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>89.09557239948225</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 63.345x + -26595.582</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-26595.58197902434</v>
       </c>
       <c r="Y16" t="n">
         <v>386.1619194211478</v>
       </c>
       <c r="Z16" t="n">
-        <v>630147973.6149029</v>
+        <v>119.337</v>
       </c>
       <c r="AA16" t="n">
         <v>1.664281427213033e-07</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>89.1260787236988</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 65.557x + -27301.216</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-27301.21563522803</v>
       </c>
       <c r="Y17" t="n">
         <v>383.1139822365346</v>
       </c>
       <c r="Z17" t="n">
-        <v>235037887.056922</v>
+        <v>110.985</v>
       </c>
       <c r="AA17" t="n">
         <v>1.658346229963305e-07</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>89.11289757595712</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 64.582x + -26639.038</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-26639.03816144041</v>
       </c>
       <c r="Y18" t="n">
         <v>380.0618972010561</v>
       </c>
       <c r="Z18" t="n">
-        <v>1033766805.194658</v>
+        <v>113.409</v>
       </c>
       <c r="AA18" t="n">
         <v>1.656828516500103e-07</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>89.14182050853864</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 66.759x + -27314.911</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-27314.91109448129</v>
       </c>
       <c r="Y19" t="n">
         <v>376.961918160021</v>
       </c>
       <c r="Z19" t="n">
-        <v>309418650.2319997</v>
+        <v>110.349</v>
       </c>
       <c r="AA19" t="n">
         <v>1.653061657371997e-07</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>89.13020675648549</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 65.868x + -26689.192</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-26689.19248452581</v>
       </c>
       <c r="Y20" t="n">
         <v>373.938434749889</v>
       </c>
       <c r="Z20" t="n">
-        <v>205348113.3277394</v>
+        <v>108.847</v>
       </c>
       <c r="AA20" t="n">
         <v>1.649336675343289e-07</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>89.09339115417504</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 63.193x + -25320.881</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-25320.88127509539</v>
       </c>
       <c r="Y21" t="n">
         <v>370.903070994451</v>
       </c>
       <c r="Z21" t="n">
-        <v>38637295.74779098</v>
+        <v>109.006</v>
       </c>
       <c r="AA21" t="n">
         <v>1.645484748636624e-07</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>89.16389312927488</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 68.522x + -27301.233</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-27301.23258940838</v>
       </c>
       <c r="Y22" t="n">
         <v>367.7975938516235</v>
       </c>
       <c r="Z22" t="n">
-        <v>800821460.7859757</v>
+        <v>106.333</v>
       </c>
       <c r="AA22" t="n">
         <v>1.645206086526355e-07</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>85.59107526851361</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.970x + -6441.186</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6441.185630714731</v>
       </c>
       <c r="Y2" t="n">
         <v>431.8804385697641</v>
       </c>
       <c r="Z2" t="n">
-        <v>236325911.4878342</v>
+        <v>754.7139999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>2.421535611000204e-07</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>87.13674553142994</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 19.994x + -8801.431</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8801.431445806935</v>
       </c>
       <c r="Y3" t="n">
         <v>388.8880946342742</v>
       </c>
       <c r="Z3" t="n">
-        <v>3286.19399190833</v>
+        <v>497.308</v>
       </c>
       <c r="AA3" t="n">
         <v>1.320028754645425e-06</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>87.91102970620548</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 27.416x + -11727.899</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11727.89934096327</v>
       </c>
       <c r="Y4" t="n">
         <v>383.6039142069445</v>
       </c>
       <c r="Z4" t="n">
-        <v>3210.996368504371</v>
+        <v>361.8100000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>4.203063429814494e-06</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>88.32852274969719</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 34.269x + -14433.980</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14433.98027306289</v>
       </c>
       <c r="Y5" t="n">
         <v>386.2083336826761</v>
       </c>
       <c r="Z5" t="n">
-        <v>6380.724393138067</v>
+        <v>284.087</v>
       </c>
       <c r="AA5" t="n">
         <v>8.038272625164862e-07</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>88.51560631152049</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 38.590x + -15955.651</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15955.65087096711</v>
       </c>
       <c r="Y6" t="n">
         <v>382.4736754823203</v>
       </c>
       <c r="Z6" t="n">
-        <v>209185431.4402277</v>
+        <v>238.5700000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.794745490306424e-07</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>88.65957793641439</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 42.737x + -17405.514</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17405.51411385684</v>
       </c>
       <c r="Y7" t="n">
         <v>377.2917233827275</v>
       </c>
       <c r="Z7" t="n">
-        <v>307775388.5564924</v>
+        <v>206.832</v>
       </c>
       <c r="AA7" t="n">
         <v>1.761317038744865e-07</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>88.78294966683336</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 47.070x + -18921.753</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-18921.75319589645</v>
       </c>
       <c r="Y8" t="n">
         <v>372.3037068619515</v>
       </c>
       <c r="Z8" t="n">
-        <v>304006294.589339</v>
+        <v>184.732</v>
       </c>
       <c r="AA8" t="n">
         <v>1.73812905593134e-07</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>88.87275466523322</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 50.822x + -20167.596</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20167.59559117172</v>
       </c>
       <c r="Y9" t="n">
         <v>367.5314693890718</v>
       </c>
       <c r="Z9" t="n">
-        <v>38393525.61343922</v>
+        <v>169.393</v>
       </c>
       <c r="AA9" t="n">
         <v>1.720479364240339e-07</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>88.93311863277523</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 53.698x + -21028.191</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21028.19098596118</v>
       </c>
       <c r="Y10" t="n">
         <v>363.1266844353947</v>
       </c>
       <c r="Z10" t="n">
-        <v>148258672.0502665</v>
+        <v>156.482</v>
       </c>
       <c r="AA10" t="n">
         <v>1.709239146154232e-07</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>88.9737992355857</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 55.827x + -21600.451</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-21600.45072945064</v>
       </c>
       <c r="Y11" t="n">
         <v>351.5106155674105</v>
       </c>
       <c r="Z11" t="n">
-        <v>5898.008891584643</v>
+        <v>147.681</v>
       </c>
       <c r="AA11" t="n">
         <v>1.235512271654899e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>86.56603481257713</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.665x + -8204.892</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.66503770425023</v>
       </c>
       <c r="X2" t="n">
         <v>-8204.891919915419</v>
@@ -600,7 +598,7 @@
         <v>445.0244163987439</v>
       </c>
       <c r="Z2" t="n">
-        <v>608.6600000000001</v>
+        <v>486964752.1258806</v>
       </c>
       <c r="AA2" t="n">
         <v>2.228960720397941e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>87.30161957723325</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 21.218x + -10274.914</t>
-        </is>
+      <c r="W3" t="n">
+        <v>21.21769492893483</v>
       </c>
       <c r="X3" t="n">
         <v>-10274.91400160013</v>
@@ -652,7 +648,7 @@
         <v>438.7994999563107</v>
       </c>
       <c r="Z3" t="n">
-        <v>487.385</v>
+        <v>239988503.5616964</v>
       </c>
       <c r="AA3" t="n">
         <v>2.03784965291014e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.68508427257339</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 24.737x + -11761.524</t>
-        </is>
+      <c r="W4" t="n">
+        <v>24.73722866194396</v>
       </c>
       <c r="X4" t="n">
         <v>-11761.52385783254</v>
@@ -704,7 +698,7 @@
         <v>432.8256052678489</v>
       </c>
       <c r="Z4" t="n">
-        <v>416.6139999999999</v>
+        <v>1063254965.513357</v>
       </c>
       <c r="AA4" t="n">
         <v>1.938977506697763e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>88.03375180799974</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.128x + -13739.046</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.12820758641326</v>
       </c>
       <c r="X5" t="n">
         <v>-13739.04637824691</v>
@@ -756,7 +748,7 @@
         <v>411.3187824562365</v>
       </c>
       <c r="Z5" t="n">
-        <v>361.974</v>
+        <v>3501.376424990312</v>
       </c>
       <c r="AA5" t="n">
         <v>2.630400549407319e-06</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>88.22545674805478</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 32.277x + -14992.525</t>
-        </is>
+      <c r="W6" t="n">
+        <v>32.27729620983263</v>
       </c>
       <c r="X6" t="n">
         <v>-14992.52478000839</v>
@@ -808,7 +798,7 @@
         <v>421.866699372222</v>
       </c>
       <c r="Z6" t="n">
-        <v>325.338</v>
+        <v>115146782.9545396</v>
       </c>
       <c r="AA6" t="n">
         <v>1.824509949546205e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>88.3652592097021</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 35.039x + -16004.119</t>
-        </is>
+      <c r="W7" t="n">
+        <v>35.03933574510697</v>
       </c>
       <c r="X7" t="n">
         <v>-16004.11879585791</v>
@@ -860,7 +848,7 @@
         <v>413.3690171197563</v>
       </c>
       <c r="Z7" t="n">
-        <v>294.284</v>
+        <v>6447.618479083058</v>
       </c>
       <c r="AA7" t="n">
         <v>4.370851338602851e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>88.48841713881001</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 37.896x + -17093.425</t>
-        </is>
+      <c r="W8" t="n">
+        <v>37.89569692670363</v>
       </c>
       <c r="X8" t="n">
         <v>-17093.42473464095</v>
@@ -912,7 +898,7 @@
         <v>412.9992153348903</v>
       </c>
       <c r="Z8" t="n">
-        <v>269.049</v>
+        <v>450261770.4522188</v>
       </c>
       <c r="AA8" t="n">
         <v>1.756077495807179e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>88.5885531646659</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 40.585x + -18100.591</t>
-        </is>
+      <c r="W9" t="n">
+        <v>40.58543868891009</v>
       </c>
       <c r="X9" t="n">
         <v>-18100.59079228311</v>
@@ -964,7 +948,7 @@
         <v>397.4850624089426</v>
       </c>
       <c r="Z9" t="n">
-        <v>248.641</v>
+        <v>3348.871187404912</v>
       </c>
       <c r="AA9" t="n">
         <v>3.088510335412902e-06</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>88.73948548702943</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 45.447x + -20143.103</t>
-        </is>
+      <c r="W10" t="n">
+        <v>45.44694630504332</v>
       </c>
       <c r="X10" t="n">
         <v>-20143.10255451971</v>
@@ -1016,7 +998,7 @@
         <v>406.4658718266165</v>
       </c>
       <c r="Z10" t="n">
-        <v>225.139</v>
+        <v>5421.831715459281</v>
       </c>
       <c r="AA10" t="n">
         <v>7.027691994699986e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>88.77140104859826</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 46.628x + -20407.899</t>
-        </is>
+      <c r="W11" t="n">
+        <v>46.62790695293129</v>
       </c>
       <c r="X11" t="n">
         <v>-20407.89935235872</v>
@@ -1068,7 +1048,7 @@
         <v>392.7309796848951</v>
       </c>
       <c r="Z11" t="n">
-        <v>212.641</v>
+        <v>3292.823352096475</v>
       </c>
       <c r="AA11" t="n">
         <v>4.521469716471364e-06</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>88.2343794523108</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 32.441x + -16105.915</t>
-        </is>
+      <c r="W2" t="n">
+        <v>32.44051619648437</v>
       </c>
       <c r="X2" t="n">
         <v>-16105.91496641924</v>
@@ -1266,7 +1244,7 @@
         <v>419.2326892825938</v>
       </c>
       <c r="Z2" t="n">
-        <v>286.5500000000001</v>
+        <v>7283.020815301395</v>
       </c>
       <c r="AA2" t="n">
         <v>7.208497343607827e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>88.51704152719303</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 38.628x + -18438.480</t>
-        </is>
+      <c r="W3" t="n">
+        <v>38.62750425171154</v>
       </c>
       <c r="X3" t="n">
         <v>-18438.47981940698</v>
@@ -1318,7 +1294,7 @@
         <v>415.8312423507439</v>
       </c>
       <c r="Z3" t="n">
-        <v>229.497</v>
+        <v>3537.425526003954</v>
       </c>
       <c r="AA3" t="n">
         <v>1.058952545786878e-06</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>88.63173771670471</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 41.867x + -19638.793</t>
-        </is>
+      <c r="W4" t="n">
+        <v>41.86689066823836</v>
       </c>
       <c r="X4" t="n">
         <v>-19638.79252253433</v>
@@ -1370,7 +1344,7 @@
         <v>426.9358447869628</v>
       </c>
       <c r="Z4" t="n">
-        <v>200.145</v>
+        <v>174689281.998233</v>
       </c>
       <c r="AA4" t="n">
         <v>1.81308952672996e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>88.75344427271543</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 45.956x + -21341.593</t>
-        </is>
+      <c r="W5" t="n">
+        <v>45.95601924830282</v>
       </c>
       <c r="X5" t="n">
         <v>-21341.5930482217</v>
@@ -1422,7 +1394,7 @@
         <v>407.5001834965634</v>
       </c>
       <c r="Z5" t="n">
-        <v>180.649</v>
+        <v>3459.085167738524</v>
       </c>
       <c r="AA5" t="n">
         <v>1.970744449809594e-06</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>88.82438455887657</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 48.730x + -22379.847</t>
-        </is>
+      <c r="W6" t="n">
+        <v>48.72999853220286</v>
       </c>
       <c r="X6" t="n">
         <v>-22379.84733407621</v>
@@ -1474,7 +1444,7 @@
         <v>416.2955460959788</v>
       </c>
       <c r="Z6" t="n">
-        <v>168.091</v>
+        <v>5373.300659411513</v>
       </c>
       <c r="AA6" t="n">
         <v>8.886465498890387e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>88.81374997364514</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 48.293x + -21849.680</t>
-        </is>
+      <c r="W7" t="n">
+        <v>48.29301691202554</v>
       </c>
       <c r="X7" t="n">
         <v>-21849.67980895728</v>
@@ -1526,7 +1494,7 @@
         <v>413.4572111420966</v>
       </c>
       <c r="Z7" t="n">
-        <v>158.6559999999999</v>
+        <v>6825.418772768077</v>
       </c>
       <c r="AA7" t="n">
         <v>6.361469973584559e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>88.91345318528198</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 52.726x + -23681.335</t>
-        </is>
+      <c r="W8" t="n">
+        <v>52.72567202186245</v>
       </c>
       <c r="X8" t="n">
         <v>-23681.33456379035</v>
@@ -1578,7 +1544,7 @@
         <v>398.6739443155888</v>
       </c>
       <c r="Z8" t="n">
-        <v>150.795</v>
+        <v>3354.608012709333</v>
       </c>
       <c r="AA8" t="n">
         <v>4.236408422876814e-06</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>88.92842992015298</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 53.463x + -23736.442</t>
-        </is>
+      <c r="W9" t="n">
+        <v>53.4627646988959</v>
       </c>
       <c r="X9" t="n">
         <v>-23736.44190164505</v>
@@ -1630,7 +1594,7 @@
         <v>396.0362382921331</v>
       </c>
       <c r="Z9" t="n">
-        <v>142.993</v>
+        <v>3322.582231403105</v>
       </c>
       <c r="AA9" t="n">
         <v>4.439434287426658e-06</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>88.9251467226117</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 53.299x + -23408.920</t>
-        </is>
+      <c r="W10" t="n">
+        <v>53.29942164382769</v>
       </c>
       <c r="X10" t="n">
         <v>-23408.91966239561</v>
@@ -1682,7 +1644,7 @@
         <v>393.4370342247838</v>
       </c>
       <c r="Z10" t="n">
-        <v>140.446</v>
+        <v>3294.122405107289</v>
       </c>
       <c r="AA10" t="n">
         <v>3.849900843905989e-06</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>88.95413911794064</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 54.777x + -23837.615</t>
-        </is>
+      <c r="W11" t="n">
+        <v>54.77728131786293</v>
       </c>
       <c r="X11" t="n">
         <v>-23837.61526272434</v>
@@ -1734,7 +1694,7 @@
         <v>391.0632391930403</v>
       </c>
       <c r="Z11" t="n">
-        <v>135.631</v>
+        <v>3264.069938753463</v>
       </c>
       <c r="AA11" t="n">
         <v>5.724265934223685e-06</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>88.97330415228687</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 55.800x + -24053.498</t>
-        </is>
+      <c r="W12" t="n">
+        <v>55.80001806650652</v>
       </c>
       <c r="X12" t="n">
         <v>-24053.49785526302</v>
@@ -1786,7 +1744,7 @@
         <v>394.0977679144297</v>
       </c>
       <c r="Z12" t="n">
-        <v>131.0170000000001</v>
+        <v>6519.887508174598</v>
       </c>
       <c r="AA12" t="n">
         <v>9.549030011595242e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>89.05634127267498</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 60.711x + -26034.306</t>
-        </is>
+      <c r="W13" t="n">
+        <v>60.71114173928162</v>
       </c>
       <c r="X13" t="n">
         <v>-26034.30608589084</v>
@@ -1838,7 +1794,7 @@
         <v>392.8430672948829</v>
       </c>
       <c r="Z13" t="n">
-        <v>126.0149999999999</v>
+        <v>855128219.2084062</v>
       </c>
       <c r="AA13" t="n">
         <v>1.712016493363925e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>88.98416076772514</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 56.396x + -23863.414</t>
-        </is>
+      <c r="W14" t="n">
+        <v>56.39649862448768</v>
       </c>
       <c r="X14" t="n">
         <v>-23863.41449898794</v>
@@ -1890,7 +1844,7 @@
         <v>389.695358208202</v>
       </c>
       <c r="Z14" t="n">
-        <v>125.866</v>
+        <v>321334355.8278245</v>
       </c>
       <c r="AA14" t="n">
         <v>1.708134112227292e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>89.03575403470118</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 59.415x + -24961.219</t>
-        </is>
+      <c r="W15" t="n">
+        <v>59.41468493358725</v>
       </c>
       <c r="X15" t="n">
         <v>-24961.21932336222</v>
@@ -1942,7 +1894,7 @@
         <v>386.6341236401993</v>
       </c>
       <c r="Z15" t="n">
-        <v>121.0189999999999</v>
+        <v>105628032.5617058</v>
       </c>
       <c r="AA15" t="n">
         <v>1.702302874103545e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>89.00221894496224</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 57.417x + -23863.700</t>
-        </is>
+      <c r="W16" t="n">
+        <v>57.4173934577143</v>
       </c>
       <c r="X16" t="n">
         <v>-23863.70018466999</v>
@@ -1994,7 +1944,7 @@
         <v>383.5601705167197</v>
       </c>
       <c r="Z16" t="n">
-        <v>120.169</v>
+        <v>209024500.0176502</v>
       </c>
       <c r="AA16" t="n">
         <v>1.698854366435733e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>89.03097801498369</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 59.122x + -24377.925</t>
-        </is>
+      <c r="W17" t="n">
+        <v>59.12179227429597</v>
       </c>
       <c r="X17" t="n">
         <v>-24377.9248764107</v>
@@ -2046,7 +1994,7 @@
         <v>380.5290257264724</v>
       </c>
       <c r="Z17" t="n">
-        <v>117.5959999999999</v>
+        <v>207300632.6712884</v>
       </c>
       <c r="AA17" t="n">
         <v>1.695154011482158e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>89.10550813941626</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 64.049x + -26268.556</t>
-        </is>
+      <c r="W18" t="n">
+        <v>64.04879359737185</v>
       </c>
       <c r="X18" t="n">
         <v>-26268.55606877112</v>
@@ -2098,7 +2044,7 @@
         <v>377.5196203385924</v>
       </c>
       <c r="Z18" t="n">
-        <v>115.3820000000001</v>
+        <v>117820159.098676</v>
       </c>
       <c r="AA18" t="n">
         <v>1.692053420978269e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>89.08940839896985</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 62.916x + -25535.822</t>
-        </is>
+      <c r="W19" t="n">
+        <v>62.91619141931726</v>
       </c>
       <c r="X19" t="n">
         <v>-25535.82191588283</v>
@@ -2150,7 +2094,7 @@
         <v>374.4969979867185</v>
       </c>
       <c r="Z19" t="n">
-        <v>111.521</v>
+        <v>156466484.3031162</v>
       </c>
       <c r="AA19" t="n">
         <v>1.687436587151995e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>89.05474568298867</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 60.609x + -24340.325</t>
-        </is>
+      <c r="W20" t="n">
+        <v>60.60864275585362</v>
       </c>
       <c r="X20" t="n">
         <v>-24340.3247656731</v>
@@ -2202,7 +2144,7 @@
         <v>371.4986777876879</v>
       </c>
       <c r="Z20" t="n">
-        <v>111.873</v>
+        <v>222024150.6506714</v>
       </c>
       <c r="AA20" t="n">
         <v>1.68509893582668e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>89.1488362482192</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 67.310x + -26900.502</t>
-        </is>
+      <c r="W21" t="n">
+        <v>67.30968568500788</v>
       </c>
       <c r="X21" t="n">
         <v>-26900.50165895274</v>
@@ -2254,7 +2194,7 @@
         <v>368.4761277387811</v>
       </c>
       <c r="Z21" t="n">
-        <v>106.295</v>
+        <v>327113719.9689867</v>
       </c>
       <c r="AA21" t="n">
         <v>1.680504414924477e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>89.10539835048284</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 64.041x + -25303.807</t>
-        </is>
+      <c r="W22" t="n">
+        <v>64.04093200722461</v>
       </c>
       <c r="X22" t="n">
         <v>-25303.80680019316</v>
@@ -2306,7 +2244,7 @@
         <v>365.4780612686336</v>
       </c>
       <c r="Z22" t="n">
-        <v>107.269</v>
+        <v>298274177.4419369</v>
       </c>
       <c r="AA22" t="n">
         <v>1.67870213672396e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>88.18517492560989</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 31.560x + -16088.814</t>
-        </is>
+      <c r="W2" t="n">
+        <v>31.56040640467317</v>
       </c>
       <c r="X2" t="n">
         <v>-16088.81420677342</v>
@@ -2504,7 +2440,7 @@
         <v>450.4684834829814</v>
       </c>
       <c r="Z2" t="n">
-        <v>326.13</v>
+        <v>28832820.6289399</v>
       </c>
       <c r="AA2" t="n">
         <v>1.837048170211643e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>88.43713032555434</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 36.652x + -17721.496</t>
-        </is>
+      <c r="W3" t="n">
+        <v>36.65153243247671</v>
       </c>
       <c r="X3" t="n">
         <v>-17721.49634677437</v>
@@ -2556,7 +2490,7 @@
         <v>436.945861412715</v>
       </c>
       <c r="Z3" t="n">
-        <v>278.083</v>
+        <v>238201488.2065381</v>
       </c>
       <c r="AA3" t="n">
         <v>1.782556758605042e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>88.53373275930893</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 39.067x + -18470.522</t>
-        </is>
+      <c r="W4" t="n">
+        <v>39.06741522660464</v>
       </c>
       <c r="X4" t="n">
         <v>-18470.5222536253</v>
@@ -2608,7 +2540,7 @@
         <v>414.3112736839394</v>
       </c>
       <c r="Z4" t="n">
-        <v>249.624</v>
+        <v>3534.597164143562</v>
       </c>
       <c r="AA4" t="n">
         <v>2.562502442294363e-06</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>88.72532217965134</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 44.942x + -21133.161</t>
-        </is>
+      <c r="W5" t="n">
+        <v>44.94180848117169</v>
       </c>
       <c r="X5" t="n">
         <v>-21133.16091644632</v>
@@ -2660,7 +2590,7 @@
         <v>427.0585486463653</v>
       </c>
       <c r="Z5" t="n">
-        <v>224.401</v>
+        <v>175095748.6313168</v>
       </c>
       <c r="AA5" t="n">
         <v>1.723974774484817e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>88.76879421157902</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 46.529x + -21547.561</t>
-        </is>
+      <c r="W6" t="n">
+        <v>46.52915119437498</v>
       </c>
       <c r="X6" t="n">
         <v>-21547.56147767845</v>
@@ -2712,7 +2640,7 @@
         <v>422.7493752504539</v>
       </c>
       <c r="Z6" t="n">
-        <v>207.116</v>
+        <v>115613851.7829081</v>
       </c>
       <c r="AA6" t="n">
         <v>1.702798754841155e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>88.84376734030843</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 49.547x + -22702.574</t>
-        </is>
+      <c r="W7" t="n">
+        <v>49.54712289458529</v>
       </c>
       <c r="X7" t="n">
         <v>-22702.57419919123</v>
@@ -2764,7 +2690,7 @@
         <v>418.6153878666947</v>
       </c>
       <c r="Z7" t="n">
-        <v>192.922</v>
+        <v>114297912.4161528</v>
       </c>
       <c r="AA7" t="n">
         <v>1.686923980205979e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>88.88027298043149</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 51.163x + -23160.916</t>
-        </is>
+      <c r="W8" t="n">
+        <v>51.16290317173809</v>
       </c>
       <c r="X8" t="n">
         <v>-23160.91605284272</v>
@@ -2816,7 +2740,7 @@
         <v>414.8066137859243</v>
       </c>
       <c r="Z8" t="n">
-        <v>180.4830000000001</v>
+        <v>113911701.4805088</v>
       </c>
       <c r="AA8" t="n">
         <v>1.671914608872588e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>88.9374410821389</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 53.916x + -24186.023</t>
-        </is>
+      <c r="W9" t="n">
+        <v>53.91626756947566</v>
       </c>
       <c r="X9" t="n">
         <v>-24186.02289824299</v>
@@ -2868,7 +2790,7 @@
         <v>411.1964330576128</v>
       </c>
       <c r="Z9" t="n">
-        <v>170.912</v>
+        <v>112476134.3346335</v>
       </c>
       <c r="AA9" t="n">
         <v>1.660903334854821e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>89.02204433206558</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 58.582x + -26103.312</t>
-        </is>
+      <c r="W10" t="n">
+        <v>58.58160772475124</v>
       </c>
       <c r="X10" t="n">
         <v>-26103.31153531824</v>
@@ -2920,7 +2840,7 @@
         <v>397.6480759034161</v>
       </c>
       <c r="Z10" t="n">
-        <v>159.095</v>
+        <v>3337.356367973481</v>
       </c>
       <c r="AA10" t="n">
         <v>4.398185265419246e-06</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>89.00696568856972</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 57.692x + -25393.939</t>
-        </is>
+      <c r="W11" t="n">
+        <v>57.6919062531543</v>
       </c>
       <c r="X11" t="n">
         <v>-25393.93913333458</v>
@@ -2972,7 +2890,7 @@
         <v>395.385174804119</v>
       </c>
       <c r="Z11" t="n">
-        <v>152.358</v>
+        <v>3309.521757091255</v>
       </c>
       <c r="AA11" t="n">
         <v>3.86398736120781e-06</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>89.08710479955295</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 62.757x + -27463.065</t>
-        </is>
+      <c r="W12" t="n">
+        <v>62.75740195408181</v>
       </c>
       <c r="X12" t="n">
         <v>-27463.06474505195</v>
@@ -3024,7 +2940,7 @@
         <v>393.1439615832914</v>
       </c>
       <c r="Z12" t="n">
-        <v>144.2209999999999</v>
+        <v>3282.148245631112</v>
       </c>
       <c r="AA12" t="n">
         <v>4.640301048061864e-06</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>89.12278836452018</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 65.311x + -28329.992</t>
-        </is>
+      <c r="W13" t="n">
+        <v>65.3106962503746</v>
       </c>
       <c r="X13" t="n">
         <v>-28329.992125253</v>
@@ -3076,7 +2990,7 @@
         <v>390.838525250868</v>
       </c>
       <c r="Z13" t="n">
-        <v>136.078</v>
+        <v>3257.801580590356</v>
       </c>
       <c r="AA13" t="n">
         <v>5.755749929442009e-06</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>89.11322531876897</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 64.606x + -27727.522</t>
-        </is>
+      <c r="W14" t="n">
+        <v>64.60627004950472</v>
       </c>
       <c r="X14" t="n">
         <v>-27727.52163474765</v>
@@ -3128,7 +3040,7 @@
         <v>388.5851151114368</v>
       </c>
       <c r="Z14" t="n">
-        <v>131.7619999999999</v>
+        <v>3231.417363139588</v>
       </c>
       <c r="AA14" t="n">
         <v>5.634747470496693e-06</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>89.1650016430421</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 68.613x + -29245.628</t>
-        </is>
+      <c r="W15" t="n">
+        <v>68.61297714370748</v>
       </c>
       <c r="X15" t="n">
         <v>-29245.62761920104</v>
@@ -3180,7 +3090,7 @@
         <v>391.327822567147</v>
       </c>
       <c r="Z15" t="n">
-        <v>127.6</v>
+        <v>5236.532117874331</v>
       </c>
       <c r="AA15" t="n">
         <v>7.643917021953699e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>89.12779420332863</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 65.686x + -27662.537</t>
-        </is>
+      <c r="W16" t="n">
+        <v>65.68559145130547</v>
       </c>
       <c r="X16" t="n">
         <v>-27662.5367367368</v>
@@ -3232,7 +3140,7 @@
         <v>388.7695746202324</v>
       </c>
       <c r="Z16" t="n">
-        <v>125.127</v>
+        <v>317453227.8957834</v>
       </c>
       <c r="AA16" t="n">
         <v>1.609519091912995e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>89.14943303210345</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 67.357x + -28123.082</t>
-        </is>
+      <c r="W17" t="n">
+        <v>67.35691917241277</v>
       </c>
       <c r="X17" t="n">
         <v>-28123.08245496312</v>
@@ -3284,7 +3190,7 @@
         <v>385.7283556142595</v>
       </c>
       <c r="Z17" t="n">
-        <v>119.9429999999999</v>
+        <v>108447564.1346637</v>
       </c>
       <c r="AA17" t="n">
         <v>1.603503911150147e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>89.19919001883319</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 71.543x + -29665.815</t>
-        </is>
+      <c r="W18" t="n">
+        <v>71.54262546588316</v>
       </c>
       <c r="X18" t="n">
         <v>-29665.81517515678</v>
@@ -3336,7 +3240,7 @@
         <v>382.7288031680701</v>
       </c>
       <c r="Z18" t="n">
-        <v>114.354</v>
+        <v>313217643.6100243</v>
       </c>
       <c r="AA18" t="n">
         <v>1.598774880315277e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>89.23578150019959</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 74.969x + -30852.623</t>
-        </is>
+      <c r="W19" t="n">
+        <v>74.96858783113515</v>
       </c>
       <c r="X19" t="n">
         <v>-30852.6232540144</v>
@@ -3388,7 +3290,7 @@
         <v>379.7377611207317</v>
       </c>
       <c r="Z19" t="n">
-        <v>108.39</v>
+        <v>413092949.4906744</v>
       </c>
       <c r="AA19" t="n">
         <v>1.594107282117107e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>89.14549169996715</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 67.046x + -27211.056</t>
-        </is>
+      <c r="W20" t="n">
+        <v>67.04619651680511</v>
       </c>
       <c r="X20" t="n">
         <v>-27211.05566833534</v>
@@ -3440,7 +3340,7 @@
         <v>376.8309540999307</v>
       </c>
       <c r="Z20" t="n">
-        <v>108.2</v>
+        <v>1024963641.172531</v>
       </c>
       <c r="AA20" t="n">
         <v>1.590356800892361e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>89.24036593942184</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 75.421x + -30491.363</t>
-        </is>
+      <c r="W21" t="n">
+        <v>75.42108146753357</v>
       </c>
       <c r="X21" t="n">
         <v>-30491.36332095984</v>
@@ -3492,7 +3390,7 @@
         <v>373.9924789566734</v>
       </c>
       <c r="Z21" t="n">
-        <v>104.229</v>
+        <v>1219714497.02813</v>
       </c>
       <c r="AA21" t="n">
         <v>1.587205510494637e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>89.2594148876689</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 77.361x + -31030.122</t>
-        </is>
+      <c r="W22" t="n">
+        <v>77.36124812118389</v>
       </c>
       <c r="X22" t="n">
         <v>-31030.1220791261</v>
@@ -3544,7 +3440,7 @@
         <v>371.1337623225913</v>
       </c>
       <c r="Z22" t="n">
-        <v>100.227</v>
+        <v>202846650.1296242</v>
       </c>
       <c r="AA22" t="n">
         <v>1.583705252172225e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>87.19793351182348</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 20.431x + -10804.473</t>
-        </is>
+      <c r="W2" t="n">
+        <v>20.43138299841736</v>
       </c>
       <c r="X2" t="n">
         <v>-10804.47260449541</v>
@@ -3742,7 +3636,7 @@
         <v>454.5794073840062</v>
       </c>
       <c r="Z2" t="n">
-        <v>516.1890000000001</v>
+        <v>736737071.9532801</v>
       </c>
       <c r="AA2" t="n">
         <v>2.003872975957584e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>87.68962738094933</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.786x + -11630.288</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.78592478400139</v>
       </c>
       <c r="X3" t="n">
         <v>-11630.28770275351</v>
@@ -3794,7 +3686,7 @@
         <v>408.9207503450474</v>
       </c>
       <c r="Z3" t="n">
-        <v>424.239</v>
+        <v>3489.288174957848</v>
       </c>
       <c r="AA3" t="n">
         <v>2.324373287264978e-06</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>88.03664702988991</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 29.171x + -13296.596</t>
-        </is>
+      <c r="W4" t="n">
+        <v>29.17119467278279</v>
       </c>
       <c r="X4" t="n">
         <v>-13296.59635142475</v>
@@ -3846,7 +3736,7 @@
         <v>417.4499877467158</v>
       </c>
       <c r="Z4" t="n">
-        <v>359.397</v>
+        <v>966855033.5855224</v>
       </c>
       <c r="AA4" t="n">
         <v>1.828363463551726e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>88.28014656513224</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 33.304x + -14939.030</t>
-        </is>
+      <c r="W5" t="n">
+        <v>33.30433220507999</v>
       </c>
       <c r="X5" t="n">
         <v>-14939.02966586925</v>
@@ -3898,7 +3786,7 @@
         <v>411.9548059643218</v>
       </c>
       <c r="Z5" t="n">
-        <v>312.485</v>
+        <v>112876492.8521605</v>
       </c>
       <c r="AA5" t="n">
         <v>1.778603561807484e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>88.46697743725498</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 37.365x + -16558.876</t>
-        </is>
+      <c r="W6" t="n">
+        <v>37.36546844546758</v>
       </c>
       <c r="X6" t="n">
         <v>-16558.87633341621</v>
@@ -3950,7 +3836,7 @@
         <v>396.160984841526</v>
       </c>
       <c r="Z6" t="n">
-        <v>277.463</v>
+        <v>3331.650565335081</v>
       </c>
       <c r="AA6" t="n">
         <v>3.884789522626573e-06</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>88.60767135371988</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 41.143x + -17995.618</t>
-        </is>
+      <c r="W7" t="n">
+        <v>41.14294496942372</v>
       </c>
       <c r="X7" t="n">
         <v>-17995.61827354145</v>
@@ -4002,7 +3886,7 @@
         <v>392.7280518508706</v>
       </c>
       <c r="Z7" t="n">
-        <v>251.1650000000001</v>
+        <v>3287.27072288689</v>
       </c>
       <c r="AA7" t="n">
         <v>4.521316533480897e-06</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>88.72244516517623</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 44.841x + -19367.250</t>
-        </is>
+      <c r="W8" t="n">
+        <v>44.84056746076497</v>
       </c>
       <c r="X8" t="n">
         <v>-19367.25000866836</v>
@@ -4054,7 +3936,7 @@
         <v>389.3162630114839</v>
       </c>
       <c r="Z8" t="n">
-        <v>229.595</v>
+        <v>3246.866204574776</v>
       </c>
       <c r="AA8" t="n">
         <v>4.448483453491044e-06</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>88.77241592232483</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 46.666x + -19817.192</t>
-        </is>
+      <c r="W9" t="n">
+        <v>46.66646719615327</v>
       </c>
       <c r="X9" t="n">
         <v>-19817.1919479509</v>
@@ -4106,7 +3986,7 @@
         <v>385.959650966054</v>
       </c>
       <c r="Z9" t="n">
-        <v>213.3079999999999</v>
+        <v>3207.657416673737</v>
       </c>
       <c r="AA9" t="n">
         <v>5.600902006448315e-06</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>88.84041693729746</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 49.404x + -20694.792</t>
-        </is>
+      <c r="W10" t="n">
+        <v>49.40392662251721</v>
       </c>
       <c r="X10" t="n">
         <v>-20694.79226048642</v>
@@ -4158,7 +4036,7 @@
         <v>387.3450379457233</v>
       </c>
       <c r="Z10" t="n">
-        <v>198.412</v>
+        <v>6379.659292308062</v>
       </c>
       <c r="AA10" t="n">
         <v>1.122412543331055e-06</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>88.95390704849997</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 54.765x + -22756.507</t>
-        </is>
+      <c r="W11" t="n">
+        <v>54.76512660680767</v>
       </c>
       <c r="X11" t="n">
         <v>-22756.50704360376</v>
@@ -4210,7 +4086,7 @@
         <v>383.2532454365163</v>
       </c>
       <c r="Z11" t="n">
-        <v>184.275</v>
+        <v>312966827.1727201</v>
       </c>
       <c r="AA11" t="n">
         <v>1.644941800157093e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>87.76498880630163</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 25.623x + -12826.701</t>
-        </is>
+      <c r="W2" t="n">
+        <v>25.62256305199043</v>
       </c>
       <c r="X2" t="n">
         <v>-12826.70080709606</v>
@@ -4408,7 +4282,7 @@
         <v>445.5217413763704</v>
       </c>
       <c r="Z2" t="n">
-        <v>411.295</v>
+        <v>364301404.1346943</v>
       </c>
       <c r="AA2" t="n">
         <v>1.91923481557885e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>88.19650747490451</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 31.759x + -15183.470</t>
-        </is>
+      <c r="W3" t="n">
+        <v>31.75885383049608</v>
       </c>
       <c r="X3" t="n">
         <v>-15183.47037551354</v>
@@ -4460,7 +4332,7 @@
         <v>427.9261418923682</v>
       </c>
       <c r="Z3" t="n">
-        <v>325.431</v>
+        <v>15303.38066629657</v>
       </c>
       <c r="AA3" t="n">
         <v>1.88800024798695e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>88.49949242872881</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 38.176x + -17996.417</t>
-        </is>
+      <c r="W4" t="n">
+        <v>38.17553551956504</v>
       </c>
       <c r="X4" t="n">
         <v>-17996.41734846085</v>
@@ -4512,7 +4382,7 @@
         <v>428.6542212651177</v>
       </c>
       <c r="Z4" t="n">
-        <v>269.539</v>
+        <v>116762374.6555094</v>
       </c>
       <c r="AA4" t="n">
         <v>1.765931770364124e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>88.6738344489425</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 43.196x + -20102.819</t>
-        </is>
+      <c r="W5" t="n">
+        <v>43.19637718867707</v>
       </c>
       <c r="X5" t="n">
         <v>-20102.8191344386</v>
@@ -4564,7 +4432,7 @@
         <v>423.9464700506286</v>
       </c>
       <c r="Z5" t="n">
-        <v>233.819</v>
+        <v>173605973.5623363</v>
       </c>
       <c r="AA5" t="n">
         <v>1.728458101141928e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>88.80615247011848</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 47.986x + -22072.289</t>
-        </is>
+      <c r="W6" t="n">
+        <v>47.98559777798011</v>
       </c>
       <c r="X6" t="n">
         <v>-22072.28940661754</v>
@@ -4616,7 +4482,7 @@
         <v>409.4762507523336</v>
       </c>
       <c r="Z6" t="n">
-        <v>208.241</v>
+        <v>6634.489808736175</v>
       </c>
       <c r="AA6" t="n">
         <v>4.474904544031344e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>88.89680133452164</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 51.930x + -23590.427</t>
-        </is>
+      <c r="W7" t="n">
+        <v>51.92963029835049</v>
       </c>
       <c r="X7" t="n">
         <v>-23590.42694492583</v>
@@ -4668,7 +4532,7 @@
         <v>414.7822903069173</v>
       </c>
       <c r="Z7" t="n">
-        <v>188.177</v>
+        <v>464361701.3064986</v>
       </c>
       <c r="AA7" t="n">
         <v>1.679803956322664e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>88.96059567111276</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 55.118x + -24738.503</t>
-        </is>
+      <c r="W8" t="n">
+        <v>55.11762121378192</v>
       </c>
       <c r="X8" t="n">
         <v>-24738.50326950821</v>
@@ -4720,7 +4582,7 @@
         <v>410.6263840299802</v>
       </c>
       <c r="Z8" t="n">
-        <v>171.5380000000001</v>
+        <v>224219218.8157094</v>
       </c>
       <c r="AA8" t="n">
         <v>1.662751648033464e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>88.97844311556345</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 56.081x + -24829.512</t>
-        </is>
+      <c r="W9" t="n">
+        <v>56.08078117214754</v>
       </c>
       <c r="X9" t="n">
         <v>-24829.51235185706</v>
@@ -4772,7 +4632,7 @@
         <v>396.9008938885154</v>
       </c>
       <c r="Z9" t="n">
-        <v>159.1630000000001</v>
+        <v>3330.061449918616</v>
       </c>
       <c r="AA9" t="n">
         <v>4.344437710028993e-06</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>89.04388766450577</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 59.920x + -26313.311</t>
-        </is>
+      <c r="W10" t="n">
+        <v>59.92021959529691</v>
       </c>
       <c r="X10" t="n">
         <v>-26313.31105928323</v>
@@ -4824,7 +4682,7 @@
         <v>394.4043571083006</v>
       </c>
       <c r="Z10" t="n">
-        <v>148.453</v>
+        <v>3299.951747559794</v>
       </c>
       <c r="AA10" t="n">
         <v>3.67483432733058e-06</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>89.12237823926489</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 65.280x + -28470.458</t>
-        </is>
+      <c r="W11" t="n">
+        <v>65.28017085281029</v>
       </c>
       <c r="X11" t="n">
         <v>-28470.45822842</v>
@@ -4876,7 +4732,7 @@
         <v>392.0388811811654</v>
       </c>
       <c r="Z11" t="n">
-        <v>140.0120000000001</v>
+        <v>3273.180475907599</v>
       </c>
       <c r="AA11" t="n">
         <v>6.128354893777338e-06</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>89.14996582156013</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 67.399x + -29121.175</t>
-        </is>
+      <c r="W12" t="n">
+        <v>67.39914374254423</v>
       </c>
       <c r="X12" t="n">
         <v>-29121.17547699118</v>
@@ -4928,7 +4782,7 @@
         <v>389.7561682247307</v>
       </c>
       <c r="Z12" t="n">
-        <v>130.943</v>
+        <v>3245.541536701804</v>
       </c>
       <c r="AA12" t="n">
         <v>5.700437883643665e-06</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>89.16134179986844</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 68.314x + -29230.219</t>
-        </is>
+      <c r="W13" t="n">
+        <v>68.31351262685321</v>
       </c>
       <c r="X13" t="n">
         <v>-29230.2190850054</v>
@@ -4980,7 +4832,7 @@
         <v>387.4442877909653</v>
       </c>
       <c r="Z13" t="n">
-        <v>126.54</v>
+        <v>3218.404699776368</v>
       </c>
       <c r="AA13" t="n">
         <v>5.583406276037654e-06</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>89.20508838239715</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 72.074x + -30606.603</t>
-        </is>
+      <c r="W14" t="n">
+        <v>72.07355137642995</v>
       </c>
       <c r="X14" t="n">
         <v>-30606.60289461131</v>
@@ -5032,7 +4882,7 @@
         <v>389.7406547608484</v>
       </c>
       <c r="Z14" t="n">
-        <v>118.631</v>
+        <v>6428.329509532081</v>
       </c>
       <c r="AA14" t="n">
         <v>1.404332381958741e-06</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>89.1878417462287</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 70.543x + -29635.204</t>
-        </is>
+      <c r="W15" t="n">
+        <v>70.54283052890734</v>
       </c>
       <c r="X15" t="n">
         <v>-29635.20413203444</v>
@@ -5084,7 +4932,7 @@
         <v>387.2330232416897</v>
       </c>
       <c r="Z15" t="n">
-        <v>114.64</v>
+        <v>1685873676.812895</v>
       </c>
       <c r="AA15" t="n">
         <v>1.602149282356551e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>89.18097761505307</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 69.952x + -29097.288</t>
-        </is>
+      <c r="W16" t="n">
+        <v>69.95153975064504</v>
       </c>
       <c r="X16" t="n">
         <v>-29097.28831433077</v>
@@ -5136,7 +4982,7 @@
         <v>384.180802477226</v>
       </c>
       <c r="Z16" t="n">
-        <v>111.169</v>
+        <v>32699356.54622534</v>
       </c>
       <c r="AA16" t="n">
         <v>1.595471982436994e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>89.20381774901686</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 71.959x + -29700.810</t>
-        </is>
+      <c r="W17" t="n">
+        <v>71.95851386817088</v>
       </c>
       <c r="X17" t="n">
         <v>-29700.81025677378</v>
@@ -5188,7 +5032,7 @@
         <v>381.1678759208106</v>
       </c>
       <c r="Z17" t="n">
-        <v>106.103</v>
+        <v>156745896.91315</v>
       </c>
       <c r="AA17" t="n">
         <v>1.592581634940034e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>89.24646638241214</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 76.032x + -31154.694</t>
-        </is>
+      <c r="W18" t="n">
+        <v>76.03174528134205</v>
       </c>
       <c r="X18" t="n">
         <v>-31154.69381519698</v>
@@ -5240,7 +5082,7 @@
         <v>378.1684127705454</v>
       </c>
       <c r="Z18" t="n">
-        <v>101.91</v>
+        <v>824277120.1782154</v>
       </c>
       <c r="AA18" t="n">
         <v>1.589103556328105e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>89.24863645460839</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 76.251x + -30964.859</t>
-        </is>
+      <c r="W19" t="n">
+        <v>76.25136383642679</v>
       </c>
       <c r="X19" t="n">
         <v>-30964.85902371214</v>
@@ -5292,7 +5132,7 @@
         <v>375.2080221451005</v>
       </c>
       <c r="Z19" t="n">
-        <v>99.745</v>
+        <v>204741793.2675469</v>
       </c>
       <c r="AA19" t="n">
         <v>1.585612533663524e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>89.20082965421912</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 71.689x + -28783.942</t>
-        </is>
+      <c r="W20" t="n">
+        <v>71.68942656224965</v>
       </c>
       <c r="X20" t="n">
         <v>-28783.94244058224</v>
@@ -5344,7 +5182,7 @@
         <v>372.271572841044</v>
       </c>
       <c r="Z20" t="n">
-        <v>97.34300000000002</v>
+        <v>102338665.8058016</v>
       </c>
       <c r="AA20" t="n">
         <v>1.581391330094839e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>89.22789773890457</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 74.203x + -29563.860</t>
-        </is>
+      <c r="W21" t="n">
+        <v>74.20300929673849</v>
       </c>
       <c r="X21" t="n">
         <v>-29563.8603020616</v>
@@ -5396,7 +5232,7 @@
         <v>369.2783700430094</v>
       </c>
       <c r="Z21" t="n">
-        <v>94.233</v>
+        <v>167282172.5652885</v>
       </c>
       <c r="AA21" t="n">
         <v>1.578380550462287e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>89.24567236948779</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 75.952x + -30011.966</t>
-        </is>
+      <c r="W22" t="n">
+        <v>75.95170426001862</v>
       </c>
       <c r="X22" t="n">
         <v>-30011.96598531417</v>
@@ -5448,7 +5282,7 @@
         <v>366.3474447787102</v>
       </c>
       <c r="Z22" t="n">
-        <v>90.32999999999998</v>
+        <v>199545158.8411019</v>
       </c>
       <c r="AA22" t="n">
         <v>1.574402716137631e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>86.10449652226727</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.686x + -7984.235</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.68551327358024</v>
       </c>
       <c r="X2" t="n">
         <v>-7984.234650369973</v>
@@ -5646,7 +5478,7 @@
         <v>465.9385210326996</v>
       </c>
       <c r="Z2" t="n">
-        <v>698.2180000000001</v>
+        <v>125944830.0616441</v>
       </c>
       <c r="AA2" t="n">
         <v>2.217924434706812e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>87.07975860361393</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 19.603x + -9314.389</t>
-        </is>
+      <c r="W3" t="n">
+        <v>19.60322807675627</v>
       </c>
       <c r="X3" t="n">
         <v>-9314.38895203223</v>
@@ -5698,7 +5528,7 @@
         <v>429.6809189207714</v>
       </c>
       <c r="Z3" t="n">
-        <v>536.298</v>
+        <v>235133123.0002992</v>
       </c>
       <c r="AA3" t="n">
         <v>2.027784351602589e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>87.63522719125206</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 24.215x + -11088.536</t>
-        </is>
+      <c r="W4" t="n">
+        <v>24.21511351682594</v>
       </c>
       <c r="X4" t="n">
         <v>-11088.53596514757</v>
@@ -5750,7 +5578,7 @@
         <v>419.1457457201915</v>
       </c>
       <c r="Z4" t="n">
-        <v>432.936</v>
+        <v>114473230.6109785</v>
       </c>
       <c r="AA4" t="n">
         <v>1.912782323924476e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>88.04764426360474</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.336x + -13231.085</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.33563858171446</v>
       </c>
       <c r="X5" t="n">
         <v>-13231.08512810853</v>
@@ -5802,7 +5628,7 @@
         <v>412.8967978783018</v>
       </c>
       <c r="Z5" t="n">
-        <v>358.3320000000001</v>
+        <v>119797743.5511172</v>
       </c>
       <c r="AA5" t="n">
         <v>1.835494335189894e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>88.35315008012894</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 34.782x + -15489.980</t>
-        </is>
+      <c r="W6" t="n">
+        <v>34.781554475208</v>
       </c>
       <c r="X6" t="n">
         <v>-15489.98017282409</v>
@@ -5854,7 +5678,7 @@
         <v>395.9831167167076</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.413</v>
+        <v>3336.055198839147</v>
       </c>
       <c r="AA6" t="n">
         <v>3.05322933536866e-06</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>88.52520479587945</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 38.841x + -17009.142</t>
-        </is>
+      <c r="W7" t="n">
+        <v>38.84141000421531</v>
       </c>
       <c r="X7" t="n">
         <v>-17009.14249155791</v>
@@ -5906,7 +5728,7 @@
         <v>392.2258068671704</v>
       </c>
       <c r="Z7" t="n">
-        <v>266.626</v>
+        <v>3287.626786119543</v>
       </c>
       <c r="AA7" t="n">
         <v>4.265270617677732e-06</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>88.65921782205136</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 42.725x + -18422.555</t>
-        </is>
+      <c r="W8" t="n">
+        <v>42.72529982653244</v>
       </c>
       <c r="X8" t="n">
         <v>-18422.55495118479</v>
@@ -5958,7 +5778,7 @@
         <v>388.5763487116285</v>
       </c>
       <c r="Z8" t="n">
-        <v>237.98</v>
+        <v>3241.865783801222</v>
       </c>
       <c r="AA8" t="n">
         <v>6.159831949522686e-06</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>88.72436859326332</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 44.908x + -19002.983</t>
-        </is>
+      <c r="W9" t="n">
+        <v>44.90820155836985</v>
       </c>
       <c r="X9" t="n">
         <v>-19002.98295864273</v>
@@ -6010,7 +5828,7 @@
         <v>385.0824326971173</v>
       </c>
       <c r="Z9" t="n">
-        <v>216.23</v>
+        <v>3198.838064944804</v>
       </c>
       <c r="AA9" t="n">
         <v>5.578920216903476e-06</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>88.85729932848511</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 50.134x + -21035.600</t>
-        </is>
+      <c r="W10" t="n">
+        <v>50.1340238155891</v>
       </c>
       <c r="X10" t="n">
         <v>-21035.60011296409</v>
@@ -6062,7 +5878,7 @@
         <v>386.4806172968474</v>
       </c>
       <c r="Z10" t="n">
-        <v>198.86</v>
+        <v>6365.913405262596</v>
       </c>
       <c r="AA10" t="n">
         <v>1.397234723466366e-06</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>88.89963523684352</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 52.063x + -21517.563</t>
-        </is>
+      <c r="W11" t="n">
+        <v>52.06340396749443</v>
       </c>
       <c r="X11" t="n">
         <v>-21517.56347801927</v>
@@ -6114,7 +5928,7 @@
         <v>382.3158348878899</v>
       </c>
       <c r="Z11" t="n">
-        <v>185.408</v>
+        <v>416139392.9200711</v>
       </c>
       <c r="AA11" t="n">
         <v>1.654709682333789e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>87.18653222989532</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 20.348x + -10250.959</t>
-        </is>
+      <c r="W2" t="n">
+        <v>20.34845453634298</v>
       </c>
       <c r="X2" t="n">
         <v>-10250.95867513279</v>
@@ -6312,7 +6124,7 @@
         <v>447.743774507379</v>
       </c>
       <c r="Z2" t="n">
-        <v>509.7910000000001</v>
+        <v>30778583.24879043</v>
       </c>
       <c r="AA2" t="n">
         <v>2.052089358659983e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>88.10521808608657</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 30.228x + -14561.042</t>
-        </is>
+      <c r="W3" t="n">
+        <v>30.22769567372829</v>
       </c>
       <c r="X3" t="n">
         <v>-14561.04227016276</v>
@@ -6364,7 +6174,7 @@
         <v>435.21944108829</v>
       </c>
       <c r="Z3" t="n">
-        <v>342.783</v>
+        <v>475366282.7591516</v>
       </c>
       <c r="AA3" t="n">
         <v>1.86397735280607e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>88.42475046954964</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 36.363x + -17150.115</t>
-        </is>
+      <c r="W4" t="n">
+        <v>36.36334524389967</v>
       </c>
       <c r="X4" t="n">
         <v>-17150.11455124067</v>
@@ -6416,7 +6224,7 @@
         <v>412.6806406451644</v>
       </c>
       <c r="Z4" t="n">
-        <v>273.986</v>
+        <v>3522.630093569946</v>
       </c>
       <c r="AA4" t="n">
         <v>2.578283406252619e-06</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>88.64437714473877</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 42.257x + -19714.397</t>
-        </is>
+      <c r="W5" t="n">
+        <v>42.25739298285365</v>
       </c>
       <c r="X5" t="n">
         <v>-19714.39747457574</v>
@@ -6468,7 +6274,7 @@
         <v>425.0270033480434</v>
       </c>
       <c r="Z5" t="n">
-        <v>231.005</v>
+        <v>231840496.8403437</v>
       </c>
       <c r="AA5" t="n">
         <v>1.740383282684285e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>88.82450896285805</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 48.735x + -22545.273</t>
-        </is>
+      <c r="W6" t="n">
+        <v>48.73515714877987</v>
       </c>
       <c r="X6" t="n">
         <v>-22545.27319824054</v>
@@ -6520,7 +6324,7 @@
         <v>422.7110849134795</v>
       </c>
       <c r="Z6" t="n">
-        <v>201.1249999999999</v>
+        <v>10926.48629287233</v>
       </c>
       <c r="AA6" t="n">
         <v>2.44331616981372e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>88.85921148358472</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 50.218x + -22886.242</t>
-        </is>
+      <c r="W7" t="n">
+        <v>50.2180792139989</v>
       </c>
       <c r="X7" t="n">
         <v>-22886.24164235841</v>
@@ -6572,7 +6374,7 @@
         <v>416.3709010465464</v>
       </c>
       <c r="Z7" t="n">
-        <v>184.603</v>
+        <v>227030833.2324212</v>
       </c>
       <c r="AA7" t="n">
         <v>1.689034763179671e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>88.91292527282339</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 52.700x + -23744.987</t>
-        </is>
+      <c r="W8" t="n">
+        <v>52.70006088901937</v>
       </c>
       <c r="X8" t="n">
         <v>-23744.98673057721</v>
@@ -6624,7 +6424,7 @@
         <v>413.121377527487</v>
       </c>
       <c r="Z8" t="n">
-        <v>171.938</v>
+        <v>6683.192422803645</v>
       </c>
       <c r="AA8" t="n">
         <v>1.106353207470936e-06</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>88.9661537017887</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 55.414x + -24730.506</t>
-        </is>
+      <c r="W9" t="n">
+        <v>55.41400228333963</v>
       </c>
       <c r="X9" t="n">
         <v>-24730.50644335342</v>
@@ -6676,7 +6474,7 @@
         <v>409.2460785515499</v>
       </c>
       <c r="Z9" t="n">
-        <v>159.488</v>
+        <v>5466.576901333721</v>
       </c>
       <c r="AA9" t="n">
         <v>7.727846956299995e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>89.06871706157064</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 61.518x + -27316.270</t>
-        </is>
+      <c r="W10" t="n">
+        <v>61.51807510217653</v>
       </c>
       <c r="X10" t="n">
         <v>-27316.27022963938</v>
@@ -6728,7 +6524,7 @@
         <v>395.8910871285624</v>
       </c>
       <c r="Z10" t="n">
-        <v>148.47</v>
+        <v>3320.625198204999</v>
       </c>
       <c r="AA10" t="n">
         <v>4.574161057298543e-06</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>89.00823369920913</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 57.766x + -25295.647</t>
-        </is>
+      <c r="W11" t="n">
+        <v>57.7656822962722</v>
       </c>
       <c r="X11" t="n">
         <v>-25295.6471690317</v>
@@ -6780,7 +6574,7 @@
         <v>393.8316717896972</v>
       </c>
       <c r="Z11" t="n">
-        <v>145.249</v>
+        <v>3293.769767612086</v>
       </c>
       <c r="AA11" t="n">
         <v>3.578325690877909e-06</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>89.05655104008662</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 60.725x + -26418.907</t>
-        </is>
+      <c r="W12" t="n">
+        <v>60.72464275806209</v>
       </c>
       <c r="X12" t="n">
         <v>-26418.90728981206</v>
@@ -6832,7 +6624,7 @@
         <v>391.8424530579769</v>
       </c>
       <c r="Z12" t="n">
-        <v>139.0890000000001</v>
+        <v>3270.317355555084</v>
       </c>
       <c r="AA12" t="n">
         <v>6.066630005625109e-06</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>89.1296181681449</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 65.823x + -28499.843</t>
-        </is>
+      <c r="W13" t="n">
+        <v>65.82326286770892</v>
       </c>
       <c r="X13" t="n">
         <v>-28499.84257358155</v>
@@ -6884,7 +6674,7 @@
         <v>389.8289478579588</v>
       </c>
       <c r="Z13" t="n">
-        <v>131.6079999999999</v>
+        <v>3246.622202714017</v>
       </c>
       <c r="AA13" t="n">
         <v>5.708662111489181e-06</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>89.13147266081205</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 65.964x + -28311.090</t>
-        </is>
+      <c r="W14" t="n">
+        <v>65.96383129253033</v>
       </c>
       <c r="X14" t="n">
         <v>-28311.08958908441</v>
@@ -6936,7 +6724,7 @@
         <v>387.8941981626574</v>
       </c>
       <c r="Z14" t="n">
-        <v>128.303</v>
+        <v>3225.342151708438</v>
       </c>
       <c r="AA14" t="n">
         <v>5.619389206315173e-06</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>89.15968101814754</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 68.178x + -29049.599</t>
-        </is>
+      <c r="W15" t="n">
+        <v>68.17848050415313</v>
       </c>
       <c r="X15" t="n">
         <v>-29049.59931635962</v>
@@ -6988,7 +6774,7 @@
         <v>391.1532336160193</v>
       </c>
       <c r="Z15" t="n">
-        <v>122.366</v>
+        <v>6451.145522897522</v>
       </c>
       <c r="AA15" t="n">
         <v>1.050197949507803e-06</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>89.11445303669798</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 64.696x + -27259.194</t>
-        </is>
+      <c r="W16" t="n">
+        <v>64.69585415819186</v>
       </c>
       <c r="X16" t="n">
         <v>-27259.19356633699</v>
@@ -7040,7 +6824,7 @@
         <v>388.8264473583125</v>
       </c>
       <c r="Z16" t="n">
-        <v>120.816</v>
+        <v>159832079.2250715</v>
       </c>
       <c r="AA16" t="n">
         <v>1.615536210353232e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>89.16896176629569</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 68.940x + -28880.545</t>
-        </is>
+      <c r="W17" t="n">
+        <v>68.93998283402046</v>
       </c>
       <c r="X17" t="n">
         <v>-28880.54549330903</v>
@@ -7092,7 +6874,7 @@
         <v>386.034710055192</v>
       </c>
       <c r="Z17" t="n">
-        <v>116.407</v>
+        <v>420412153.1588411</v>
       </c>
       <c r="AA17" t="n">
         <v>1.611705287351e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>89.16317318030586</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 68.463x + -28425.147</t>
-        </is>
+      <c r="W18" t="n">
+        <v>68.46303685303937</v>
       </c>
       <c r="X18" t="n">
         <v>-28425.14716559185</v>
@@ -7144,7 +6924,7 @@
         <v>383.2136317446345</v>
       </c>
       <c r="Z18" t="n">
-        <v>113.7910000000001</v>
+        <v>313980803.5212577</v>
       </c>
       <c r="AA18" t="n">
         <v>1.607471483106774e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>89.19079324006958</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 70.800x + -29184.068</t>
-        </is>
+      <c r="W19" t="n">
+        <v>70.80016225361923</v>
       </c>
       <c r="X19" t="n">
         <v>-29184.06750991363</v>
@@ -7196,7 +6974,7 @@
         <v>380.3232093163263</v>
       </c>
       <c r="Z19" t="n">
-        <v>110.864</v>
+        <v>310644615.4314929</v>
       </c>
       <c r="AA19" t="n">
         <v>1.604137434342052e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>89.19279528563034</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 70.976x + -28988.997</t>
-        </is>
+      <c r="W20" t="n">
+        <v>70.97578558132599</v>
       </c>
       <c r="X20" t="n">
         <v>-28988.99657579932</v>
@@ -7248,7 +7024,7 @@
         <v>377.3952586420104</v>
       </c>
       <c r="Z20" t="n">
-        <v>107.718</v>
+        <v>206279049.5861789</v>
       </c>
       <c r="AA20" t="n">
         <v>1.60055151696587e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>89.25410106462239</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 76.810x + -31198.966</t>
-        </is>
+      <c r="W21" t="n">
+        <v>76.81006093117836</v>
       </c>
       <c r="X21" t="n">
         <v>-31198.96571073774</v>
@@ -7300,7 +7074,7 @@
         <v>374.4372449724538</v>
       </c>
       <c r="Z21" t="n">
-        <v>104.699</v>
+        <v>319226464.8156897</v>
       </c>
       <c r="AA21" t="n">
         <v>1.598147789401788e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>89.21795392947773</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 73.259x + -29436.657</t>
-        </is>
+      <c r="W22" t="n">
+        <v>73.25939417993858</v>
       </c>
       <c r="X22" t="n">
         <v>-29436.65716876552</v>
@@ -7352,7 +7124,7 @@
         <v>371.479829090248</v>
       </c>
       <c r="Z22" t="n">
-        <v>103.25</v>
+        <v>606907419.4105353</v>
       </c>
       <c r="AA22" t="n">
         <v>1.595275182660601e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.69387133424055</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.767x + -5387.806</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.76715063313547</v>
       </c>
       <c r="X2" t="n">
         <v>-5387.805928715256</v>
@@ -7550,7 +7320,7 @@
         <v>439.5821624890179</v>
       </c>
       <c r="Z2" t="n">
-        <v>916.8920000000001</v>
+        <v>179437612.1642645</v>
       </c>
       <c r="AA2" t="n">
         <v>2.656262698550957e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>86.45393516384725</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.137x + -7388.070</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.13693137386896</v>
       </c>
       <c r="X3" t="n">
         <v>-7388.069706441625</v>
@@ -7602,7 +7370,7 @@
         <v>400.8704822541768</v>
       </c>
       <c r="Z3" t="n">
-        <v>624.9380000000001</v>
+        <v>3419.239551428888</v>
       </c>
       <c r="AA3" t="n">
         <v>2.532936774713646e-06</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>87.41118647874454</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 22.117x + -9881.900</t>
-        </is>
+      <c r="W4" t="n">
+        <v>22.11699813021316</v>
       </c>
       <c r="X4" t="n">
         <v>-9881.900400862911</v>
@@ -7654,7 +7420,7 @@
         <v>409.407617747873</v>
       </c>
       <c r="Z4" t="n">
-        <v>458.975</v>
+        <v>181930353.206481</v>
       </c>
       <c r="AA4" t="n">
         <v>2.018214439935201e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>87.94948734474607</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 27.930x + -12292.182</t>
-        </is>
+      <c r="W5" t="n">
+        <v>27.93024266086277</v>
       </c>
       <c r="X5" t="n">
         <v>-12292.18184384115</v>
@@ -7706,7 +7470,7 @@
         <v>392.2942363708429</v>
       </c>
       <c r="Z5" t="n">
-        <v>360.698</v>
+        <v>3311.443666203407</v>
       </c>
       <c r="AA5" t="n">
         <v>3.426062328510996e-06</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>88.31136112682967</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 33.920x + -14767.628</t>
-        </is>
+      <c r="W6" t="n">
+        <v>33.92033080645216</v>
       </c>
       <c r="X6" t="n">
         <v>-14767.62845276563</v>
@@ -7758,7 +7520,7 @@
         <v>389.1104300571027</v>
       </c>
       <c r="Z6" t="n">
-        <v>295.8559999999999</v>
+        <v>3266.097246308253</v>
       </c>
       <c r="AA6" t="n">
         <v>3.625341197155095e-06</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>88.52341347472644</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 38.794x + -16633.027</t>
-        </is>
+      <c r="W7" t="n">
+        <v>38.79426870998044</v>
       </c>
       <c r="X7" t="n">
         <v>-16633.02655156043</v>
@@ -7810,7 +7570,7 @@
         <v>385.7990518375054</v>
       </c>
       <c r="Z7" t="n">
-        <v>252.701</v>
+        <v>3219.360410303704</v>
       </c>
       <c r="AA7" t="n">
         <v>5.694982343220032e-06</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>88.64962108815162</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 42.422x + -17889.926</t>
-        </is>
+      <c r="W8" t="n">
+        <v>42.42155278758862</v>
       </c>
       <c r="X8" t="n">
         <v>-17889.92606714007</v>
@@ -7862,7 +7620,7 @@
         <v>387.7873766025926</v>
       </c>
       <c r="Z8" t="n">
-        <v>224.205</v>
+        <v>6402.446348565064</v>
       </c>
       <c r="AA8" t="n">
         <v>9.583818891856134e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>88.7830010822081</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 47.072x + -19597.341</t>
-        </is>
+      <c r="W9" t="n">
+        <v>47.07248445762566</v>
       </c>
       <c r="X9" t="n">
         <v>-19597.34089013432</v>
@@ -7914,7 +7670,7 @@
         <v>383.7743960295181</v>
       </c>
       <c r="Z9" t="n">
-        <v>199.7330000000001</v>
+        <v>313346146.0761515</v>
       </c>
       <c r="AA9" t="n">
         <v>1.723040403138065e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>88.82390532328188</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 48.710x + -19947.208</t>
-        </is>
+      <c r="W10" t="n">
+        <v>48.71013643486328</v>
       </c>
       <c r="X10" t="n">
         <v>-19947.20813040185</v>
@@ -7966,7 +7720,7 @@
         <v>379.1208119834776</v>
       </c>
       <c r="Z10" t="n">
-        <v>184.455</v>
+        <v>206565007.5045739</v>
       </c>
       <c r="AA10" t="n">
         <v>1.704464585334878e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>88.92454085184558</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 53.269x + -21601.165</t>
-        </is>
+      <c r="W11" t="n">
+        <v>53.2693878287027</v>
       </c>
       <c r="X11" t="n">
         <v>-21601.1652768092</v>
@@ -8018,7 +7770,7 @@
         <v>374.8848460024854</v>
       </c>
       <c r="Z11" t="n">
-        <v>168.986</v>
+        <v>229459817.9932854</v>
       </c>
       <c r="AA11" t="n">
         <v>1.689847293904402e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>87.82290876471947</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 26.305x + -13183.646</t>
-        </is>
+      <c r="W2" t="n">
+        <v>26.30491608296539</v>
       </c>
       <c r="X2" t="n">
         <v>-13183.64591278973</v>
@@ -8216,7 +7966,7 @@
         <v>445.2107445227359</v>
       </c>
       <c r="Z2" t="n">
-        <v>371.904</v>
+        <v>484757949.2143062</v>
       </c>
       <c r="AA2" t="n">
         <v>1.985003324268114e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>88.4011402363483</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 35.826x + -17219.712</t>
-        </is>
+      <c r="W3" t="n">
+        <v>35.82609793986977</v>
       </c>
       <c r="X3" t="n">
         <v>-17219.7122207606</v>
@@ -8268,7 +8016,7 @@
         <v>414.0888565555738</v>
       </c>
       <c r="Z3" t="n">
-        <v>270.399</v>
+        <v>3551.88036038065</v>
       </c>
       <c r="AA3" t="n">
         <v>2.824848398905355e-06</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>88.65591714947475</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 42.620x + -20167.683</t>
-        </is>
+      <c r="W4" t="n">
+        <v>42.620340682535</v>
       </c>
       <c r="X4" t="n">
         <v>-20167.68347234795</v>
@@ -8320,7 +8066,7 @@
         <v>427.8187709455693</v>
       </c>
       <c r="Z4" t="n">
-        <v>223.461</v>
+        <v>240267045.2171544</v>
       </c>
       <c r="AA4" t="n">
         <v>1.799402542672796e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>88.7299404691602</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 45.105x + -20992.341</t>
-        </is>
+      <c r="W5" t="n">
+        <v>45.10528322733751</v>
       </c>
       <c r="X5" t="n">
         <v>-20992.34145579227</v>
@@ -8372,7 +8116,7 @@
         <v>423.4845522674789</v>
       </c>
       <c r="Z5" t="n">
-        <v>196.9239999999999</v>
+        <v>230711883.3746552</v>
       </c>
       <c r="AA5" t="n">
         <v>1.764613456250841e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>88.80509088880189</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 47.943x + -22050.598</t>
-        </is>
+      <c r="W6" t="n">
+        <v>47.94295405932738</v>
       </c>
       <c r="X6" t="n">
         <v>-22050.59842642148</v>
@@ -8424,7 +8166,7 @@
         <v>419.3363685423765</v>
       </c>
       <c r="Z6" t="n">
-        <v>180.642</v>
+        <v>114431946.7009747</v>
       </c>
       <c r="AA6" t="n">
         <v>1.742469253335535e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>88.85215892479286</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 49.909x + -22692.498</t>
-        </is>
+      <c r="W7" t="n">
+        <v>49.90944775667173</v>
       </c>
       <c r="X7" t="n">
         <v>-22692.49838129308</v>
@@ -8476,7 +8216,7 @@
         <v>415.069877870661</v>
       </c>
       <c r="Z7" t="n">
-        <v>167.714</v>
+        <v>6699.275184442167</v>
       </c>
       <c r="AA7" t="n">
         <v>8.432145177788463e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>88.8574131229344</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 50.139x + -22513.854</t>
-        </is>
+      <c r="W8" t="n">
+        <v>50.13901817247561</v>
       </c>
       <c r="X8" t="n">
         <v>-22513.85403880199</v>
@@ -8528,7 +8266,7 @@
         <v>411.7900922825735</v>
       </c>
       <c r="Z8" t="n">
-        <v>158.921</v>
+        <v>6788.468379783648</v>
       </c>
       <c r="AA8" t="n">
         <v>6.638363161511533e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>88.99057701950217</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 56.755x + -25371.295</t>
-        </is>
+      <c r="W9" t="n">
+        <v>56.75504974144478</v>
       </c>
       <c r="X9" t="n">
         <v>-25371.29466502148</v>
@@ -8580,7 +8316,7 @@
         <v>397.3939176713774</v>
       </c>
       <c r="Z9" t="n">
-        <v>147.3020000000001</v>
+        <v>3339.040714941274</v>
       </c>
       <c r="AA9" t="n">
         <v>4.251818003045368e-06</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>88.99394217515265</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 56.945x + -25198.542</t>
-        </is>
+      <c r="W10" t="n">
+        <v>56.94492852542965</v>
       </c>
       <c r="X10" t="n">
         <v>-25198.54161031957</v>
@@ -8632,7 +8366,7 @@
         <v>394.9405005528467</v>
       </c>
       <c r="Z10" t="n">
-        <v>142.7090000000001</v>
+        <v>3312.978033132198</v>
       </c>
       <c r="AA10" t="n">
         <v>3.572980120354203e-06</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>88.99417310334179</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 56.958x + -24938.719</t>
-        </is>
+      <c r="W11" t="n">
+        <v>56.95800522115</v>
       </c>
       <c r="X11" t="n">
         <v>-24938.71876990232</v>
@@ -8684,7 +8416,7 @@
         <v>392.6520746059164</v>
       </c>
       <c r="Z11" t="n">
-        <v>138.268</v>
+        <v>3285.306692972217</v>
       </c>
       <c r="AA11" t="n">
         <v>4.877486350574464e-06</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>89.0113552010319</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 57.948x + -25150.243</t>
-        </is>
+      <c r="W12" t="n">
+        <v>57.94810539584014</v>
       </c>
       <c r="X12" t="n">
         <v>-25150.24252877807</v>
@@ -8736,7 +8466,7 @@
         <v>390.4070269839705</v>
       </c>
       <c r="Z12" t="n">
-        <v>134.1199999999999</v>
+        <v>3257.477024161224</v>
       </c>
       <c r="AA12" t="n">
         <v>5.730720833761005e-06</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>89.06915122590496</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 61.547x + -26531.690</t>
-        </is>
+      <c r="W13" t="n">
+        <v>61.54677327370452</v>
       </c>
       <c r="X13" t="n">
         <v>-26531.69042211393</v>
@@ -8788,7 +8516,7 @@
         <v>388.1213415078581</v>
       </c>
       <c r="Z13" t="n">
-        <v>128.152</v>
+        <v>3232.569053716101</v>
       </c>
       <c r="AA13" t="n">
         <v>5.629135381785853e-06</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>89.03403213158484</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 59.309x + -25280.494</t>
-        </is>
+      <c r="W14" t="n">
+        <v>59.30875421748169</v>
       </c>
       <c r="X14" t="n">
         <v>-25280.49402069625</v>
@@ -8840,7 +8566,7 @@
         <v>390.583764969574</v>
       </c>
       <c r="Z14" t="n">
-        <v>123.9520000000001</v>
+        <v>6458.350086340269</v>
       </c>
       <c r="AA14" t="n">
         <v>1.23462095952067e-06</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>89.04748147753429</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 60.146x + -25419.839</t>
-        </is>
+      <c r="W15" t="n">
+        <v>60.14633800435683</v>
       </c>
       <c r="X15" t="n">
         <v>-25419.83934485272</v>
@@ -8892,7 +8616,7 @@
         <v>389.2140831090402</v>
       </c>
       <c r="Z15" t="n">
-        <v>122.354</v>
+        <v>212123666.6558876</v>
       </c>
       <c r="AA15" t="n">
         <v>1.667756367745261e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>89.09557239948225</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 63.345x + -26595.582</t>
-        </is>
+      <c r="W16" t="n">
+        <v>63.34505993899006</v>
       </c>
       <c r="X16" t="n">
         <v>-26595.58197902434</v>
@@ -8944,7 +8666,7 @@
         <v>386.1619194211478</v>
       </c>
       <c r="Z16" t="n">
-        <v>119.337</v>
+        <v>630147973.6149029</v>
       </c>
       <c r="AA16" t="n">
         <v>1.664281427213033e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>89.1260787236988</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 65.557x + -27301.216</t>
-        </is>
+      <c r="W17" t="n">
+        <v>65.55663278592131</v>
       </c>
       <c r="X17" t="n">
         <v>-27301.21563522803</v>
@@ -8996,7 +8716,7 @@
         <v>383.1139822365346</v>
       </c>
       <c r="Z17" t="n">
-        <v>110.985</v>
+        <v>235037887.056922</v>
       </c>
       <c r="AA17" t="n">
         <v>1.658346229963305e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>89.11289757595712</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 64.582x + -26639.038</t>
-        </is>
+      <c r="W18" t="n">
+        <v>64.58239724468777</v>
       </c>
       <c r="X18" t="n">
         <v>-26639.03816144041</v>
@@ -9048,7 +8766,7 @@
         <v>380.0618972010561</v>
       </c>
       <c r="Z18" t="n">
-        <v>113.409</v>
+        <v>1033766805.194658</v>
       </c>
       <c r="AA18" t="n">
         <v>1.656828516500103e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>89.14182050853864</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 66.759x + -27314.911</t>
-        </is>
+      <c r="W19" t="n">
+        <v>66.75933810862095</v>
       </c>
       <c r="X19" t="n">
         <v>-27314.91109448129</v>
@@ -9100,7 +8816,7 @@
         <v>376.961918160021</v>
       </c>
       <c r="Z19" t="n">
-        <v>110.349</v>
+        <v>309418650.2319997</v>
       </c>
       <c r="AA19" t="n">
         <v>1.653061657371997e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>89.13020675648549</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 65.868x + -26689.192</t>
-        </is>
+      <c r="W20" t="n">
+        <v>65.86781226420273</v>
       </c>
       <c r="X20" t="n">
         <v>-26689.19248452581</v>
@@ -9152,7 +8866,7 @@
         <v>373.938434749889</v>
       </c>
       <c r="Z20" t="n">
-        <v>108.847</v>
+        <v>205348113.3277394</v>
       </c>
       <c r="AA20" t="n">
         <v>1.649336675343289e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>89.09339115417504</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 63.193x + -25320.881</t>
-        </is>
+      <c r="W21" t="n">
+        <v>63.19263025762518</v>
       </c>
       <c r="X21" t="n">
         <v>-25320.88127509539</v>
@@ -9204,7 +8916,7 @@
         <v>370.903070994451</v>
       </c>
       <c r="Z21" t="n">
-        <v>109.006</v>
+        <v>38637295.74779098</v>
       </c>
       <c r="AA21" t="n">
         <v>1.645484748636624e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>89.16389312927488</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 68.522x + -27301.233</t>
-        </is>
+      <c r="W22" t="n">
+        <v>68.52199689964934</v>
       </c>
       <c r="X22" t="n">
         <v>-27301.23258940838</v>
@@ -9256,7 +8966,7 @@
         <v>367.7975938516235</v>
       </c>
       <c r="Z22" t="n">
-        <v>106.333</v>
+        <v>800821460.7859757</v>
       </c>
       <c r="AA22" t="n">
         <v>1.645206086526355e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>85.59107526851361</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.970x + -6441.186</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.969748643155</v>
       </c>
       <c r="X2" t="n">
         <v>-6441.185630714731</v>
@@ -9454,7 +9162,7 @@
         <v>431.8804385697641</v>
       </c>
       <c r="Z2" t="n">
-        <v>754.7139999999999</v>
+        <v>236325911.4878342</v>
       </c>
       <c r="AA2" t="n">
         <v>2.421535611000204e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>87.13674553142994</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 19.994x + -8801.431</t>
-        </is>
+      <c r="W3" t="n">
+        <v>19.9940581085279</v>
       </c>
       <c r="X3" t="n">
         <v>-8801.431445806935</v>
@@ -9506,7 +9212,7 @@
         <v>388.8880946342742</v>
       </c>
       <c r="Z3" t="n">
-        <v>497.308</v>
+        <v>3286.19399190833</v>
       </c>
       <c r="AA3" t="n">
         <v>1.320028754645425e-06</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>87.91102970620548</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 27.416x + -11727.899</t>
-        </is>
+      <c r="W4" t="n">
+        <v>27.41560753252618</v>
       </c>
       <c r="X4" t="n">
         <v>-11727.89934096327</v>
@@ -9558,7 +9262,7 @@
         <v>383.6039142069445</v>
       </c>
       <c r="Z4" t="n">
-        <v>361.8100000000001</v>
+        <v>3210.996368504371</v>
       </c>
       <c r="AA4" t="n">
         <v>4.203063429814494e-06</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>88.32852274969719</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 34.269x + -14433.980</t>
-        </is>
+      <c r="W5" t="n">
+        <v>34.26880306046514</v>
       </c>
       <c r="X5" t="n">
         <v>-14433.98027306289</v>
@@ -9610,7 +9312,7 @@
         <v>386.2083336826761</v>
       </c>
       <c r="Z5" t="n">
-        <v>284.087</v>
+        <v>6380.724393138067</v>
       </c>
       <c r="AA5" t="n">
         <v>8.038272625164862e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>88.51560631152049</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 38.590x + -15955.651</t>
-        </is>
+      <c r="W6" t="n">
+        <v>38.59013978514398</v>
       </c>
       <c r="X6" t="n">
         <v>-15955.65087096711</v>
@@ -9662,7 +9362,7 @@
         <v>382.4736754823203</v>
       </c>
       <c r="Z6" t="n">
-        <v>238.5700000000001</v>
+        <v>209185431.4402277</v>
       </c>
       <c r="AA6" t="n">
         <v>1.794745490306424e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>88.65957793641439</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 42.737x + -17405.514</t>
-        </is>
+      <c r="W7" t="n">
+        <v>42.73678248728942</v>
       </c>
       <c r="X7" t="n">
         <v>-17405.51411385684</v>
@@ -9714,7 +9412,7 @@
         <v>377.2917233827275</v>
       </c>
       <c r="Z7" t="n">
-        <v>206.832</v>
+        <v>307775388.5564924</v>
       </c>
       <c r="AA7" t="n">
         <v>1.761317038744865e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>88.78294966683336</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 47.070x + -18921.753</t>
-        </is>
+      <c r="W8" t="n">
+        <v>47.07049524034769</v>
       </c>
       <c r="X8" t="n">
         <v>-18921.75319589645</v>
@@ -9766,7 +9462,7 @@
         <v>372.3037068619515</v>
       </c>
       <c r="Z8" t="n">
-        <v>184.732</v>
+        <v>304006294.589339</v>
       </c>
       <c r="AA8" t="n">
         <v>1.73812905593134e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>88.87275466523322</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 50.822x + -20167.596</t>
-        </is>
+      <c r="W9" t="n">
+        <v>50.82157807793389</v>
       </c>
       <c r="X9" t="n">
         <v>-20167.59559117172</v>
@@ -9818,7 +9512,7 @@
         <v>367.5314693890718</v>
       </c>
       <c r="Z9" t="n">
-        <v>169.393</v>
+        <v>38393525.61343922</v>
       </c>
       <c r="AA9" t="n">
         <v>1.720479364240339e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>88.93311863277523</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 53.698x + -21028.191</t>
-        </is>
+      <c r="W10" t="n">
+        <v>53.69777665278218</v>
       </c>
       <c r="X10" t="n">
         <v>-21028.19098596118</v>
@@ -9870,7 +9562,7 @@
         <v>363.1266844353947</v>
       </c>
       <c r="Z10" t="n">
-        <v>156.482</v>
+        <v>148258672.0502665</v>
       </c>
       <c r="AA10" t="n">
         <v>1.709239146154232e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>88.9737992355857</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 55.827x + -21600.451</t>
-        </is>
+      <c r="W11" t="n">
+        <v>55.82694415265196</v>
       </c>
       <c r="X11" t="n">
         <v>-21600.45072945064</v>
@@ -9922,7 +9612,7 @@
         <v>351.5106155674105</v>
       </c>
       <c r="Z11" t="n">
-        <v>147.681</v>
+        <v>5898.008891584643</v>
       </c>
       <c r="AA11" t="n">
         <v>1.235512271654899e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-608.6600000000001</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-487.385</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-416.6139999999999</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-361.974</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-325.338</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-294.284</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-269.049</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-248.641</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-225.139</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-212.641</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-516.1890000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-424.239</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-359.397</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-312.485</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-277.463</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-251.1650000000001</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-229.595</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-213.3079999999999</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-198.412</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-184.275</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-698.2180000000001</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-536.298</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-432.936</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-358.3320000000001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-303.413</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-266.626</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-237.98</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-216.23</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-198.86</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-185.408</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-916.8920000000001</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-624.9380000000001</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-458.975</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-360.698</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-295.8559999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-252.701</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-224.205</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-199.7330000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-184.455</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-168.986</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-754.7139999999999</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-497.308</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-361.8100000000001</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-284.087</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-238.5700000000001</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-206.832</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-184.732</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-169.393</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-156.482</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-147.681</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-608.6600000000001</v>
+        <v>97.28100000000001</v>
       </c>
       <c r="D2" t="n">
         <v>1.5369e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-487.385</v>
+        <v>92.44900000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.50123e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-416.6139999999999</v>
+        <v>87.62200000000001</v>
       </c>
       <c r="D4" t="n">
         <v>1.48329e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-361.974</v>
+        <v>88.428</v>
       </c>
       <c r="D5" t="n">
         <v>1.47135e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-325.338</v>
+        <v>84.20600000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.46258e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-294.284</v>
+        <v>78.577</v>
       </c>
       <c r="D7" t="n">
         <v>1.45626e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-269.049</v>
+        <v>76.40300000000002</v>
       </c>
       <c r="D8" t="n">
         <v>1.45096e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-248.641</v>
+        <v>73.80000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>1.44661e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-225.139</v>
+        <v>73.86100000000005</v>
       </c>
       <c r="D10" t="n">
         <v>1.44317e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-212.641</v>
+        <v>70.34899999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.43999e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-286.5500000000001</v>
+        <v>102.808</v>
       </c>
       <c r="D2" t="n">
         <v>1.52874e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-229.497</v>
+        <v>89.36900000000003</v>
       </c>
       <c r="D3" t="n">
         <v>1.51864e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-200.145</v>
+        <v>84.33500000000004</v>
       </c>
       <c r="D4" t="n">
         <v>1.51232e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-180.649</v>
+        <v>82.63200000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.50798e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-168.091</v>
+        <v>80.65300000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.50537e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-158.6559999999999</v>
+        <v>76.928</v>
       </c>
       <c r="D7" t="n">
         <v>1.5037e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-150.795</v>
+        <v>76.46300000000002</v>
       </c>
       <c r="D8" t="n">
         <v>1.50231e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-142.993</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>1.50176e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-140.446</v>
+        <v>71.96299999999997</v>
       </c>
       <c r="D10" t="n">
         <v>1.50105e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-135.631</v>
+        <v>70.26400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>1.50078e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-131.0170000000001</v>
+        <v>69.63499999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.50054e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-126.0149999999999</v>
+        <v>69.911</v>
       </c>
       <c r="D13" t="n">
         <v>1.50039e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-125.866</v>
+        <v>66.96699999999998</v>
       </c>
       <c r="D14" t="n">
         <v>1.50045e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-121.0189999999999</v>
+        <v>66.23099999999999</v>
       </c>
       <c r="D15" t="n">
         <v>1.5005e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-120.169</v>
+        <v>63.53700000000003</v>
       </c>
       <c r="D16" t="n">
         <v>1.50046e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-117.5959999999999</v>
+        <v>63.39699999999999</v>
       </c>
       <c r="D17" t="n">
         <v>1.50041e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-115.3820000000001</v>
+        <v>63.50899999999996</v>
       </c>
       <c r="D18" t="n">
         <v>1.50048e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-111.521</v>
+        <v>61.73399999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.50077e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-111.873</v>
+        <v>59.654</v>
       </c>
       <c r="D20" t="n">
         <v>1.50097e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-106.295</v>
+        <v>60.66199999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.50091e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-107.269</v>
+        <v>58.286</v>
       </c>
       <c r="D22" t="n">
         <v>1.50118e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-326.13</v>
+        <v>111.569</v>
       </c>
       <c r="D2" t="n">
         <v>1.4458e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-278.083</v>
+        <v>92.62700000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.44701e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-249.624</v>
+        <v>84.10599999999999</v>
       </c>
       <c r="D4" t="n">
         <v>1.44392e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-224.401</v>
+        <v>85.24400000000003</v>
       </c>
       <c r="D5" t="n">
         <v>1.44064e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-207.116</v>
+        <v>81.00900000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.438e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-192.922</v>
+        <v>79.471</v>
       </c>
       <c r="D7" t="n">
         <v>1.43573e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-180.4830000000001</v>
+        <v>76.327</v>
       </c>
       <c r="D8" t="n">
         <v>1.43369e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-170.912</v>
+        <v>74.90300000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.43237e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-159.095</v>
+        <v>74.71899999999999</v>
       </c>
       <c r="D10" t="n">
         <v>1.43113e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-152.358</v>
+        <v>71.50599999999997</v>
       </c>
       <c r="D11" t="n">
         <v>1.43053e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-144.2209999999999</v>
+        <v>71.74599999999998</v>
       </c>
       <c r="D12" t="n">
         <v>1.42966e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-136.078</v>
+        <v>70.08499999999998</v>
       </c>
       <c r="D13" t="n">
         <v>1.42916e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-131.7619999999999</v>
+        <v>68.21199999999999</v>
       </c>
       <c r="D14" t="n">
         <v>1.42854e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-127.6</v>
+        <v>67.95099999999996</v>
       </c>
       <c r="D15" t="n">
         <v>1.42828e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-125.127</v>
+        <v>65.00800000000004</v>
       </c>
       <c r="D16" t="n">
         <v>1.42802e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-119.9429999999999</v>
+        <v>64.149</v>
       </c>
       <c r="D17" t="n">
         <v>1.42778e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-114.354</v>
+        <v>63.66700000000003</v>
       </c>
       <c r="D18" t="n">
         <v>1.42772e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-108.39</v>
+        <v>63.09300000000002</v>
       </c>
       <c r="D19" t="n">
         <v>1.42793e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-108.2</v>
+        <v>59.72399999999999</v>
       </c>
       <c r="D20" t="n">
         <v>1.42774e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-104.229</v>
+        <v>60.34000000000003</v>
       </c>
       <c r="D21" t="n">
         <v>1.42781e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-100.227</v>
+        <v>60.12399999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.42815e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-516.1890000000001</v>
+        <v>129.99</v>
       </c>
       <c r="D2" t="n">
         <v>1.44567e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-424.239</v>
+        <v>85.50400000000002</v>
       </c>
       <c r="D3" t="n">
         <v>1.46029e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-359.397</v>
+        <v>77.54300000000001</v>
       </c>
       <c r="D4" t="n">
         <v>1.45557e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-312.485</v>
+        <v>73.39400000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.44921e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-277.463</v>
+        <v>71.78499999999997</v>
       </c>
       <c r="D6" t="n">
         <v>1.44382e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-251.1650000000001</v>
+        <v>69.63799999999998</v>
       </c>
       <c r="D7" t="n">
         <v>1.43966e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-229.595</v>
+        <v>67.887</v>
       </c>
       <c r="D8" t="n">
         <v>1.43633e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-213.3079999999999</v>
+        <v>63.94400000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.43368e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-198.412</v>
+        <v>62.01099999999997</v>
       </c>
       <c r="D10" t="n">
         <v>1.43162e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-184.275</v>
+        <v>62.42699999999996</v>
       </c>
       <c r="D11" t="n">
         <v>1.43006e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-411.295</v>
+        <v>106.705</v>
       </c>
       <c r="D2" t="n">
         <v>1.46314e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-325.431</v>
+        <v>89.92000000000002</v>
       </c>
       <c r="D3" t="n">
         <v>1.45624e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-269.539</v>
+        <v>86.75099999999998</v>
       </c>
       <c r="D4" t="n">
         <v>1.44916e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-233.819</v>
+        <v>83.63099999999997</v>
       </c>
       <c r="D5" t="n">
         <v>1.44353e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-208.241</v>
+        <v>81.73200000000003</v>
       </c>
       <c r="D6" t="n">
         <v>1.43943e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-188.177</v>
+        <v>79.34900000000005</v>
       </c>
       <c r="D7" t="n">
         <v>1.43615e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-171.5380000000001</v>
+        <v>77.149</v>
       </c>
       <c r="D8" t="n">
         <v>1.43417e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-159.1630000000001</v>
+        <v>73.39099999999996</v>
       </c>
       <c r="D9" t="n">
         <v>1.43228e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-148.453</v>
+        <v>72.53700000000003</v>
       </c>
       <c r="D10" t="n">
         <v>1.43116e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-140.0120000000001</v>
+        <v>72.33399999999995</v>
       </c>
       <c r="D11" t="n">
         <v>1.43021e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-130.943</v>
+        <v>71.02100000000002</v>
       </c>
       <c r="D12" t="n">
         <v>1.42966e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-126.54</v>
+        <v>68.92000000000002</v>
       </c>
       <c r="D13" t="n">
         <v>1.42903e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-118.631</v>
+        <v>68.77800000000002</v>
       </c>
       <c r="D14" t="n">
         <v>1.42868e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-114.64</v>
+        <v>66.82499999999999</v>
       </c>
       <c r="D15" t="n">
         <v>1.42845e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-111.169</v>
+        <v>64.565</v>
       </c>
       <c r="D16" t="n">
         <v>1.42846e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-106.103</v>
+        <v>64.21700000000004</v>
       </c>
       <c r="D17" t="n">
         <v>1.42851e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-101.91</v>
+        <v>64.08499999999998</v>
       </c>
       <c r="D18" t="n">
         <v>1.42865e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-99.745</v>
+        <v>62.55700000000002</v>
       </c>
       <c r="D19" t="n">
         <v>1.42879e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-97.34300000000002</v>
+        <v>60.09100000000001</v>
       </c>
       <c r="D20" t="n">
         <v>1.42897e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-94.233</v>
+        <v>59.94599999999997</v>
       </c>
       <c r="D21" t="n">
         <v>1.42901e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-90.32999999999998</v>
+        <v>58.75299999999999</v>
       </c>
       <c r="D22" t="n">
         <v>1.42914e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-698.2180000000001</v>
+        <v>137.544</v>
       </c>
       <c r="D2" t="n">
         <v>1.46552e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-536.298</v>
+        <v>90.36699999999996</v>
       </c>
       <c r="D3" t="n">
         <v>1.48235e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-432.936</v>
+        <v>79.47200000000004</v>
       </c>
       <c r="D4" t="n">
         <v>1.47334e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-358.3320000000001</v>
+        <v>76.82999999999998</v>
       </c>
       <c r="D5" t="n">
         <v>1.46346e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-303.413</v>
+        <v>74.733</v>
       </c>
       <c r="D6" t="n">
         <v>1.45553e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-266.626</v>
+        <v>71.06799999999998</v>
       </c>
       <c r="D7" t="n">
         <v>1.44965e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-237.98</v>
+        <v>68.54599999999999</v>
       </c>
       <c r="D8" t="n">
         <v>1.44513e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-216.23</v>
+        <v>63.29699999999997</v>
       </c>
       <c r="D9" t="n">
         <v>1.44184e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-198.86</v>
+        <v>63.92100000000005</v>
       </c>
       <c r="D10" t="n">
         <v>1.43944e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-185.408</v>
+        <v>60.53500000000003</v>
       </c>
       <c r="D11" t="n">
         <v>1.43775e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-509.7910000000001</v>
+        <v>108.15</v>
       </c>
       <c r="D2" t="n">
         <v>1.48966e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-342.783</v>
+        <v>93.166</v>
       </c>
       <c r="D3" t="n">
         <v>1.46983e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-273.986</v>
+        <v>84.99800000000005</v>
       </c>
       <c r="D4" t="n">
         <v>1.45814e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-231.005</v>
+        <v>83.40699999999998</v>
       </c>
       <c r="D5" t="n">
         <v>1.4504e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-201.1249999999999</v>
+        <v>82.41899999999998</v>
       </c>
       <c r="D6" t="n">
         <v>1.44557e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-184.603</v>
+        <v>78.279</v>
       </c>
       <c r="D7" t="n">
         <v>1.44212e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-171.938</v>
+        <v>76.28500000000003</v>
       </c>
       <c r="D8" t="n">
         <v>1.43979e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-159.488</v>
+        <v>74.70000000000005</v>
       </c>
       <c r="D9" t="n">
         <v>1.43841e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-148.47</v>
+        <v>75.37799999999999</v>
       </c>
       <c r="D10" t="n">
         <v>1.43722e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-145.249</v>
+        <v>70.90499999999997</v>
       </c>
       <c r="D11" t="n">
         <v>1.43611e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-139.0890000000001</v>
+        <v>70.32599999999996</v>
       </c>
       <c r="D12" t="n">
         <v>1.43544e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-131.6079999999999</v>
+        <v>70.27800000000002</v>
       </c>
       <c r="D13" t="n">
         <v>1.4353e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-128.303</v>
+        <v>69.04499999999996</v>
       </c>
       <c r="D14" t="n">
         <v>1.43474e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-122.366</v>
+        <v>68.36199999999997</v>
       </c>
       <c r="D15" t="n">
         <v>1.43446e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-120.816</v>
+        <v>65.73099999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1.43442e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-116.407</v>
+        <v>65.62799999999999</v>
       </c>
       <c r="D17" t="n">
         <v>1.43441e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-113.7910000000001</v>
+        <v>63.923</v>
       </c>
       <c r="D18" t="n">
         <v>1.43414e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-110.864</v>
+        <v>63.81099999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.43426e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-107.718</v>
+        <v>62.517</v>
       </c>
       <c r="D20" t="n">
         <v>1.43445e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-104.699</v>
+        <v>62.59499999999997</v>
       </c>
       <c r="D21" t="n">
         <v>1.43491e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-103.25</v>
+        <v>60.60300000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.43515e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-916.8920000000001</v>
+        <v>114.597</v>
       </c>
       <c r="D2" t="n">
         <v>1.57293e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-624.9380000000001</v>
+        <v>83.63999999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.55133e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-458.975</v>
+        <v>75.69200000000001</v>
       </c>
       <c r="D4" t="n">
         <v>1.52503e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-360.698</v>
+        <v>71.43200000000002</v>
       </c>
       <c r="D5" t="n">
         <v>1.50662e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-295.8559999999999</v>
+        <v>70.99099999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1.49432e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-252.701</v>
+        <v>68.19499999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.48639e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-224.205</v>
+        <v>64.32899999999995</v>
       </c>
       <c r="D8" t="n">
         <v>1.48072e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-199.7330000000001</v>
+        <v>63.42499999999995</v>
       </c>
       <c r="D9" t="n">
         <v>1.47724e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-184.455</v>
+        <v>59.10699999999997</v>
       </c>
       <c r="D10" t="n">
         <v>1.475e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-168.986</v>
+        <v>59.40999999999997</v>
       </c>
       <c r="D11" t="n">
         <v>1.47335e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-371.904</v>
+        <v>106.311</v>
       </c>
       <c r="D2" t="n">
         <v>1.51399e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-270.399</v>
+        <v>92.39400000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.49834e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-223.461</v>
+        <v>88.21699999999998</v>
       </c>
       <c r="D4" t="n">
         <v>1.48879e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-196.9239999999999</v>
+        <v>82.83100000000002</v>
       </c>
       <c r="D5" t="n">
         <v>1.48296e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-180.642</v>
+        <v>80.47500000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.47905e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-167.714</v>
+        <v>78.49499999999995</v>
       </c>
       <c r="D7" t="n">
         <v>1.47673e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-158.921</v>
+        <v>75.005</v>
       </c>
       <c r="D8" t="n">
         <v>1.47524e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-147.3020000000001</v>
+        <v>76.15599999999995</v>
       </c>
       <c r="D9" t="n">
         <v>1.47422e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-142.7090000000001</v>
+        <v>73.93399999999997</v>
       </c>
       <c r="D10" t="n">
         <v>1.47345e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-138.268</v>
+        <v>71.91399999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.47276e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-134.1199999999999</v>
+        <v>70.46300000000002</v>
       </c>
       <c r="D12" t="n">
         <v>1.47245e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-128.152</v>
+        <v>70.36800000000005</v>
       </c>
       <c r="D13" t="n">
         <v>1.47247e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-123.9520000000001</v>
+        <v>68.02999999999997</v>
       </c>
       <c r="D14" t="n">
         <v>1.47216e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-122.354</v>
+        <v>66.863</v>
       </c>
       <c r="D15" t="n">
         <v>1.47205e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-119.337</v>
+        <v>66.55400000000003</v>
       </c>
       <c r="D16" t="n">
         <v>1.47199e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-110.985</v>
+        <v>65.63</v>
       </c>
       <c r="D17" t="n">
         <v>1.47301e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-113.409</v>
+        <v>64.55500000000001</v>
       </c>
       <c r="D18" t="n">
         <v>1.47247e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-110.349</v>
+        <v>63.72699999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.47271e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-108.847</v>
+        <v>61.61199999999997</v>
       </c>
       <c r="D20" t="n">
         <v>1.47275e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-109.006</v>
+        <v>59.72899999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.47295e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-106.333</v>
+        <v>60.125</v>
       </c>
       <c r="D22" t="n">
         <v>1.47365e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-754.7139999999999</v>
+        <v>113.397</v>
       </c>
       <c r="D2" t="n">
         <v>1.55372e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-497.308</v>
+        <v>75.17099999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.54859e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-361.8100000000001</v>
+        <v>67.47399999999999</v>
       </c>
       <c r="D4" t="n">
         <v>1.53088e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-284.087</v>
+        <v>64.238</v>
       </c>
       <c r="D5" t="n">
         <v>1.51792e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-238.5700000000001</v>
+        <v>59.93599999999998</v>
       </c>
       <c r="D6" t="n">
         <v>1.50988e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-206.832</v>
+        <v>57.58200000000005</v>
       </c>
       <c r="D7" t="n">
         <v>1.50524e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-184.732</v>
+        <v>56.41200000000003</v>
       </c>
       <c r="D8" t="n">
         <v>1.50224e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-169.393</v>
+        <v>54.548</v>
       </c>
       <c r="D9" t="n">
         <v>1.50088e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-156.482</v>
+        <v>53.39799999999997</v>
       </c>
       <c r="D10" t="n">
         <v>1.50031e-07</v>
@@ -9538,7 +9538,7 @@
         <v>0.5394665844542564</v>
       </c>
       <c r="G10" t="n">
-        <v>1.35767389866034</v>
+        <v>1.357673898660345</v>
       </c>
       <c r="H10" t="n">
         <v>2.362572431479899</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-147.681</v>
+        <v>51.69199999999995</v>
       </c>
       <c r="D11" t="n">
         <v>1.50046e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>97.28100000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1182.815875092113</v>
+      </c>
       <c r="D2" t="n">
         <v>1.5369e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>92.44900000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>1183.687788971377</v>
+      </c>
       <c r="D3" t="n">
         <v>1.50123e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>87.62200000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>1126.59998817977</v>
+      </c>
       <c r="D4" t="n">
         <v>1.48329e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>88.428</v>
       </c>
+      <c r="C5" t="n">
+        <v>1623.163905601603</v>
+      </c>
       <c r="D5" t="n">
         <v>1.47135e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>84.20600000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>1527.306407542362</v>
+      </c>
       <c r="D6" t="n">
         <v>1.46258e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>78.577</v>
       </c>
+      <c r="C7" t="n">
+        <v>1246.977345804482</v>
+      </c>
       <c r="D7" t="n">
         <v>1.45626e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>76.40300000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>1232.626356900621</v>
+      </c>
       <c r="D8" t="n">
         <v>1.45096e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>73.80000000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1207.166595164718</v>
+      </c>
       <c r="D9" t="n">
         <v>1.44661e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>73.86100000000005</v>
       </c>
+      <c r="C10" t="n">
+        <v>1534.439850147957</v>
+      </c>
       <c r="D10" t="n">
         <v>1.44317e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>70.34899999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1396.056723622238</v>
       </c>
       <c r="D11" t="n">
         <v>1.43999e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>102.808</v>
       </c>
+      <c r="C2" t="n">
+        <v>1793.025355254218</v>
+      </c>
       <c r="D2" t="n">
         <v>1.52874e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>89.36900000000003</v>
       </c>
+      <c r="C3" t="n">
+        <v>1069.327671542842</v>
+      </c>
       <c r="D3" t="n">
         <v>1.51864e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>84.33500000000004</v>
       </c>
+      <c r="C4" t="n">
+        <v>958.8845416804633</v>
+      </c>
       <c r="D4" t="n">
         <v>1.51232e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>82.63200000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1094.889748475819</v>
+      </c>
       <c r="D5" t="n">
         <v>1.50798e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>80.65300000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>1170.807954243927</v>
+      </c>
       <c r="D6" t="n">
         <v>1.50537e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>76.928</v>
       </c>
+      <c r="C7" t="n">
+        <v>1020.437100054264</v>
+      </c>
       <c r="D7" t="n">
         <v>1.5037e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>76.46300000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>1210.629830277368</v>
+      </c>
       <c r="D8" t="n">
         <v>1.50231e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>74.18000000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1173.487346501315</v>
+      </c>
       <c r="D9" t="n">
         <v>1.50176e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>71.96299999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>1123.303945517593</v>
+      </c>
       <c r="D10" t="n">
         <v>1.50105e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>70.26400000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>1153.013060338801</v>
+      </c>
       <c r="D11" t="n">
         <v>1.50078e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>69.63499999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1207.041654912689</v>
+      </c>
       <c r="D12" t="n">
         <v>1.50054e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>69.911</v>
       </c>
+      <c r="C13" t="n">
+        <v>1388.279402647019</v>
+      </c>
       <c r="D13" t="n">
         <v>1.50039e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>66.96699999999998</v>
       </c>
+      <c r="C14" t="n">
+        <v>1252.453157749394</v>
+      </c>
       <c r="D14" t="n">
         <v>1.50045e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>66.23099999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>1349.108446338159</v>
+      </c>
       <c r="D15" t="n">
         <v>1.5005e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>63.53700000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>1268.853149487215</v>
+      </c>
       <c r="D16" t="n">
         <v>1.50046e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>63.39699999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>1346.831299232614</v>
+      </c>
       <c r="D17" t="n">
         <v>1.50041e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>63.50899999999996</v>
       </c>
+      <c r="C18" t="n">
+        <v>1600.93646038177</v>
+      </c>
       <c r="D18" t="n">
         <v>1.50048e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>61.73399999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>1485.740425045114</v>
+      </c>
       <c r="D19" t="n">
         <v>1.50077e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>59.654</v>
       </c>
+      <c r="C20" t="n">
+        <v>1431.458830118129</v>
+      </c>
       <c r="D20" t="n">
         <v>1.50097e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>60.66199999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1992.533416559046</v>
+      </c>
       <c r="D21" t="n">
         <v>1.50091e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>58.286</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1757.38057724114</v>
       </c>
       <c r="D22" t="n">
         <v>1.50118e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>111.569</v>
       </c>
+      <c r="C2" t="n">
+        <v>3013.756550655469</v>
+      </c>
       <c r="D2" t="n">
         <v>1.4458e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>92.62700000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>1234.445310653209</v>
+      </c>
       <c r="D3" t="n">
         <v>1.44701e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>84.10599999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>978.1209868676775</v>
+      </c>
       <c r="D4" t="n">
         <v>1.44392e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>85.24400000000003</v>
       </c>
+      <c r="C5" t="n">
+        <v>1194.520386178371</v>
+      </c>
       <c r="D5" t="n">
         <v>1.44064e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>81.00900000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1166.730238592301</v>
+      </c>
       <c r="D6" t="n">
         <v>1.438e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>79.471</v>
       </c>
+      <c r="C7" t="n">
+        <v>1172.534392992894</v>
+      </c>
       <c r="D7" t="n">
         <v>1.43573e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>76.327</v>
       </c>
+      <c r="C8" t="n">
+        <v>1082.287721820642</v>
+      </c>
       <c r="D8" t="n">
         <v>1.43369e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>74.90300000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1161.28601680131</v>
+      </c>
       <c r="D9" t="n">
         <v>1.43237e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>74.71899999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>1353.014285164601</v>
+      </c>
       <c r="D10" t="n">
         <v>1.43113e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>71.50599999999997</v>
       </c>
+      <c r="C11" t="n">
+        <v>1178.481354290112</v>
+      </c>
       <c r="D11" t="n">
         <v>1.43053e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>71.74599999999998</v>
       </c>
+      <c r="C12" t="n">
+        <v>1390.597268076718</v>
+      </c>
       <c r="D12" t="n">
         <v>1.42966e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>70.08499999999998</v>
       </c>
+      <c r="C13" t="n">
+        <v>1572.159808134865</v>
+      </c>
       <c r="D13" t="n">
         <v>1.42916e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>68.21199999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>1482.29771500875</v>
+      </c>
       <c r="D14" t="n">
         <v>1.42854e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>67.95099999999996</v>
       </c>
+      <c r="C15" t="n">
+        <v>1655.691842158782</v>
+      </c>
       <c r="D15" t="n">
         <v>1.42828e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>65.00800000000004</v>
       </c>
+      <c r="C16" t="n">
+        <v>1314.054666771343</v>
+      </c>
       <c r="D16" t="n">
         <v>1.42802e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>64.149</v>
       </c>
+      <c r="C17" t="n">
+        <v>1419.811765987608</v>
+      </c>
       <c r="D17" t="n">
         <v>1.42778e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>63.66700000000003</v>
       </c>
+      <c r="C18" t="n">
+        <v>1622.909256074026</v>
+      </c>
       <c r="D18" t="n">
         <v>1.42772e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>63.09300000000002</v>
       </c>
+      <c r="C19" t="n">
+        <v>1992.366956458803</v>
+      </c>
       <c r="D19" t="n">
         <v>1.42793e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>59.72399999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>1596.584745754216</v>
+      </c>
       <c r="D20" t="n">
         <v>1.42774e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>60.34000000000003</v>
       </c>
+      <c r="C21" t="n">
+        <v>1934.033896555276</v>
+      </c>
       <c r="D21" t="n">
         <v>1.42781e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>60.12399999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1887.938531451151</v>
       </c>
       <c r="D22" t="n">
         <v>1.42815e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>129.99</v>
       </c>
+      <c r="C2" t="n">
+        <v>2563.017114567224</v>
+      </c>
       <c r="D2" t="n">
         <v>1.44567e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>85.50400000000002</v>
       </c>
+      <c r="C3" t="n">
+        <v>1686.780194718028</v>
+      </c>
       <c r="D3" t="n">
         <v>1.46029e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>77.54300000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>1274.938749267051</v>
+      </c>
       <c r="D4" t="n">
         <v>1.45557e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>73.39400000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1250.97590615496</v>
+      </c>
       <c r="D5" t="n">
         <v>1.44921e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>71.78499999999997</v>
       </c>
+      <c r="C6" t="n">
+        <v>1434.182114950244</v>
+      </c>
       <c r="D6" t="n">
         <v>1.44382e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>69.63799999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>1533.992605317163</v>
+      </c>
       <c r="D7" t="n">
         <v>1.43966e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>67.887</v>
       </c>
+      <c r="C8" t="n">
+        <v>1686.213066771085</v>
+      </c>
       <c r="D8" t="n">
         <v>1.43633e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>63.94400000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1347.721802197299</v>
+      </c>
       <c r="D9" t="n">
         <v>1.43368e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>62.01099999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>1572.957364006709</v>
+      </c>
       <c r="D10" t="n">
         <v>1.43162e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>62.42699999999996</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2104.812518981881</v>
       </c>
       <c r="D11" t="n">
         <v>1.43006e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>106.705</v>
       </c>
+      <c r="C2" t="n">
+        <v>1912.440123799267</v>
+      </c>
       <c r="D2" t="n">
         <v>1.46314e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>89.92000000000002</v>
       </c>
+      <c r="C3" t="n">
+        <v>1072.656592759998</v>
+      </c>
       <c r="D3" t="n">
         <v>1.45624e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>86.75099999999998</v>
       </c>
+      <c r="C4" t="n">
+        <v>1111.732642602691</v>
+      </c>
       <c r="D4" t="n">
         <v>1.44916e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>83.63099999999997</v>
       </c>
+      <c r="C5" t="n">
+        <v>1074.396004727845</v>
+      </c>
       <c r="D5" t="n">
         <v>1.44353e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>81.73200000000003</v>
       </c>
+      <c r="C6" t="n">
+        <v>1128.47871941567</v>
+      </c>
       <c r="D6" t="n">
         <v>1.43943e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>79.34900000000005</v>
       </c>
+      <c r="C7" t="n">
+        <v>1150.54733993838</v>
+      </c>
       <c r="D7" t="n">
         <v>1.43615e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>77.149</v>
       </c>
+      <c r="C8" t="n">
+        <v>1158.92719714933</v>
+      </c>
       <c r="D8" t="n">
         <v>1.43417e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>73.39099999999996</v>
       </c>
+      <c r="C9" t="n">
+        <v>1031.967460006077</v>
+      </c>
       <c r="D9" t="n">
         <v>1.43228e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>72.53700000000003</v>
       </c>
+      <c r="C10" t="n">
+        <v>1281.376399019318</v>
+      </c>
       <c r="D10" t="n">
         <v>1.43116e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>72.33399999999995</v>
       </c>
+      <c r="C11" t="n">
+        <v>1318.332450563865</v>
+      </c>
       <c r="D11" t="n">
         <v>1.43021e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>71.02100000000002</v>
       </c>
+      <c r="C12" t="n">
+        <v>1351.941644547521</v>
+      </c>
       <c r="D12" t="n">
         <v>1.42966e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>68.92000000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>1235.682884738866</v>
+      </c>
       <c r="D13" t="n">
         <v>1.42903e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>68.77800000000002</v>
       </c>
+      <c r="C14" t="n">
+        <v>1510.266341076298</v>
+      </c>
       <c r="D14" t="n">
         <v>1.42868e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>66.82499999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>1381.326344395011</v>
+      </c>
       <c r="D15" t="n">
         <v>1.42845e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>64.565</v>
       </c>
+      <c r="C16" t="n">
+        <v>1186.073917725104</v>
+      </c>
       <c r="D16" t="n">
         <v>1.42846e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>64.21700000000004</v>
       </c>
+      <c r="C17" t="n">
+        <v>1440.609429724009</v>
+      </c>
       <c r="D17" t="n">
         <v>1.42851e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>64.08499999999998</v>
       </c>
+      <c r="C18" t="n">
+        <v>1463.289119790709</v>
+      </c>
       <c r="D18" t="n">
         <v>1.42865e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>62.55700000000002</v>
       </c>
+      <c r="C19" t="n">
+        <v>1476.006307885823</v>
+      </c>
       <c r="D19" t="n">
         <v>1.42879e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>60.09100000000001</v>
       </c>
+      <c r="C20" t="n">
+        <v>1439.359701410888</v>
+      </c>
       <c r="D20" t="n">
         <v>1.42897e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>59.94599999999997</v>
       </c>
+      <c r="C21" t="n">
+        <v>1446.46831149877</v>
+      </c>
       <c r="D21" t="n">
         <v>1.42901e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>58.75299999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1436.242120489184</v>
       </c>
       <c r="D22" t="n">
         <v>1.42914e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>137.544</v>
       </c>
+      <c r="C2" t="n">
+        <v>6196.275659093436</v>
+      </c>
       <c r="D2" t="n">
         <v>1.46552e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>90.36699999999996</v>
       </c>
+      <c r="C3" t="n">
+        <v>1866.291739245986</v>
+      </c>
       <c r="D3" t="n">
         <v>1.48235e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>79.47200000000004</v>
       </c>
+      <c r="C4" t="n">
+        <v>1202.216464266786</v>
+      </c>
       <c r="D4" t="n">
         <v>1.47334e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>76.82999999999998</v>
       </c>
+      <c r="C5" t="n">
+        <v>1343.575048013013</v>
+      </c>
       <c r="D5" t="n">
         <v>1.46346e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>74.733</v>
       </c>
+      <c r="C6" t="n">
+        <v>1705.901735662813</v>
+      </c>
       <c r="D6" t="n">
         <v>1.45553e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>71.06799999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>1588.283780575926</v>
+      </c>
       <c r="D7" t="n">
         <v>1.44965e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>68.54599999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1766.645389583148</v>
+      </c>
       <c r="D8" t="n">
         <v>1.44513e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>63.29699999999997</v>
       </c>
+      <c r="C9" t="n">
+        <v>1635.120217715056</v>
+      </c>
       <c r="D9" t="n">
         <v>1.44184e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>63.92100000000005</v>
       </c>
+      <c r="C10" t="n">
+        <v>2133.330735286719</v>
+      </c>
       <c r="D10" t="n">
         <v>1.43944e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>60.53500000000003</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1700.76733376636</v>
       </c>
       <c r="D11" t="n">
         <v>1.43775e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>108.15</v>
       </c>
+      <c r="C2" t="n">
+        <v>2258.879895137717</v>
+      </c>
       <c r="D2" t="n">
         <v>1.48966e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>93.166</v>
       </c>
+      <c r="C3" t="n">
+        <v>1241.443435871459</v>
+      </c>
       <c r="D3" t="n">
         <v>1.46983e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>84.99800000000005</v>
       </c>
+      <c r="C4" t="n">
+        <v>986.63837260576</v>
+      </c>
       <c r="D4" t="n">
         <v>1.45814e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>83.40699999999998</v>
       </c>
+      <c r="C5" t="n">
+        <v>1053.197389074623</v>
+      </c>
       <c r="D5" t="n">
         <v>1.4504e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>82.41899999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>1211.585327097715</v>
+      </c>
       <c r="D6" t="n">
         <v>1.44557e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>78.279</v>
       </c>
+      <c r="C7" t="n">
+        <v>1132.672564901439</v>
+      </c>
       <c r="D7" t="n">
         <v>1.44212e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>76.28500000000003</v>
       </c>
+      <c r="C8" t="n">
+        <v>1022.739285819663</v>
+      </c>
       <c r="D8" t="n">
         <v>1.43979e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>74.70000000000005</v>
       </c>
+      <c r="C9" t="n">
+        <v>1171.429291890032</v>
+      </c>
       <c r="D9" t="n">
         <v>1.43841e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>75.37799999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>1457.818187546433</v>
+      </c>
       <c r="D10" t="n">
         <v>1.43722e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>70.90499999999997</v>
       </c>
+      <c r="C11" t="n">
+        <v>1077.504582352377</v>
+      </c>
       <c r="D11" t="n">
         <v>1.43611e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>70.32599999999996</v>
       </c>
+      <c r="C12" t="n">
+        <v>1163.125282409601</v>
+      </c>
       <c r="D12" t="n">
         <v>1.43544e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>70.27800000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>1421.78058325568</v>
+      </c>
       <c r="D13" t="n">
         <v>1.4353e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>69.04499999999996</v>
       </c>
+      <c r="C14" t="n">
+        <v>1348.215302720382</v>
+      </c>
       <c r="D14" t="n">
         <v>1.43474e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>68.36199999999997</v>
       </c>
+      <c r="C15" t="n">
+        <v>1544.943801720935</v>
+      </c>
       <c r="D15" t="n">
         <v>1.43446e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>65.73099999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>1245.141743481329</v>
+      </c>
       <c r="D16" t="n">
         <v>1.43442e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>65.62799999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>1394.635750131411</v>
+      </c>
       <c r="D17" t="n">
         <v>1.43441e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>63.923</v>
       </c>
+      <c r="C18" t="n">
+        <v>1370.409014861883</v>
+      </c>
       <c r="D18" t="n">
         <v>1.43414e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>63.81099999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>1696.809645737938</v>
+      </c>
       <c r="D19" t="n">
         <v>1.43426e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>62.517</v>
       </c>
+      <c r="C20" t="n">
+        <v>1644.610581986179</v>
+      </c>
       <c r="D20" t="n">
         <v>1.43445e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>62.59499999999997</v>
       </c>
+      <c r="C21" t="n">
+        <v>2238.785887471848</v>
+      </c>
       <c r="D21" t="n">
         <v>1.43491e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>60.60300000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1795.178738016864</v>
       </c>
       <c r="D22" t="n">
         <v>1.43515e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>114.597</v>
       </c>
+      <c r="C2" t="n">
+        <v>7851.44006932193</v>
+      </c>
       <c r="D2" t="n">
         <v>1.57293e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>83.63999999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1640.783106316603</v>
+      </c>
       <c r="D3" t="n">
         <v>1.55133e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>75.69200000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>1297.601013059806</v>
+      </c>
       <c r="D4" t="n">
         <v>1.52503e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>71.43200000000002</v>
       </c>
+      <c r="C5" t="n">
+        <v>1223.373459542942</v>
+      </c>
       <c r="D5" t="n">
         <v>1.50662e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>70.99099999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1460.336227643573</v>
+      </c>
       <c r="D6" t="n">
         <v>1.49432e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>68.19499999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1513.261284732756</v>
+      </c>
       <c r="D7" t="n">
         <v>1.48639e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>64.32899999999995</v>
       </c>
+      <c r="C8" t="n">
+        <v>1517.801734646978</v>
+      </c>
       <c r="D8" t="n">
         <v>1.48072e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>63.42499999999995</v>
       </c>
+      <c r="C9" t="n">
+        <v>1683.585319279457</v>
+      </c>
       <c r="D9" t="n">
         <v>1.47724e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>59.10699999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>1485.112728811299</v>
+      </c>
       <c r="D10" t="n">
         <v>1.475e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>59.40999999999997</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2373.207616085963</v>
       </c>
       <c r="D11" t="n">
         <v>1.47335e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>106.311</v>
       </c>
+      <c r="C2" t="n">
+        <v>1986.697608512675</v>
+      </c>
       <c r="D2" t="n">
         <v>1.51399e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>92.39400000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>1261.935918753573</v>
+      </c>
       <c r="D3" t="n">
         <v>1.49834e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>88.21699999999998</v>
       </c>
+      <c r="C4" t="n">
+        <v>1243.681193186042</v>
+      </c>
       <c r="D4" t="n">
         <v>1.48879e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>82.83100000000002</v>
       </c>
+      <c r="C5" t="n">
+        <v>1112.651922379521</v>
+      </c>
       <c r="D5" t="n">
         <v>1.48296e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>80.47500000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>1114.874122009982</v>
+      </c>
       <c r="D6" t="n">
         <v>1.47905e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>78.49499999999995</v>
       </c>
+      <c r="C7" t="n">
+        <v>1130.617171314762</v>
+      </c>
       <c r="D7" t="n">
         <v>1.47673e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>75.005</v>
       </c>
+      <c r="C8" t="n">
+        <v>1024.990403963821</v>
+      </c>
       <c r="D8" t="n">
         <v>1.47524e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>76.15599999999995</v>
       </c>
+      <c r="C9" t="n">
+        <v>1284.08907373017</v>
+      </c>
       <c r="D9" t="n">
         <v>1.47422e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>73.93399999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>1275.257898688055</v>
+      </c>
       <c r="D10" t="n">
         <v>1.47345e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>71.91399999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>1162.291933687253</v>
+      </c>
       <c r="D11" t="n">
         <v>1.47276e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>70.46300000000002</v>
       </c>
+      <c r="C12" t="n">
+        <v>1169.320563564832</v>
+      </c>
       <c r="D12" t="n">
         <v>1.47245e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>70.36800000000005</v>
       </c>
+      <c r="C13" t="n">
+        <v>1427.236988758707</v>
+      </c>
       <c r="D13" t="n">
         <v>1.47247e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>68.02999999999997</v>
       </c>
+      <c r="C14" t="n">
+        <v>1265.329089740716</v>
+      </c>
       <c r="D14" t="n">
         <v>1.47216e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>66.863</v>
       </c>
+      <c r="C15" t="n">
+        <v>1167.259727584692</v>
+      </c>
       <c r="D15" t="n">
         <v>1.47205e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>66.55400000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>1429.507106971718</v>
+      </c>
       <c r="D16" t="n">
         <v>1.47199e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>65.63</v>
       </c>
+      <c r="C17" t="n">
+        <v>1526.593468358828</v>
+      </c>
       <c r="D17" t="n">
         <v>1.47301e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>64.55500000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>1482.531756366998</v>
+      </c>
       <c r="D18" t="n">
         <v>1.47247e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>63.72699999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>1494.797082905342</v>
+      </c>
       <c r="D19" t="n">
         <v>1.47271e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>61.61199999999997</v>
       </c>
+      <c r="C20" t="n">
+        <v>1429.208141110233</v>
+      </c>
       <c r="D20" t="n">
         <v>1.47275e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>59.72899999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1256.476028884376</v>
+      </c>
       <c r="D21" t="n">
         <v>1.47295e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>60.125</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1687.030197632929</v>
       </c>
       <c r="D22" t="n">
         <v>1.47365e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>113.397</v>
       </c>
+      <c r="C2" t="n">
+        <v>1916.963163801467</v>
+      </c>
       <c r="D2" t="n">
         <v>1.55372e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>75.17099999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>3051.339869599293</v>
+      </c>
       <c r="D3" t="n">
         <v>1.54859e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>67.47399999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>2113.865636293965</v>
+      </c>
       <c r="D4" t="n">
         <v>1.53088e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>64.238</v>
       </c>
+      <c r="C5" t="n">
+        <v>2252.779004659418</v>
+      </c>
       <c r="D5" t="n">
         <v>1.51792e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>59.93599999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>1612.655629040645</v>
+      </c>
       <c r="D6" t="n">
         <v>1.50988e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>57.58200000000005</v>
       </c>
+      <c r="C7" t="n">
+        <v>1774.678971240392</v>
+      </c>
       <c r="D7" t="n">
         <v>1.50524e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>56.41200000000003</v>
       </c>
+      <c r="C8" t="n">
+        <v>2253.832274003391</v>
+      </c>
       <c r="D8" t="n">
         <v>1.50224e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>54.548</v>
       </c>
+      <c r="C9" t="n">
+        <v>3882.088128335772</v>
+      </c>
       <c r="D9" t="n">
         <v>1.50088e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>53.39799999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>4170.860138173474</v>
+      </c>
       <c r="D10" t="n">
         <v>1.50031e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>51.69199999999995</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6008.259011873782</v>
       </c>
       <c r="D11" t="n">
         <v>1.50046e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -565,7 +565,7 @@
         <v>97.28100000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1182.815875092113</v>
+        <v>283.3103348079002</v>
       </c>
       <c r="D2" t="n">
         <v>1.5369e-07</v>
@@ -598,16 +598,13 @@
         <v>-8204.891919915419</v>
       </c>
       <c r="Y2" t="n">
-        <v>445.0244163987439</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>486964752.1258806</v>
+        <v>212.5376937606694</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.228960720397941e-07</v>
+        <v>2.196326579475475e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9431952925240271</v>
+        <v>0.9982953489971578</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>92.44900000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>1183.687788971377</v>
+        <v>327.1735300719598</v>
       </c>
       <c r="D3" t="n">
         <v>1.50123e-07</v>
@@ -651,16 +648,13 @@
         <v>-10274.91400160013</v>
       </c>
       <c r="Y3" t="n">
-        <v>438.7994999563107</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>239988503.5616964</v>
+        <v>157.1277484218515</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03784965291014e-07</v>
+        <v>1.671042003626162e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9531298208429709</v>
+        <v>0.9994527181932028</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>87.62200000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1126.59998817977</v>
+        <v>341.0849830910215</v>
       </c>
       <c r="D4" t="n">
         <v>1.48329e-07</v>
@@ -704,10 +698,7 @@
         <v>-11761.52385783254</v>
       </c>
       <c r="Y4" t="n">
-        <v>432.8256052678489</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1063254965.513357</v>
+        <v>540.3272632022615</v>
       </c>
       <c r="AA4" t="n">
         <v>1.938977506697763e-07</v>
@@ -724,7 +715,7 @@
         <v>88.428</v>
       </c>
       <c r="C5" t="n">
-        <v>1623.163905601603</v>
+        <v>303.8111877194315</v>
       </c>
       <c r="D5" t="n">
         <v>1.47135e-07</v>
@@ -757,16 +748,13 @@
         <v>-13739.04637824691</v>
       </c>
       <c r="Y5" t="n">
-        <v>411.3187824562365</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3501.376424990312</v>
+        <v>170.1077779460336</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.630400549407319e-06</v>
+        <v>1.902290096057767e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7387540163156397</v>
+        <v>0.999104330417934</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>84.20600000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>1527.306407542362</v>
+        <v>315.8458042441073</v>
       </c>
       <c r="D6" t="n">
         <v>1.46258e-07</v>
@@ -810,16 +798,13 @@
         <v>-14992.52478000839</v>
       </c>
       <c r="Y6" t="n">
-        <v>421.866699372222</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>115146782.9545396</v>
+        <v>154.1037054379253</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.824509949546205e-07</v>
+        <v>1.815953656076665e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9658957504319755</v>
+        <v>0.9995721699112194</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>78.577</v>
       </c>
       <c r="C7" t="n">
-        <v>1246.977345804482</v>
+        <v>265.5081306421471</v>
       </c>
       <c r="D7" t="n">
         <v>1.45626e-07</v>
@@ -863,16 +848,13 @@
         <v>-16004.11879585791</v>
       </c>
       <c r="Y7" t="n">
-        <v>413.3690171197563</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6447.618479083058</v>
+        <v>201.4352652547699</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.370851338602851e-07</v>
+        <v>2.440057999867442e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9632196828583551</v>
+        <v>0.9990746625798433</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>76.40300000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>1232.626356900621</v>
+        <v>264.9243434706683</v>
       </c>
       <c r="D8" t="n">
         <v>1.45096e-07</v>
@@ -916,16 +898,13 @@
         <v>-17093.42473464095</v>
       </c>
       <c r="Y8" t="n">
-        <v>412.9992153348903</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>450261770.4522188</v>
+        <v>196.2806475636547</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.756077495807179e-07</v>
+        <v>2.390386500916465e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9704915414757052</v>
+        <v>0.9993780192629763</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>73.80000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1207.166595164718</v>
+        <v>305.0517612286749</v>
       </c>
       <c r="D9" t="n">
         <v>1.44661e-07</v>
@@ -969,16 +948,13 @@
         <v>-18100.59079228311</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.4850624089426</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3348.871187404912</v>
+        <v>149.6577730926533</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.088510335412902e-06</v>
+        <v>1.839224918288388e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7118209399384114</v>
+        <v>0.9999355477542364</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>73.86100000000005</v>
       </c>
       <c r="C10" t="n">
-        <v>1534.439850147957</v>
+        <v>288.9241535643721</v>
       </c>
       <c r="D10" t="n">
         <v>1.44317e-07</v>
@@ -1022,16 +998,13 @@
         <v>-20143.10255451971</v>
       </c>
       <c r="Y10" t="n">
-        <v>406.4658718266165</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5421.831715459281</v>
+        <v>169.2679054610318</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.027691994699986e-07</v>
+        <v>2.154930817398146e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8544745903309675</v>
+        <v>0.9999451433867904</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>70.34899999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1396.056723622238</v>
+        <v>285.1555891610266</v>
       </c>
       <c r="D11" t="n">
         <v>1.43999e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-20407.89935235872</v>
       </c>
       <c r="Y11" t="n">
-        <v>392.7309796848951</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3292.823352096475</v>
+        <v>166.0526291732602</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.521469716471364e-06</v>
+        <v>2.162356193760762e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6877219055020486</v>
+        <v>0.9993911230584693</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>102.808</v>
       </c>
       <c r="C2" t="n">
-        <v>1793.025355254218</v>
+        <v>302.0808069289747</v>
       </c>
       <c r="D2" t="n">
         <v>1.52874e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-16105.91496641924</v>
       </c>
       <c r="Y2" t="n">
-        <v>419.2326892825938</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7283.020815301395</v>
+        <v>185.7148149929809</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.208497343607827e-07</v>
+        <v>1.940925286281776e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8723576743306077</v>
+        <v>0.9982916922972535</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>89.36900000000003</v>
       </c>
       <c r="C3" t="n">
-        <v>1069.327671542842</v>
+        <v>89.36900000000003</v>
       </c>
       <c r="D3" t="n">
         <v>1.51864e-07</v>
@@ -1326,11 +1293,10 @@
       <c r="X3" t="n">
         <v>-18438.47981940698</v>
       </c>
-      <c r="Y3" t="n">
-        <v>415.8312423507439</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3537.425526003954</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.058952545786878e-06</v>
@@ -1347,7 +1313,7 @@
         <v>84.33500000000004</v>
       </c>
       <c r="C4" t="n">
-        <v>958.8845416804633</v>
+        <v>282.8867625922326</v>
       </c>
       <c r="D4" t="n">
         <v>1.51232e-07</v>
@@ -1380,16 +1346,13 @@
         <v>-19638.79252253433</v>
       </c>
       <c r="Y4" t="n">
-        <v>426.9358447869628</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>174689281.998233</v>
+        <v>198.2669212976955</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.81308952672996e-07</v>
+        <v>2.681377745920006e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9718976251082175</v>
+        <v>0.987542643019433</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1363,7 @@
         <v>82.63200000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1094.889748475819</v>
+        <v>262.3742070832591</v>
       </c>
       <c r="D5" t="n">
         <v>1.50798e-07</v>
@@ -1433,16 +1396,13 @@
         <v>-21341.5930482217</v>
       </c>
       <c r="Y5" t="n">
-        <v>407.5001834965634</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3459.085167738524</v>
+        <v>209.844562498416</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.970744449809594e-06</v>
+        <v>2.499187417156764e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7772845170568609</v>
+        <v>0.998707139828021</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1413,7 @@
         <v>80.65300000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>1170.807954243927</v>
+        <v>360.7041820009157</v>
       </c>
       <c r="D6" t="n">
         <v>1.50537e-07</v>
@@ -1486,16 +1446,13 @@
         <v>-22379.84733407621</v>
       </c>
       <c r="Y6" t="n">
-        <v>416.2955460959788</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5373.300659411513</v>
+        <v>99.66626169458365</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.886465498890387e-07</v>
+        <v>1.420834044135358e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8853846798524502</v>
+        <v>0.999438773684526</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1463,7 @@
         <v>76.928</v>
       </c>
       <c r="C7" t="n">
-        <v>1020.437100054264</v>
+        <v>254.243844401594</v>
       </c>
       <c r="D7" t="n">
         <v>1.5037e-07</v>
@@ -1539,16 +1496,13 @@
         <v>-21849.67980895728</v>
       </c>
       <c r="Y7" t="n">
-        <v>413.4572111420966</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6825.418772768077</v>
+        <v>210.6077219947007</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.361469973584559e-07</v>
+        <v>2.75661414324168e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.877804163304986</v>
+        <v>0.9965592843310509</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1513,7 @@
         <v>76.46300000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>1210.629830277368</v>
+        <v>76.46300000000002</v>
       </c>
       <c r="D8" t="n">
         <v>1.50231e-07</v>
@@ -1591,11 +1545,10 @@
       <c r="X8" t="n">
         <v>-23681.33456379035</v>
       </c>
-      <c r="Y8" t="n">
-        <v>398.6739443155888</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3354.608012709333</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>4.236408422876814e-06</v>
@@ -1612,7 +1565,7 @@
         <v>74.18000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1173.487346501315</v>
+        <v>248.3060747169789</v>
       </c>
       <c r="D9" t="n">
         <v>1.50176e-07</v>
@@ -1645,16 +1598,13 @@
         <v>-23736.44190164505</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.0362382921331</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3322.582231403105</v>
+        <v>207.1137547001761</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.439434287426658e-06</v>
+        <v>2.654276268790771e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6700199123941255</v>
+        <v>0.9996948349284364</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1615,7 @@
         <v>71.96299999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>1123.303945517593</v>
+        <v>247.8692580407463</v>
       </c>
       <c r="D10" t="n">
         <v>1.50105e-07</v>
@@ -1698,16 +1648,13 @@
         <v>-23408.91966239561</v>
       </c>
       <c r="Y10" t="n">
-        <v>393.4370342247838</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3294.122405107289</v>
+        <v>209.0649379250879</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.849900843905989e-06</v>
+        <v>2.83026466901215e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6845499496079346</v>
+        <v>0.9997528844243019</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1665,7 @@
         <v>70.26400000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1153.013060338801</v>
+        <v>70.26400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>1.50078e-07</v>
@@ -1750,11 +1697,10 @@
       <c r="X11" t="n">
         <v>-23837.61526272434</v>
       </c>
-      <c r="Y11" t="n">
-        <v>391.0632391930403</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3264.069938753463</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>5.724265934223685e-06</v>
@@ -1771,7 +1717,7 @@
         <v>69.63499999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1207.041654912689</v>
+        <v>355.19686296422</v>
       </c>
       <c r="D12" t="n">
         <v>1.50054e-07</v>
@@ -1804,16 +1750,13 @@
         <v>-24053.49785526302</v>
       </c>
       <c r="Y12" t="n">
-        <v>394.0977679144297</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6519.887508174598</v>
+        <v>80.65462608721339</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.549030011595242e-07</v>
+        <v>1.390117113637715e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.835028137467054</v>
+        <v>0.9999095533534819</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1767,7 @@
         <v>69.911</v>
       </c>
       <c r="C13" t="n">
-        <v>1388.279402647019</v>
+        <v>237.0559286062417</v>
       </c>
       <c r="D13" t="n">
         <v>1.50039e-07</v>
@@ -1857,16 +1800,13 @@
         <v>-26034.30608589084</v>
       </c>
       <c r="Y13" t="n">
-        <v>392.8430672948829</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>855128219.2084062</v>
+        <v>200.8629523066157</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.712016493363925e-07</v>
+        <v>2.710467316230492e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.979474372054447</v>
+        <v>0.9987103315910405</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1817,7 @@
         <v>66.96699999999998</v>
       </c>
       <c r="C14" t="n">
-        <v>1252.453157749394</v>
+        <v>234.5000593863414</v>
       </c>
       <c r="D14" t="n">
         <v>1.50045e-07</v>
@@ -1910,16 +1850,13 @@
         <v>-23863.41449898794</v>
       </c>
       <c r="Y14" t="n">
-        <v>389.695358208202</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>321334355.8278245</v>
+        <v>202.1894667159897</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.708134112227292e-07</v>
+        <v>2.848981238297262e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9798302819661022</v>
+        <v>0.9981758816939407</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1867,7 @@
         <v>66.23099999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>1349.108446338159</v>
+        <v>234.7138962583606</v>
       </c>
       <c r="D15" t="n">
         <v>1.5005e-07</v>
@@ -1963,16 +1900,13 @@
         <v>-24961.21932336222</v>
       </c>
       <c r="Y15" t="n">
-        <v>386.6341236401993</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>105628032.5617058</v>
+        <v>210.1553197391842</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.702302874103545e-07</v>
+        <v>3.616931627405246e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9803626081801807</v>
+        <v>0.9900758583921691</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1917,7 @@
         <v>63.53700000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>1268.853149487215</v>
+        <v>231.9173994198526</v>
       </c>
       <c r="D16" t="n">
         <v>1.50046e-07</v>
@@ -2016,16 +1950,13 @@
         <v>-23863.70018466999</v>
       </c>
       <c r="Y16" t="n">
-        <v>383.5601705167197</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>209024500.0176502</v>
+        <v>198.8914687692244</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.698854366435733e-07</v>
+        <v>2.930079833374285e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9806699975155032</v>
+        <v>0.9987675859404354</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1967,7 @@
         <v>63.39699999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>1346.831299232614</v>
+        <v>63.39699999999999</v>
       </c>
       <c r="D17" t="n">
         <v>1.50041e-07</v>
@@ -2068,11 +1999,10 @@
       <c r="X17" t="n">
         <v>-24377.9248764107</v>
       </c>
-      <c r="Y17" t="n">
-        <v>380.5290257264724</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>207300632.6712884</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.695154011482158e-07</v>
@@ -2089,7 +2019,7 @@
         <v>63.50899999999996</v>
       </c>
       <c r="C18" t="n">
-        <v>1600.93646038177</v>
+        <v>227.6343841834354</v>
       </c>
       <c r="D18" t="n">
         <v>1.50048e-07</v>
@@ -2122,16 +2052,13 @@
         <v>-26268.55606877112</v>
       </c>
       <c r="Y18" t="n">
-        <v>377.5196203385924</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>117820159.098676</v>
+        <v>200.296845388964</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.692053420978269e-07</v>
+        <v>2.973865275378797e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9812947421950817</v>
+        <v>0.9998776576760682</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2069,7 @@
         <v>61.73399999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>1485.740425045114</v>
+        <v>61.73399999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.50077e-07</v>
@@ -2174,11 +2101,10 @@
       <c r="X19" t="n">
         <v>-25535.82191588283</v>
       </c>
-      <c r="Y19" t="n">
-        <v>374.4969979867185</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>156466484.3031162</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>1.687436587151995e-07</v>
@@ -2195,7 +2121,7 @@
         <v>59.654</v>
       </c>
       <c r="C20" t="n">
-        <v>1431.458830118129</v>
+        <v>59.654</v>
       </c>
       <c r="D20" t="n">
         <v>1.50097e-07</v>
@@ -2227,11 +2153,10 @@
       <c r="X20" t="n">
         <v>-24340.3247656731</v>
       </c>
-      <c r="Y20" t="n">
-        <v>371.4986777876879</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>222024150.6506714</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>1.68509893582668e-07</v>
@@ -2248,7 +2173,7 @@
         <v>60.66199999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1992.533416559046</v>
+        <v>60.66199999999998</v>
       </c>
       <c r="D21" t="n">
         <v>1.50091e-07</v>
@@ -2280,11 +2205,10 @@
       <c r="X21" t="n">
         <v>-26900.50165895274</v>
       </c>
-      <c r="Y21" t="n">
-        <v>368.4761277387811</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>327113719.9689867</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1.680504414924477e-07</v>
@@ -2301,7 +2225,7 @@
         <v>58.286</v>
       </c>
       <c r="C22" t="n">
-        <v>1757.38057724114</v>
+        <v>58.286</v>
       </c>
       <c r="D22" t="n">
         <v>1.50118e-07</v>
@@ -2333,11 +2257,10 @@
       <c r="X22" t="n">
         <v>-25303.80680019316</v>
       </c>
-      <c r="Y22" t="n">
-        <v>365.4780612686336</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>298274177.4419369</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>1.67870213672396e-07</v>
@@ -2500,7 +2423,7 @@
         <v>111.569</v>
       </c>
       <c r="C2" t="n">
-        <v>3013.756550655469</v>
+        <v>310.0888555458832</v>
       </c>
       <c r="D2" t="n">
         <v>1.4458e-07</v>
@@ -2533,16 +2456,13 @@
         <v>-16088.81420677342</v>
       </c>
       <c r="Y2" t="n">
-        <v>450.4684834829814</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>28832820.6289399</v>
+        <v>185.7949663973179</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.837048170211643e-07</v>
+        <v>1.795939960486342e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9630781018369076</v>
+        <v>0.9995920556496446</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2473,7 @@
         <v>92.62700000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>1234.445310653209</v>
+        <v>310.8722716663597</v>
       </c>
       <c r="D3" t="n">
         <v>1.44701e-07</v>
@@ -2586,16 +2506,13 @@
         <v>-17721.49634677437</v>
       </c>
       <c r="Y3" t="n">
-        <v>436.945861412715</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>238201488.2065381</v>
+        <v>174.9898242530357</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.782556758605042e-07</v>
+        <v>1.91025757128371e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9677668587007904</v>
+        <v>0.9991508247994448</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2523,7 @@
         <v>84.10599999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>978.1209868676775</v>
+        <v>315.6327239240202</v>
       </c>
       <c r="D4" t="n">
         <v>1.44392e-07</v>
@@ -2639,16 +2556,13 @@
         <v>-18470.5222536253</v>
       </c>
       <c r="Y4" t="n">
-        <v>414.3112736839394</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3534.597164143562</v>
+        <v>163.3215712579876</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.562502442294363e-06</v>
+        <v>1.836786490894029e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.744252698759901</v>
+        <v>0.9992115828990913</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2573,7 @@
         <v>85.24400000000003</v>
       </c>
       <c r="C5" t="n">
-        <v>1194.520386178371</v>
+        <v>268.5184121724552</v>
       </c>
       <c r="D5" t="n">
         <v>1.44064e-07</v>
@@ -2692,16 +2606,13 @@
         <v>-21133.16091644632</v>
       </c>
       <c r="Y5" t="n">
-        <v>427.0585486463653</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>175095748.6313168</v>
+        <v>202.2936381397998</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.723974774484817e-07</v>
+        <v>2.21588803595584e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9721783028520264</v>
+        <v>0.9994132774630979</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2623,7 @@
         <v>81.00900000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1166.730238592301</v>
+        <v>81.00900000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.438e-07</v>
@@ -2744,11 +2655,10 @@
       <c r="X6" t="n">
         <v>-21547.56147767845</v>
       </c>
-      <c r="Y6" t="n">
-        <v>422.7493752504539</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>115613851.7829081</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.702798754841155e-07</v>
@@ -2765,7 +2675,7 @@
         <v>79.471</v>
       </c>
       <c r="C7" t="n">
-        <v>1172.534392992894</v>
+        <v>269.0271761684735</v>
       </c>
       <c r="D7" t="n">
         <v>1.43573e-07</v>
@@ -2798,16 +2708,13 @@
         <v>-22702.57419919123</v>
       </c>
       <c r="Y7" t="n">
-        <v>418.6153878666947</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>114297912.4161528</v>
+        <v>195.5602495041686</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.686923980205979e-07</v>
+        <v>2.22115860339817e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9749735352325676</v>
+        <v>0.9998656692785385</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2725,7 @@
         <v>76.327</v>
       </c>
       <c r="C8" t="n">
-        <v>1082.287721820642</v>
+        <v>259.2807418031464</v>
       </c>
       <c r="D8" t="n">
         <v>1.43369e-07</v>
@@ -2851,16 +2758,13 @@
         <v>-23160.91605284272</v>
       </c>
       <c r="Y8" t="n">
-        <v>414.8066137859243</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>113911701.4805088</v>
+        <v>201.8127652165605</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.671914608872588e-07</v>
+        <v>2.420385874137379e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9761205730851896</v>
+        <v>0.9986285993514818</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2775,7 @@
         <v>74.90300000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1161.28601680131</v>
+        <v>74.90300000000002</v>
       </c>
       <c r="D9" t="n">
         <v>1.43237e-07</v>
@@ -2903,11 +2807,10 @@
       <c r="X9" t="n">
         <v>-24186.02289824299</v>
       </c>
-      <c r="Y9" t="n">
-        <v>411.1964330576128</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>112476134.3346335</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.660903334854821e-07</v>
@@ -2924,7 +2827,7 @@
         <v>74.71899999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>1353.014285164601</v>
+        <v>251.0527976284598</v>
       </c>
       <c r="D10" t="n">
         <v>1.43113e-07</v>
@@ -2957,16 +2860,13 @@
         <v>-26103.31153531824</v>
       </c>
       <c r="Y10" t="n">
-        <v>397.6480759034161</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3337.356367973481</v>
+        <v>203.5944863506237</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.398185265419246e-06</v>
+        <v>2.493936170793275e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6659332817379022</v>
+        <v>0.9997670932683376</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2877,7 @@
         <v>71.50599999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>1178.481354290112</v>
+        <v>71.50599999999997</v>
       </c>
       <c r="D11" t="n">
         <v>1.43053e-07</v>
@@ -3009,11 +2909,10 @@
       <c r="X11" t="n">
         <v>-25393.93913333458</v>
       </c>
-      <c r="Y11" t="n">
-        <v>395.385174804119</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3309.521757091255</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.86398736120781e-06</v>
@@ -3030,7 +2929,7 @@
         <v>71.74599999999998</v>
       </c>
       <c r="C12" t="n">
-        <v>1390.597268076718</v>
+        <v>248.4481792839254</v>
       </c>
       <c r="D12" t="n">
         <v>1.42966e-07</v>
@@ -3063,16 +2962,13 @@
         <v>-27463.06474505195</v>
       </c>
       <c r="Y12" t="n">
-        <v>393.1439615832914</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3282.148245631112</v>
+        <v>202.8001575796897</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.640301048061864e-06</v>
+        <v>2.775777760675794e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.6630492364665539</v>
+        <v>0.9979717856154389</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2979,7 @@
         <v>70.08499999999998</v>
       </c>
       <c r="C13" t="n">
-        <v>1572.159808134865</v>
+        <v>250.6382087094215</v>
       </c>
       <c r="D13" t="n">
         <v>1.42916e-07</v>
@@ -3116,16 +3012,13 @@
         <v>-28329.992125253</v>
       </c>
       <c r="Y13" t="n">
-        <v>390.838525250868</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3257.801580590356</v>
+        <v>197.5407477945222</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.755749929442009e-06</v>
+        <v>2.655353461958467e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.6304905883100571</v>
+        <v>0.9994014319779001</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3029,7 @@
         <v>68.21199999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>1482.29771500875</v>
+        <v>242.9201288982287</v>
       </c>
       <c r="D14" t="n">
         <v>1.42854e-07</v>
@@ -3169,16 +3062,13 @@
         <v>-27727.52163474765</v>
       </c>
       <c r="Y14" t="n">
-        <v>388.5851151114368</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3231.417363139588</v>
+        <v>224.5850668231283</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.634747470496693e-06</v>
+        <v>6.274830042532587e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.63465178739948</v>
+        <v>0.9545410082855696</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3079,7 @@
         <v>67.95099999999996</v>
       </c>
       <c r="C15" t="n">
-        <v>1655.691842158782</v>
+        <v>240.1611754074034</v>
       </c>
       <c r="D15" t="n">
         <v>1.42828e-07</v>
@@ -3222,16 +3112,13 @@
         <v>-29245.62761920104</v>
       </c>
       <c r="Y15" t="n">
-        <v>391.327822567147</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5236.532117874331</v>
+        <v>204.9182044822032</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.643917021953699e-07</v>
+        <v>2.837849329653783e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9352514479345544</v>
+        <v>0.9998996563786251</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3129,7 @@
         <v>65.00800000000004</v>
       </c>
       <c r="C16" t="n">
-        <v>1314.054666771343</v>
+        <v>65.00800000000004</v>
       </c>
       <c r="D16" t="n">
         <v>1.42802e-07</v>
@@ -3274,11 +3161,10 @@
       <c r="X16" t="n">
         <v>-27662.5367367368</v>
       </c>
-      <c r="Y16" t="n">
-        <v>388.7695746202324</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>317453227.8957834</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>1.609519091912995e-07</v>
@@ -3295,7 +3181,7 @@
         <v>64.149</v>
       </c>
       <c r="C17" t="n">
-        <v>1419.811765987608</v>
+        <v>234.3145421561315</v>
       </c>
       <c r="D17" t="n">
         <v>1.42778e-07</v>
@@ -3328,16 +3214,13 @@
         <v>-28123.08245496312</v>
       </c>
       <c r="Y17" t="n">
-        <v>385.7283556142595</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>108447564.1346637</v>
+        <v>205.0780738453774</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.603503911150147e-07</v>
+        <v>2.956790757059985e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9818962755714378</v>
+        <v>0.9998302965306569</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3231,7 @@
         <v>63.66700000000003</v>
       </c>
       <c r="C18" t="n">
-        <v>1622.909256074026</v>
+        <v>63.66700000000003</v>
       </c>
       <c r="D18" t="n">
         <v>1.42772e-07</v>
@@ -3380,11 +3263,10 @@
       <c r="X18" t="n">
         <v>-29665.81517515678</v>
       </c>
-      <c r="Y18" t="n">
-        <v>382.7288031680701</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>313217643.6100243</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.598774880315277e-07</v>
@@ -3401,7 +3283,7 @@
         <v>63.09300000000002</v>
       </c>
       <c r="C19" t="n">
-        <v>1992.366956458803</v>
+        <v>202.6409849358399</v>
       </c>
       <c r="D19" t="n">
         <v>1.42793e-07</v>
@@ -3434,16 +3316,13 @@
         <v>-30852.6232540144</v>
       </c>
       <c r="Y19" t="n">
-        <v>379.7377611207317</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>413092949.4906744</v>
+        <v>230.8063187801345</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.594107282117107e-07</v>
+        <v>3.635483051003357e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9828120929642581</v>
+        <v>0.9999503057725476</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3333,7 @@
         <v>59.72399999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>1596.584745754216</v>
+        <v>59.72399999999999</v>
       </c>
       <c r="D20" t="n">
         <v>1.42774e-07</v>
@@ -3486,11 +3365,10 @@
       <c r="X20" t="n">
         <v>-27211.05566833534</v>
       </c>
-      <c r="Y20" t="n">
-        <v>376.8309540999307</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1024963641.172531</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>1.590356800892361e-07</v>
@@ -3507,7 +3385,7 @@
         <v>60.34000000000003</v>
       </c>
       <c r="C21" t="n">
-        <v>1934.033896555276</v>
+        <v>193.1942752392436</v>
       </c>
       <c r="D21" t="n">
         <v>1.42781e-07</v>
@@ -3540,16 +3418,13 @@
         <v>-30491.36332095984</v>
       </c>
       <c r="Y21" t="n">
-        <v>373.9924789566734</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1219714497.02813</v>
+        <v>231.709686596693</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.587205510494637e-07</v>
+        <v>3.878995616051365e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9834744355635867</v>
+        <v>0.9996370042721919</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3435,7 @@
         <v>60.12399999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>1887.938531451151</v>
+        <v>187.5113027491251</v>
       </c>
       <c r="D22" t="n">
         <v>1.42815e-07</v>
@@ -3593,16 +3468,13 @@
         <v>-31030.1220791261</v>
       </c>
       <c r="Y22" t="n">
-        <v>371.1337623225913</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>202846650.1296242</v>
+        <v>233.7932939942067</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.583705252172225e-07</v>
+        <v>3.90770989591692e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9838515278440514</v>
+        <v>0.9999544805896312</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3631,7 @@
         <v>129.99</v>
       </c>
       <c r="C2" t="n">
-        <v>2563.017114567224</v>
+        <v>129.99</v>
       </c>
       <c r="D2" t="n">
         <v>1.44567e-07</v>
@@ -3791,11 +3663,10 @@
       <c r="X2" t="n">
         <v>-10804.47260449541</v>
       </c>
-      <c r="Y2" t="n">
-        <v>454.5794073840062</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>736737071.9532801</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.003872975957584e-07</v>
@@ -3812,7 +3683,7 @@
         <v>85.50400000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>1686.780194718028</v>
+        <v>323.3622188285124</v>
       </c>
       <c r="D3" t="n">
         <v>1.46029e-07</v>
@@ -3845,16 +3716,13 @@
         <v>-11630.28770275351</v>
       </c>
       <c r="Y3" t="n">
-        <v>408.9207503450474</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3489.288174957848</v>
+        <v>147.5056133252461</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.324373287264978e-06</v>
+        <v>1.642945248370354e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.728300516904037</v>
+        <v>0.9997883603506084</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3733,7 @@
         <v>77.54300000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1274.938749267051</v>
+        <v>300.2336642437897</v>
       </c>
       <c r="D4" t="n">
         <v>1.45557e-07</v>
@@ -3898,16 +3766,13 @@
         <v>-13296.59635142475</v>
       </c>
       <c r="Y4" t="n">
-        <v>417.4499877467158</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>966855033.5855224</v>
+        <v>165.5217311956595</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.828363463551726e-07</v>
+        <v>1.973322362407135e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9648940954335234</v>
+        <v>0.9987568830356022</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3783,7 @@
         <v>73.39400000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1250.97590615496</v>
+        <v>227.4148239989399</v>
       </c>
       <c r="D5" t="n">
         <v>1.44921e-07</v>
@@ -3951,16 +3816,13 @@
         <v>-14939.02966586925</v>
       </c>
       <c r="Y5" t="n">
-        <v>411.9548059643218</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>112876492.8521605</v>
+        <v>240.9143653052786</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.778603561807484e-07</v>
+        <v>3.250445342716278e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9684066534420489</v>
+        <v>0.9974711727769503</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3833,7 @@
         <v>71.78499999999997</v>
       </c>
       <c r="C6" t="n">
-        <v>1434.182114950244</v>
+        <v>226.6298459381427</v>
       </c>
       <c r="D6" t="n">
         <v>1.44382e-07</v>
@@ -4004,16 +3866,13 @@
         <v>-16558.87633341621</v>
       </c>
       <c r="Y6" t="n">
-        <v>396.160984841526</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3331.650565335081</v>
+        <v>231.0936176368125</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.884789522626573e-06</v>
+        <v>3.139242071615511e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6771610163355278</v>
+        <v>0.9955605933966244</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3883,7 @@
         <v>69.63799999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>1533.992605317163</v>
+        <v>237.3418652632969</v>
       </c>
       <c r="D7" t="n">
         <v>1.43966e-07</v>
@@ -4057,16 +3916,13 @@
         <v>-17995.61827354145</v>
       </c>
       <c r="Y7" t="n">
-        <v>392.7280518508706</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3287.27072288689</v>
+        <v>216.2502155485615</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.521316533480897e-06</v>
+        <v>2.939482865584448e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6870961214067036</v>
+        <v>0.9972100962473501</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3933,7 @@
         <v>67.887</v>
       </c>
       <c r="C8" t="n">
-        <v>1686.213066771085</v>
+        <v>215.3625670600274</v>
       </c>
       <c r="D8" t="n">
         <v>1.43633e-07</v>
@@ -4110,16 +3966,13 @@
         <v>-19367.25000866836</v>
       </c>
       <c r="Y8" t="n">
-        <v>389.3162630114839</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3246.866204574776</v>
+        <v>249.0950567968178</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.448483453491044e-06</v>
+        <v>5.603167188134894e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6669684330727591</v>
+        <v>0.9740866539093019</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3983,7 @@
         <v>63.94400000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1347.721802197299</v>
+        <v>285.7207344917549</v>
       </c>
       <c r="D9" t="n">
         <v>1.43368e-07</v>
@@ -4163,16 +4016,13 @@
         <v>-19817.1919479509</v>
       </c>
       <c r="Y9" t="n">
-        <v>385.959650966054</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3207.657416673737</v>
+        <v>152.3496864065575</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.600902006448315e-06</v>
+        <v>1.99069007762569e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6349211170253005</v>
+        <v>0.9999683979653243</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4033,7 @@
         <v>62.01099999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>1572.957364006709</v>
+        <v>296.2345579681313</v>
       </c>
       <c r="D10" t="n">
         <v>1.43162e-07</v>
@@ -4216,16 +4066,13 @@
         <v>-20694.79226048642</v>
       </c>
       <c r="Y10" t="n">
-        <v>387.3450379457233</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6379.659292308062</v>
+        <v>136.0238053193072</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.122412543331055e-06</v>
+        <v>1.854862673629728e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7933009686804277</v>
+        <v>0.9999747873922931</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4083,7 @@
         <v>62.42699999999996</v>
       </c>
       <c r="C11" t="n">
-        <v>2104.812518981881</v>
+        <v>269.9749219144816</v>
       </c>
       <c r="D11" t="n">
         <v>1.43006e-07</v>
@@ -4269,16 +4116,13 @@
         <v>-22756.50704360376</v>
       </c>
       <c r="Y11" t="n">
-        <v>383.2532454365163</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>312966827.1727201</v>
+        <v>176.2845162334381</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.644941800157093e-07</v>
+        <v>4.073067754415299e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9782682150218491</v>
+        <v>0.9646357305701903</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4279,7 @@
         <v>106.705</v>
       </c>
       <c r="C2" t="n">
-        <v>1912.440123799267</v>
+        <v>293.2546290745512</v>
       </c>
       <c r="D2" t="n">
         <v>1.46314e-07</v>
@@ -4468,16 +4312,13 @@
         <v>-12826.70080709606</v>
       </c>
       <c r="Y2" t="n">
-        <v>445.5217413763704</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>364301404.1346943</v>
+        <v>201.7904556659632</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91923481557885e-07</v>
+        <v>2.046577140946956e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9583470646485271</v>
+        <v>0.9996772920320494</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4329,7 @@
         <v>89.92000000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>1072.656592759998</v>
+        <v>304.7782054152098</v>
       </c>
       <c r="D3" t="n">
         <v>1.45624e-07</v>
@@ -4521,16 +4362,13 @@
         <v>-15183.47037551354</v>
       </c>
       <c r="Y3" t="n">
-        <v>427.9261418923682</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>15303.38066629657</v>
+        <v>182.9754801086265</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88800024798695e-07</v>
+        <v>2.02976220376825e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9999977050154838</v>
+        <v>0.9999941565406726</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4379,7 @@
         <v>86.75099999999998</v>
       </c>
       <c r="C4" t="n">
-        <v>1111.732642602691</v>
+        <v>305.8352333355332</v>
       </c>
       <c r="D4" t="n">
         <v>1.44916e-07</v>
@@ -4574,16 +4412,13 @@
         <v>-17996.41734846085</v>
       </c>
       <c r="Y4" t="n">
-        <v>428.6542212651177</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>116762374.6555094</v>
+        <v>170.6875169611787</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.765931770364124e-07</v>
+        <v>1.930661947361007e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9694633329565993</v>
+        <v>0.9993475535750741</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4429,7 @@
         <v>83.63099999999997</v>
       </c>
       <c r="C5" t="n">
-        <v>1074.396004727845</v>
+        <v>83.63099999999997</v>
       </c>
       <c r="D5" t="n">
         <v>1.44353e-07</v>
@@ -4626,11 +4461,10 @@
       <c r="X5" t="n">
         <v>-20102.8191344386</v>
       </c>
-      <c r="Y5" t="n">
-        <v>423.9464700506286</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>173605973.5623363</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.728458101141928e-07</v>
@@ -4647,7 +4481,7 @@
         <v>81.73200000000003</v>
       </c>
       <c r="C6" t="n">
-        <v>1128.47871941567</v>
+        <v>81.73200000000003</v>
       </c>
       <c r="D6" t="n">
         <v>1.43943e-07</v>
@@ -4679,11 +4513,10 @@
       <c r="X6" t="n">
         <v>-22072.28940661754</v>
       </c>
-      <c r="Y6" t="n">
-        <v>409.4762507523336</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6634.489808736175</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>4.474904544031344e-07</v>
@@ -4700,7 +4533,7 @@
         <v>79.34900000000005</v>
       </c>
       <c r="C7" t="n">
-        <v>1150.54733993838</v>
+        <v>259.8347445683266</v>
       </c>
       <c r="D7" t="n">
         <v>1.43615e-07</v>
@@ -4733,16 +4566,13 @@
         <v>-23590.42694492583</v>
       </c>
       <c r="Y7" t="n">
-        <v>414.7822903069173</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>464361701.3064986</v>
+        <v>200.9796708581143</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.679803956322664e-07</v>
+        <v>2.372018109961192e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9756979943363299</v>
+        <v>0.9995786598693167</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4583,7 @@
         <v>77.149</v>
       </c>
       <c r="C8" t="n">
-        <v>1158.92719714933</v>
+        <v>77.149</v>
       </c>
       <c r="D8" t="n">
         <v>1.43417e-07</v>
@@ -4785,11 +4615,10 @@
       <c r="X8" t="n">
         <v>-24738.50326950821</v>
       </c>
-      <c r="Y8" t="n">
-        <v>410.6263840299802</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>224219218.8157094</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.662751648033464e-07</v>
@@ -4806,7 +4635,7 @@
         <v>73.39099999999996</v>
       </c>
       <c r="C9" t="n">
-        <v>1031.967460006077</v>
+        <v>73.39099999999996</v>
       </c>
       <c r="D9" t="n">
         <v>1.43228e-07</v>
@@ -4838,11 +4667,10 @@
       <c r="X9" t="n">
         <v>-24829.51235185706</v>
       </c>
-      <c r="Y9" t="n">
-        <v>396.9008938885154</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3330.061449918616</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>4.344437710028993e-06</v>
@@ -4859,7 +4687,7 @@
         <v>72.53700000000003</v>
       </c>
       <c r="C10" t="n">
-        <v>1281.376399019318</v>
+        <v>72.53700000000003</v>
       </c>
       <c r="D10" t="n">
         <v>1.43116e-07</v>
@@ -4891,11 +4719,10 @@
       <c r="X10" t="n">
         <v>-26313.31105928323</v>
       </c>
-      <c r="Y10" t="n">
-        <v>394.4043571083006</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3299.951747559794</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.67483432733058e-06</v>
@@ -4912,7 +4739,7 @@
         <v>72.33399999999995</v>
       </c>
       <c r="C11" t="n">
-        <v>1318.332450563865</v>
+        <v>364.7651605422383</v>
       </c>
       <c r="D11" t="n">
         <v>1.43021e-07</v>
@@ -4945,16 +4772,13 @@
         <v>-28470.45822842</v>
       </c>
       <c r="Y11" t="n">
-        <v>392.0388811811654</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3273.180475907599</v>
+        <v>77.88022350298743</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.128354893777338e-06</v>
+        <v>1.387939804216694e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6249177268667451</v>
+        <v>0.9996805370942213</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4789,7 @@
         <v>71.02100000000002</v>
       </c>
       <c r="C12" t="n">
-        <v>1351.941644547521</v>
+        <v>71.02100000000002</v>
       </c>
       <c r="D12" t="n">
         <v>1.42966e-07</v>
@@ -4997,11 +4821,10 @@
       <c r="X12" t="n">
         <v>-29121.17547699118</v>
       </c>
-      <c r="Y12" t="n">
-        <v>389.7561682247307</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3245.541536701804</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>5.700437883643665e-06</v>
@@ -5018,7 +4841,7 @@
         <v>68.92000000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>1235.682884738866</v>
+        <v>242.2771403458611</v>
       </c>
       <c r="D13" t="n">
         <v>1.42903e-07</v>
@@ -5051,16 +4874,13 @@
         <v>-29230.2190850054</v>
       </c>
       <c r="Y13" t="n">
-        <v>387.4442877909653</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3218.404699776368</v>
+        <v>201.0148819714799</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.583406276037654e-06</v>
+        <v>2.846933705082984e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.6366755061964129</v>
+        <v>0.9983688255702891</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4891,7 @@
         <v>68.77800000000002</v>
       </c>
       <c r="C14" t="n">
-        <v>1510.266341076298</v>
+        <v>239.3322013356098</v>
       </c>
       <c r="D14" t="n">
         <v>1.42868e-07</v>
@@ -5104,16 +4924,13 @@
         <v>-30606.60289461131</v>
       </c>
       <c r="Y14" t="n">
-        <v>389.7406547608484</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6428.329509532081</v>
+        <v>211.6338366294502</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.404332381958741e-06</v>
+        <v>3.626669434144762e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.7603143428010402</v>
+        <v>0.9896962979684972</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4941,7 @@
         <v>66.82499999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>1381.326344395011</v>
+        <v>217.6996840339342</v>
       </c>
       <c r="D15" t="n">
         <v>1.42845e-07</v>
@@ -5157,16 +4974,13 @@
         <v>-29635.20413203444</v>
       </c>
       <c r="Y15" t="n">
-        <v>387.2330232416897</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1685873676.812895</v>
+        <v>243.8275687341049</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.602149282356551e-07</v>
+        <v>8.039332748715568e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9821131271518025</v>
+        <v>0.9506938576182017</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4991,7 @@
         <v>64.565</v>
       </c>
       <c r="C16" t="n">
-        <v>1186.073917725104</v>
+        <v>207.5566077620917</v>
       </c>
       <c r="D16" t="n">
         <v>1.42846e-07</v>
@@ -5210,16 +5024,13 @@
         <v>-29097.28831433077</v>
       </c>
       <c r="Y16" t="n">
-        <v>384.180802477226</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>32699356.54622534</v>
+        <v>224.8154737608533</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.595471982436994e-07</v>
+        <v>3.445594278495454e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9827547239918457</v>
+        <v>0.9986173664264046</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5041,7 @@
         <v>64.21700000000004</v>
       </c>
       <c r="C17" t="n">
-        <v>1440.609429724009</v>
+        <v>64.21700000000004</v>
       </c>
       <c r="D17" t="n">
         <v>1.42851e-07</v>
@@ -5262,11 +5073,10 @@
       <c r="X17" t="n">
         <v>-29700.81025677378</v>
       </c>
-      <c r="Y17" t="n">
-        <v>381.1678759208106</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>156745896.91315</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.592581634940034e-07</v>
@@ -5283,7 +5093,7 @@
         <v>64.08499999999998</v>
       </c>
       <c r="C18" t="n">
-        <v>1463.289119790709</v>
+        <v>64.08499999999998</v>
       </c>
       <c r="D18" t="n">
         <v>1.42865e-07</v>
@@ -5315,11 +5125,10 @@
       <c r="X18" t="n">
         <v>-31154.69381519698</v>
       </c>
-      <c r="Y18" t="n">
-        <v>378.1684127705454</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>824277120.1782154</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.589103556328105e-07</v>
@@ -5336,7 +5145,7 @@
         <v>62.55700000000002</v>
       </c>
       <c r="C19" t="n">
-        <v>1476.006307885823</v>
+        <v>188.8564794105574</v>
       </c>
       <c r="D19" t="n">
         <v>1.42879e-07</v>
@@ -5369,16 +5178,13 @@
         <v>-30964.85902371214</v>
       </c>
       <c r="Y19" t="n">
-        <v>375.2080221451005</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>204741793.2675469</v>
+        <v>239.4495495668397</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.585612533663524e-07</v>
+        <v>4.067580511860567e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9837469604722237</v>
+        <v>0.9991901375553539</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5195,7 @@
         <v>60.09100000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>1439.359701410888</v>
+        <v>182.3496340088545</v>
       </c>
       <c r="D20" t="n">
         <v>1.42897e-07</v>
@@ -5422,16 +5228,13 @@
         <v>-28783.94244058224</v>
       </c>
       <c r="Y20" t="n">
-        <v>372.271572841044</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>102338665.8058016</v>
+        <v>241.0362336495347</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.581391330094839e-07</v>
+        <v>4.130287454776442e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9841762427238474</v>
+        <v>0.9999010312556399</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5245,7 @@
         <v>59.94599999999997</v>
       </c>
       <c r="C21" t="n">
-        <v>1446.46831149877</v>
+        <v>176.0280569302203</v>
       </c>
       <c r="D21" t="n">
         <v>1.42901e-07</v>
@@ -5475,16 +5278,13 @@
         <v>-29563.8603020616</v>
       </c>
       <c r="Y21" t="n">
-        <v>369.2783700430094</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>167282172.5652885</v>
+        <v>247.2571882175293</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.578380550462287e-07</v>
+        <v>4.604324978974212e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9844766365161687</v>
+        <v>0.9983571105529503</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5295,7 @@
         <v>58.75299999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1436.242120489184</v>
+        <v>169.4403819028988</v>
       </c>
       <c r="D22" t="n">
         <v>1.42914e-07</v>
@@ -5528,16 +5328,13 @@
         <v>-30011.96598531417</v>
       </c>
       <c r="Y22" t="n">
-        <v>366.3474447787102</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>199545158.8411019</v>
+        <v>262.1284471106711</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.574402716137631e-07</v>
+        <v>7.149229435143403e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9848776475961103</v>
+        <v>0.9871464169076573</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5491,7 @@
         <v>137.544</v>
       </c>
       <c r="C2" t="n">
-        <v>6196.275659093436</v>
+        <v>387.4534038306677</v>
       </c>
       <c r="D2" t="n">
         <v>1.46552e-07</v>
@@ -5727,16 +5524,13 @@
         <v>-7984.234650369973</v>
       </c>
       <c r="Y2" t="n">
-        <v>465.9385210326996</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>125944830.0616441</v>
+        <v>128.9522613124877</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.217924434706812e-07</v>
+        <v>1.312359387818177e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9369197037901673</v>
+        <v>0.9969231243837424</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5541,7 @@
         <v>90.36699999999996</v>
       </c>
       <c r="C3" t="n">
-        <v>1866.291739245986</v>
+        <v>90.36699999999996</v>
       </c>
       <c r="D3" t="n">
         <v>1.48235e-07</v>
@@ -5779,11 +5573,10 @@
       <c r="X3" t="n">
         <v>-9314.38895203223</v>
       </c>
-      <c r="Y3" t="n">
-        <v>429.6809189207714</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>235133123.0002992</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>2.027784351602589e-07</v>
@@ -5800,7 +5593,7 @@
         <v>79.47200000000004</v>
       </c>
       <c r="C4" t="n">
-        <v>1202.216464266786</v>
+        <v>79.47200000000004</v>
       </c>
       <c r="D4" t="n">
         <v>1.47334e-07</v>
@@ -5832,11 +5625,10 @@
       <c r="X4" t="n">
         <v>-11088.53596514757</v>
       </c>
-      <c r="Y4" t="n">
-        <v>419.1457457201915</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>114473230.6109785</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.912782323924476e-07</v>
@@ -5853,7 +5645,7 @@
         <v>76.82999999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>1343.575048013013</v>
+        <v>539.9716375954924</v>
       </c>
       <c r="D5" t="n">
         <v>1.46346e-07</v>
@@ -5886,16 +5678,13 @@
         <v>-13231.08512810853</v>
       </c>
       <c r="Y5" t="n">
-        <v>412.8967978783018</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>119797743.5511172</v>
+        <v>0.6946890043136505</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.835494335189894e-07</v>
+        <v>1.372216951617967e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9651419885269856</v>
+        <v>0.6446633361164164</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5695,7 @@
         <v>74.733</v>
       </c>
       <c r="C6" t="n">
-        <v>1705.901735662813</v>
+        <v>223.7864516217042</v>
       </c>
       <c r="D6" t="n">
         <v>1.45553e-07</v>
@@ -5939,16 +5728,13 @@
         <v>-15489.98017282409</v>
       </c>
       <c r="Y6" t="n">
-        <v>395.9831167167076</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3336.055198839147</v>
+        <v>241.7106168739188</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.05322933536866e-06</v>
+        <v>3.358402521305719e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7126686329610542</v>
+        <v>0.9990501234434463</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5745,7 @@
         <v>71.06799999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>1588.283780575926</v>
+        <v>235.4628808662749</v>
       </c>
       <c r="D7" t="n">
         <v>1.44965e-07</v>
@@ -5992,16 +5778,13 @@
         <v>-17009.14249155791</v>
       </c>
       <c r="Y7" t="n">
-        <v>392.2258068671704</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3287.626786119543</v>
+        <v>210.983833774033</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.265270617677732e-06</v>
+        <v>2.749348799264973e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6695571729866691</v>
+        <v>0.9980783971590791</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5795,7 @@
         <v>68.54599999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1766.645389583148</v>
+        <v>214.3904622401751</v>
       </c>
       <c r="D8" t="n">
         <v>1.44513e-07</v>
@@ -6045,16 +5828,13 @@
         <v>-18422.55495118479</v>
       </c>
       <c r="Y8" t="n">
-        <v>388.5763487116285</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3241.865783801222</v>
+        <v>230.454446275409</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.159831949522686e-06</v>
+        <v>3.170393650990506e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6242997012247486</v>
+        <v>0.9992727644469968</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5845,7 @@
         <v>63.29699999999997</v>
       </c>
       <c r="C9" t="n">
-        <v>1635.120217715056</v>
+        <v>63.29699999999997</v>
       </c>
       <c r="D9" t="n">
         <v>1.44184e-07</v>
@@ -6097,11 +5877,10 @@
       <c r="X9" t="n">
         <v>-19002.98295864273</v>
       </c>
-      <c r="Y9" t="n">
-        <v>385.0824326971173</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3198.838064944804</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>5.578920216903476e-06</v>
@@ -6118,7 +5897,7 @@
         <v>63.92100000000005</v>
       </c>
       <c r="C10" t="n">
-        <v>2133.330735286719</v>
+        <v>63.92100000000005</v>
       </c>
       <c r="D10" t="n">
         <v>1.43944e-07</v>
@@ -6150,11 +5929,10 @@
       <c r="X10" t="n">
         <v>-21035.60011296409</v>
       </c>
-      <c r="Y10" t="n">
-        <v>386.4806172968474</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6365.913405262596</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.397234723466366e-06</v>
@@ -6171,7 +5949,7 @@
         <v>60.53500000000003</v>
       </c>
       <c r="C11" t="n">
-        <v>1700.76733376636</v>
+        <v>267.9801386871702</v>
       </c>
       <c r="D11" t="n">
         <v>1.43775e-07</v>
@@ -6204,16 +5982,13 @@
         <v>-21517.56347801927</v>
       </c>
       <c r="Y11" t="n">
-        <v>382.3158348878899</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>416139392.9200711</v>
+        <v>162.4524184439602</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.654709682333789e-07</v>
+        <v>2.248908705432753e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9781914278896926</v>
+        <v>0.998983161837647</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6145,7 @@
         <v>108.15</v>
       </c>
       <c r="C2" t="n">
-        <v>2258.879895137717</v>
+        <v>281.0409288674729</v>
       </c>
       <c r="D2" t="n">
         <v>1.48966e-07</v>
@@ -6403,16 +6178,13 @@
         <v>-10250.95867513279</v>
       </c>
       <c r="Y2" t="n">
-        <v>447.743774507379</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>30778583.24879043</v>
+        <v>215.7120628567772</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.052089358659983e-07</v>
+        <v>2.138552558186012e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9509693409218157</v>
+        <v>0.9996971898150299</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6195,7 @@
         <v>93.166</v>
       </c>
       <c r="C3" t="n">
-        <v>1241.443435871459</v>
+        <v>93.166</v>
       </c>
       <c r="D3" t="n">
         <v>1.46983e-07</v>
@@ -6455,11 +6227,10 @@
       <c r="X3" t="n">
         <v>-14561.04227016276</v>
       </c>
-      <c r="Y3" t="n">
-        <v>435.21944108829</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>475366282.7591516</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.86397735280607e-07</v>
@@ -6476,7 +6247,7 @@
         <v>84.99800000000005</v>
       </c>
       <c r="C4" t="n">
-        <v>986.63837260576</v>
+        <v>305.5809651733679</v>
       </c>
       <c r="D4" t="n">
         <v>1.45814e-07</v>
@@ -6509,16 +6280,13 @@
         <v>-17150.11455124067</v>
       </c>
       <c r="Y4" t="n">
-        <v>412.6806406451644</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3522.630093569946</v>
+        <v>172.9230421845877</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.578283406252619e-06</v>
+        <v>1.957654486844113e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7431792652140136</v>
+        <v>0.999158029430076</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6297,7 @@
         <v>83.40699999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>1053.197389074623</v>
+        <v>549.3331263965113</v>
       </c>
       <c r="D5" t="n">
         <v>1.4504e-07</v>
@@ -6562,16 +6330,13 @@
         <v>-19714.39747457574</v>
       </c>
       <c r="Y5" t="n">
-        <v>425.0270033480434</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>231840496.8403437</v>
+        <v>1.122018328146101</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.740383282684285e-07</v>
+        <v>1.007752583480563e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9717846255995866</v>
+        <v>0.6647925506906136</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6347,7 @@
         <v>82.41899999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>1211.585327097715</v>
+        <v>82.41899999999998</v>
       </c>
       <c r="D6" t="n">
         <v>1.44557e-07</v>
@@ -6614,11 +6379,10 @@
       <c r="X6" t="n">
         <v>-22545.27319824054</v>
       </c>
-      <c r="Y6" t="n">
-        <v>422.7110849134795</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>10926.48629287233</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>2.44331616981372e-07</v>
@@ -6635,7 +6399,7 @@
         <v>78.279</v>
       </c>
       <c r="C7" t="n">
-        <v>1132.672564901439</v>
+        <v>257.4012071746066</v>
       </c>
       <c r="D7" t="n">
         <v>1.44212e-07</v>
@@ -6668,16 +6432,13 @@
         <v>-22886.24164235841</v>
       </c>
       <c r="Y7" t="n">
-        <v>416.3709010465464</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>227030833.2324212</v>
+        <v>206.1549515421327</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.689034763179671e-07</v>
+        <v>2.499137341699494e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9754734755785102</v>
+        <v>0.9990209956164451</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6449,7 @@
         <v>76.28500000000003</v>
       </c>
       <c r="C8" t="n">
-        <v>1022.739285819663</v>
+        <v>258.4547523666612</v>
       </c>
       <c r="D8" t="n">
         <v>1.43979e-07</v>
@@ -6721,16 +6482,13 @@
         <v>-23744.98673057721</v>
       </c>
       <c r="Y8" t="n">
-        <v>413.121377527487</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6683.192422803645</v>
+        <v>200.8296659418979</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.106353207470936e-06</v>
+        <v>2.46755963144936e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7816812558426494</v>
+        <v>0.998322827495478</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6499,7 @@
         <v>74.70000000000005</v>
       </c>
       <c r="C9" t="n">
-        <v>1171.429291890032</v>
+        <v>252.1536928203679</v>
       </c>
       <c r="D9" t="n">
         <v>1.43841e-07</v>
@@ -6774,16 +6532,13 @@
         <v>-24730.50644335342</v>
       </c>
       <c r="Y9" t="n">
-        <v>409.2460785515499</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5466.576901333721</v>
+        <v>203.3103995299852</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.727846956299995e-07</v>
+        <v>2.506957320154795e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8478032682312012</v>
+        <v>0.999577645628526</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6549,7 @@
         <v>75.37799999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>1457.818187546433</v>
+        <v>249.8240601280796</v>
       </c>
       <c r="D10" t="n">
         <v>1.43722e-07</v>
@@ -6827,16 +6582,13 @@
         <v>-27316.27022963938</v>
       </c>
       <c r="Y10" t="n">
-        <v>395.8910871285624</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3320.625198204999</v>
+        <v>211.3956404098765</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.574161057298543e-06</v>
+        <v>3.275607928972657e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6863964127987041</v>
+        <v>0.9888528806407042</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6599,7 @@
         <v>70.90499999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>1077.504582352377</v>
+        <v>249.7643994824821</v>
       </c>
       <c r="D11" t="n">
         <v>1.43611e-07</v>
@@ -6880,16 +6632,13 @@
         <v>-25295.6471690317</v>
       </c>
       <c r="Y11" t="n">
-        <v>393.8316717896972</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3293.769767612086</v>
+        <v>197.8123440137912</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.578325690877909e-06</v>
+        <v>2.471276929346483e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6819802183137279</v>
+        <v>0.9994610263215388</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6649,7 @@
         <v>70.32599999999996</v>
       </c>
       <c r="C12" t="n">
-        <v>1163.125282409601</v>
+        <v>70.32599999999996</v>
       </c>
       <c r="D12" t="n">
         <v>1.43544e-07</v>
@@ -6932,11 +6681,10 @@
       <c r="X12" t="n">
         <v>-26418.90728981206</v>
       </c>
-      <c r="Y12" t="n">
-        <v>391.8424530579769</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3270.317355555084</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>6.066630005625109e-06</v>
@@ -6953,7 +6701,7 @@
         <v>70.27800000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>1421.78058325568</v>
+        <v>242.1240917332349</v>
       </c>
       <c r="D13" t="n">
         <v>1.4353e-07</v>
@@ -6986,16 +6734,13 @@
         <v>-28499.84257358155</v>
       </c>
       <c r="Y13" t="n">
-        <v>389.8289478579588</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3246.622202714017</v>
+        <v>198.7494040832594</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.708662111489181e-06</v>
+        <v>2.55882536354243e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.6318400119149941</v>
+        <v>0.9996167138923566</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6751,7 @@
         <v>69.04499999999996</v>
       </c>
       <c r="C14" t="n">
-        <v>1348.215302720382</v>
+        <v>69.04499999999996</v>
       </c>
       <c r="D14" t="n">
         <v>1.43474e-07</v>
@@ -7038,11 +6783,10 @@
       <c r="X14" t="n">
         <v>-28311.08958908441</v>
       </c>
-      <c r="Y14" t="n">
-        <v>387.8941981626574</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3225.342151708438</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>5.619389206315173e-06</v>
@@ -7059,7 +6803,7 @@
         <v>68.36199999999997</v>
       </c>
       <c r="C15" t="n">
-        <v>1544.943801720935</v>
+        <v>239.3863579690577</v>
       </c>
       <c r="D15" t="n">
         <v>1.43446e-07</v>
@@ -7092,16 +6836,13 @@
         <v>-29049.59931635962</v>
       </c>
       <c r="Y15" t="n">
-        <v>391.1532336160193</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6451.145522897522</v>
+        <v>202.1053660856297</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.050197949507803e-06</v>
+        <v>2.885871208544202e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8119579070368823</v>
+        <v>0.9984823978559318</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6853,7 @@
         <v>65.73099999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>1245.141743481329</v>
+        <v>65.73099999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1.43442e-07</v>
@@ -7144,11 +6885,10 @@
       <c r="X16" t="n">
         <v>-27259.19356633699</v>
       </c>
-      <c r="Y16" t="n">
-        <v>388.8264473583125</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>159832079.2250715</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>1.615536210353232e-07</v>
@@ -7165,7 +6905,7 @@
         <v>65.62799999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>1394.635750131411</v>
+        <v>217.9475878740918</v>
       </c>
       <c r="D17" t="n">
         <v>1.43441e-07</v>
@@ -7198,16 +6938,13 @@
         <v>-28880.54549330903</v>
       </c>
       <c r="Y17" t="n">
-        <v>386.034710055192</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>420412153.1588411</v>
+        <v>225.3907037881557</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.611705287351e-07</v>
+        <v>3.627376490498228e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9818357171934463</v>
+        <v>0.9992777482776589</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6955,7 @@
         <v>63.923</v>
       </c>
       <c r="C18" t="n">
-        <v>1370.409014861883</v>
+        <v>63.923</v>
       </c>
       <c r="D18" t="n">
         <v>1.43414e-07</v>
@@ -7250,11 +6987,10 @@
       <c r="X18" t="n">
         <v>-28425.14716559185</v>
       </c>
-      <c r="Y18" t="n">
-        <v>383.2136317446345</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>313980803.5212577</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.607471483106774e-07</v>
@@ -7271,7 +7007,7 @@
         <v>63.81099999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>1696.809645737938</v>
+        <v>63.81099999999998</v>
       </c>
       <c r="D19" t="n">
         <v>1.43426e-07</v>
@@ -7303,11 +7039,10 @@
       <c r="X19" t="n">
         <v>-29184.06750991363</v>
       </c>
-      <c r="Y19" t="n">
-        <v>380.3232093163263</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>310644615.4314929</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>1.604137434342052e-07</v>
@@ -7324,7 +7059,7 @@
         <v>62.517</v>
       </c>
       <c r="C20" t="n">
-        <v>1644.610581986179</v>
+        <v>201.5523275437778</v>
       </c>
       <c r="D20" t="n">
         <v>1.43445e-07</v>
@@ -7357,16 +7092,13 @@
         <v>-28988.99657579932</v>
       </c>
       <c r="Y20" t="n">
-        <v>377.3952586420104</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>206279049.5861789</v>
+        <v>247.1943208717368</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.60055151696587e-07</v>
+        <v>6.482556023868355e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9829095447455423</v>
+        <v>0.9738197606982245</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7109,7 @@
         <v>62.59499999999997</v>
       </c>
       <c r="C21" t="n">
-        <v>2238.785887471848</v>
+        <v>62.59499999999997</v>
       </c>
       <c r="D21" t="n">
         <v>1.43491e-07</v>
@@ -7409,11 +7141,10 @@
       <c r="X21" t="n">
         <v>-31198.96571073774</v>
       </c>
-      <c r="Y21" t="n">
-        <v>374.4372449724538</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>319226464.8156897</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1.598147789401788e-07</v>
@@ -7430,7 +7161,7 @@
         <v>60.60300000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1795.178738016864</v>
+        <v>60.60300000000001</v>
       </c>
       <c r="D22" t="n">
         <v>1.43515e-07</v>
@@ -7462,11 +7193,10 @@
       <c r="X22" t="n">
         <v>-29436.65716876552</v>
       </c>
-      <c r="Y22" t="n">
-        <v>371.479829090248</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>606907419.4105353</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>1.595275182660601e-07</v>
@@ -7629,7 +7359,7 @@
         <v>114.597</v>
       </c>
       <c r="C2" t="n">
-        <v>7851.44006932193</v>
+        <v>334.1603570585748</v>
       </c>
       <c r="D2" t="n">
         <v>1.57293e-07</v>
@@ -7662,16 +7392,13 @@
         <v>-5387.805928715256</v>
       </c>
       <c r="Y2" t="n">
-        <v>439.5821624890179</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>179437612.1642645</v>
+        <v>153.8207859995344</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.656262698550957e-07</v>
+        <v>1.536830668752766e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9206783514761252</v>
+        <v>0.9997696140965543</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7409,7 @@
         <v>83.63999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1640.783106316603</v>
+        <v>244.5965487384973</v>
       </c>
       <c r="D3" t="n">
         <v>1.55133e-07</v>
@@ -7715,16 +7442,13 @@
         <v>-7388.069706441625</v>
       </c>
       <c r="Y3" t="n">
-        <v>400.8704822541768</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3419.239551428888</v>
+        <v>225.8257225352453</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.532936774713646e-06</v>
+        <v>2.746384160694846e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7370591481815131</v>
+        <v>0.9987911239344199</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7459,7 @@
         <v>75.69200000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1297.601013059806</v>
+        <v>335.6640305703018</v>
       </c>
       <c r="D4" t="n">
         <v>1.52503e-07</v>
@@ -7768,16 +7492,13 @@
         <v>-9881.900400862911</v>
       </c>
       <c r="Y4" t="n">
-        <v>409.407617747873</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>181930353.206481</v>
+        <v>117.4211516145785</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.018214439935201e-07</v>
+        <v>1.53441897296202e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9570432031100142</v>
+        <v>0.9999314139343761</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7509,7 @@
         <v>71.43200000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>1223.373459542942</v>
+        <v>242.4492357892748</v>
       </c>
       <c r="D5" t="n">
         <v>1.50662e-07</v>
@@ -7821,16 +7542,13 @@
         <v>-12292.18184384115</v>
       </c>
       <c r="Y5" t="n">
-        <v>392.2942363708429</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3311.443666203407</v>
+        <v>207.7983503621808</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.426062328510996e-06</v>
+        <v>2.665295921145765e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6946169540452056</v>
+        <v>0.9970066901960255</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7559,7 @@
         <v>70.99099999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1460.336227643573</v>
+        <v>218.1066684759337</v>
       </c>
       <c r="D6" t="n">
         <v>1.49432e-07</v>
@@ -7874,16 +7592,13 @@
         <v>-14767.62845276563</v>
       </c>
       <c r="Y6" t="n">
-        <v>389.1104300571027</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3266.097246308253</v>
+        <v>235.2074617793962</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.625341197155095e-06</v>
+        <v>3.334800953967796e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6865098081672082</v>
+        <v>0.9982737197722613</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7609,7 @@
         <v>68.19499999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1513.261284732756</v>
+        <v>68.19499999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.48639e-07</v>
@@ -7926,11 +7641,10 @@
       <c r="X7" t="n">
         <v>-16633.02655156043</v>
       </c>
-      <c r="Y7" t="n">
-        <v>385.7990518375054</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3219.360410303704</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>5.694982343220032e-06</v>
@@ -7947,7 +7661,7 @@
         <v>64.32899999999995</v>
       </c>
       <c r="C8" t="n">
-        <v>1517.801734646978</v>
+        <v>210.1083239547866</v>
       </c>
       <c r="D8" t="n">
         <v>1.48072e-07</v>
@@ -7980,16 +7694,13 @@
         <v>-17889.92606714007</v>
       </c>
       <c r="Y8" t="n">
-        <v>387.7873766025926</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6402.446348565064</v>
+        <v>244.2394356649057</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.583818891856134e-07</v>
+        <v>5.361914432378412e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.835353369684867</v>
+        <v>0.9778663228361385</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7711,7 @@
         <v>63.42499999999995</v>
       </c>
       <c r="C9" t="n">
-        <v>1683.585319279457</v>
+        <v>63.42499999999995</v>
       </c>
       <c r="D9" t="n">
         <v>1.47724e-07</v>
@@ -8032,11 +7743,10 @@
       <c r="X9" t="n">
         <v>-19597.34089013432</v>
       </c>
-      <c r="Y9" t="n">
-        <v>383.7743960295181</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>313346146.0761515</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.723040403138065e-07</v>
@@ -8053,7 +7763,7 @@
         <v>59.10699999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>1485.112728811299</v>
+        <v>264.9204048920089</v>
       </c>
       <c r="D10" t="n">
         <v>1.475e-07</v>
@@ -8086,16 +7796,13 @@
         <v>-19947.20813040185</v>
       </c>
       <c r="Y10" t="n">
-        <v>379.1208119834776</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>206565007.5045739</v>
+        <v>156.4788618016251</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.704464585334878e-07</v>
+        <v>2.163828103296893e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9775685726083856</v>
+        <v>0.9996554499098295</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7813,7 @@
         <v>59.40999999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>2373.207616085963</v>
+        <v>231.6163981110363</v>
       </c>
       <c r="D11" t="n">
         <v>1.47335e-07</v>
@@ -8139,16 +7846,13 @@
         <v>-21601.1652768092</v>
       </c>
       <c r="Y11" t="n">
-        <v>374.8848460024854</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>229459817.9932854</v>
+        <v>185.2287740787792</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.689847293904402e-07</v>
+        <v>2.573585113307562e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9787166590237585</v>
+        <v>0.9994754130573339</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +8009,7 @@
         <v>106.311</v>
       </c>
       <c r="C2" t="n">
-        <v>1986.697608512675</v>
+        <v>295.1437086199578</v>
       </c>
       <c r="D2" t="n">
         <v>1.51399e-07</v>
@@ -8338,10 +8042,7 @@
         <v>-13183.64591278973</v>
       </c>
       <c r="Y2" t="n">
-        <v>445.2107445227359</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>484757949.2143062</v>
+        <v>563.3492847341224</v>
       </c>
       <c r="AA2" t="n">
         <v>1.985003324268114e-07</v>
@@ -8358,7 +8059,7 @@
         <v>92.39400000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>1261.935918753573</v>
+        <v>92.39400000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.49834e-07</v>
@@ -8390,11 +8091,10 @@
       <c r="X3" t="n">
         <v>-17219.7122207606</v>
       </c>
-      <c r="Y3" t="n">
-        <v>414.0888565555738</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3551.88036038065</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>2.824848398905355e-06</v>
@@ -8411,7 +8111,7 @@
         <v>88.21699999999998</v>
       </c>
       <c r="C4" t="n">
-        <v>1243.681193186042</v>
+        <v>268.0141452646477</v>
       </c>
       <c r="D4" t="n">
         <v>1.48879e-07</v>
@@ -8444,16 +8144,13 @@
         <v>-20167.68347234795</v>
       </c>
       <c r="Y4" t="n">
-        <v>427.8187709455693</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>240267045.2171544</v>
+        <v>215.670989616551</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.799402542672796e-07</v>
+        <v>3.053978302347901e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9706712931760222</v>
+        <v>0.98549274290791</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8161,7 @@
         <v>82.83100000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>1112.651922379521</v>
+        <v>265.8312635846895</v>
       </c>
       <c r="D5" t="n">
         <v>1.48296e-07</v>
@@ -8497,16 +8194,13 @@
         <v>-20992.34145579227</v>
       </c>
       <c r="Y5" t="n">
-        <v>423.4845522674789</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>230711883.3746552</v>
+        <v>202.3163981180456</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.764613456250841e-07</v>
+        <v>2.269225935213186e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9730451771880099</v>
+        <v>0.999515755718297</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8211,7 @@
         <v>80.47500000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>1114.874122009982</v>
+        <v>260.0923029307649</v>
       </c>
       <c r="D6" t="n">
         <v>1.47905e-07</v>
@@ -8550,16 +8244,13 @@
         <v>-22050.59842642148</v>
       </c>
       <c r="Y6" t="n">
-        <v>419.3363685423765</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>114431946.7009747</v>
+        <v>212.0401719370243</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.742469253335535e-07</v>
+        <v>2.547038235313572e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9745720067180582</v>
+        <v>0.9999799532050987</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8261,7 @@
         <v>78.49499999999995</v>
       </c>
       <c r="C7" t="n">
-        <v>1130.617171314762</v>
+        <v>364.4510880228202</v>
       </c>
       <c r="D7" t="n">
         <v>1.47673e-07</v>
@@ -8603,16 +8294,13 @@
         <v>-22692.49838129308</v>
       </c>
       <c r="Y7" t="n">
-        <v>415.069877870661</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6699.275184442167</v>
+        <v>91.67988971608844</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.432145177788463e-07</v>
+        <v>1.356809998327137e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8402983123840755</v>
+        <v>0.9999124228055719</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8311,7 @@
         <v>75.005</v>
       </c>
       <c r="C8" t="n">
-        <v>1024.990403963821</v>
+        <v>75.005</v>
       </c>
       <c r="D8" t="n">
         <v>1.47524e-07</v>
@@ -8655,11 +8343,10 @@
       <c r="X8" t="n">
         <v>-22513.85403880199</v>
       </c>
-      <c r="Y8" t="n">
-        <v>411.7900922825735</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6788.468379783648</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>6.638363161511533e-07</v>
@@ -8676,7 +8363,7 @@
         <v>76.15599999999995</v>
       </c>
       <c r="C9" t="n">
-        <v>1284.08907373017</v>
+        <v>250.8280244275861</v>
       </c>
       <c r="D9" t="n">
         <v>1.47422e-07</v>
@@ -8709,16 +8396,13 @@
         <v>-25371.29466502148</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.3939176713774</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3339.040714941274</v>
+        <v>212.6367243441501</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.251818003045368e-06</v>
+        <v>2.803522940076049e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6695653512320575</v>
+        <v>0.9997846977550818</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8413,7 @@
         <v>73.93399999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>1275.257898688055</v>
+        <v>251.1398740450863</v>
       </c>
       <c r="D10" t="n">
         <v>1.47345e-07</v>
@@ -8762,16 +8446,13 @@
         <v>-25198.54161031957</v>
       </c>
       <c r="Y10" t="n">
-        <v>394.9405005528467</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3312.978033132198</v>
+        <v>206.4870183321702</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.572980120354203e-06</v>
+        <v>2.709774740409917e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6805896875607824</v>
+        <v>0.9995594937847865</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8463,7 @@
         <v>71.91399999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1162.291933687253</v>
+        <v>71.91399999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.47276e-07</v>
@@ -8814,11 +8495,10 @@
       <c r="X11" t="n">
         <v>-24938.71876990232</v>
       </c>
-      <c r="Y11" t="n">
-        <v>392.6520746059164</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3285.306692972217</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>4.877486350574464e-06</v>
@@ -8835,7 +8515,7 @@
         <v>70.46300000000002</v>
       </c>
       <c r="C12" t="n">
-        <v>1169.320563564832</v>
+        <v>359.2714532842356</v>
       </c>
       <c r="D12" t="n">
         <v>1.47245e-07</v>
@@ -8868,16 +8548,13 @@
         <v>-25150.24252877807</v>
       </c>
       <c r="Y12" t="n">
-        <v>390.4070269839705</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3257.477024161224</v>
+        <v>80.9569532501279</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.730720833761005e-06</v>
+        <v>1.396878671339473e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.6307817034250055</v>
+        <v>0.9997469384688852</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8565,7 @@
         <v>70.36800000000005</v>
       </c>
       <c r="C13" t="n">
-        <v>1427.236988758707</v>
+        <v>70.36800000000005</v>
       </c>
       <c r="D13" t="n">
         <v>1.47247e-07</v>
@@ -8920,11 +8597,10 @@
       <c r="X13" t="n">
         <v>-26531.69042211393</v>
       </c>
-      <c r="Y13" t="n">
-        <v>388.1213415078581</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3232.569053716101</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>5.629135381785853e-06</v>
@@ -8941,7 +8617,7 @@
         <v>68.02999999999997</v>
       </c>
       <c r="C14" t="n">
-        <v>1265.329089740716</v>
+        <v>237.0066604736441</v>
       </c>
       <c r="D14" t="n">
         <v>1.47216e-07</v>
@@ -8974,16 +8650,13 @@
         <v>-25280.49402069625</v>
       </c>
       <c r="Y14" t="n">
-        <v>390.583764969574</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6458.350086340269</v>
+        <v>203.3380287112363</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.23462095952067e-06</v>
+        <v>2.847868807366486e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.7741013293075699</v>
+        <v>0.9979757146289749</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8667,7 @@
         <v>66.863</v>
       </c>
       <c r="C15" t="n">
-        <v>1167.259727584692</v>
+        <v>237.6009582766221</v>
       </c>
       <c r="D15" t="n">
         <v>1.47205e-07</v>
@@ -9027,16 +8700,13 @@
         <v>-25419.83934485272</v>
       </c>
       <c r="Y15" t="n">
-        <v>389.2140831090402</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>212123666.6558876</v>
+        <v>203.6335644772842</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.667756367745261e-07</v>
+        <v>2.861493679864437e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9805657373557194</v>
+        <v>0.9998487864587822</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8717,7 @@
         <v>66.55400000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>1429.507106971718</v>
+        <v>234.920246964464</v>
       </c>
       <c r="D16" t="n">
         <v>1.47199e-07</v>
@@ -9080,16 +8750,13 @@
         <v>-26595.58197902434</v>
       </c>
       <c r="Y16" t="n">
-        <v>386.1619194211478</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>630147973.6149029</v>
+        <v>199.4732819602494</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.664281427213033e-07</v>
+        <v>2.908707535842557e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9808823324143803</v>
+        <v>0.99869446240015</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8767,7 @@
         <v>65.63</v>
       </c>
       <c r="C17" t="n">
-        <v>1526.593468358828</v>
+        <v>65.63</v>
       </c>
       <c r="D17" t="n">
         <v>1.47301e-07</v>
@@ -9132,11 +8799,10 @@
       <c r="X17" t="n">
         <v>-27301.21563522803</v>
       </c>
-      <c r="Y17" t="n">
-        <v>383.1139822365346</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>235037887.056922</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.658346229963305e-07</v>
@@ -9153,7 +8819,7 @@
         <v>64.55500000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>1482.531756366998</v>
+        <v>64.55500000000001</v>
       </c>
       <c r="D18" t="n">
         <v>1.47247e-07</v>
@@ -9185,11 +8851,10 @@
       <c r="X18" t="n">
         <v>-26639.03816144041</v>
       </c>
-      <c r="Y18" t="n">
-        <v>380.0618972010561</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1033766805.194658</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.656828516500103e-07</v>
@@ -9206,7 +8871,7 @@
         <v>63.72699999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>1494.797082905342</v>
+        <v>211.08590072232</v>
       </c>
       <c r="D19" t="n">
         <v>1.47271e-07</v>
@@ -9239,16 +8904,13 @@
         <v>-27314.91109448129</v>
       </c>
       <c r="Y19" t="n">
-        <v>376.961918160021</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>309418650.2319997</v>
+        <v>233.7420151784868</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.653061657371997e-07</v>
+        <v>6.836273111869968e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9820010834511069</v>
+        <v>0.9636842278339329</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8921,7 @@
         <v>61.61199999999997</v>
       </c>
       <c r="C20" t="n">
-        <v>1429.208141110233</v>
+        <v>206.9435169408619</v>
       </c>
       <c r="D20" t="n">
         <v>1.47275e-07</v>
@@ -9292,16 +8954,13 @@
         <v>-26689.19248452581</v>
       </c>
       <c r="Y20" t="n">
-        <v>373.938434749889</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>205348113.3277394</v>
+        <v>217.7231070823523</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.649336675343289e-07</v>
+        <v>3.425139114818643e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9823539224522917</v>
+        <v>0.9999898975400129</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8971,7 @@
         <v>59.72899999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>1256.476028884376</v>
+        <v>205.2907660705783</v>
       </c>
       <c r="D21" t="n">
         <v>1.47295e-07</v>
@@ -9345,16 +9004,13 @@
         <v>-25320.88127509539</v>
       </c>
       <c r="Y21" t="n">
-        <v>370.903070994451</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>38637295.74779098</v>
+        <v>223.4743097609033</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.645484748636624e-07</v>
+        <v>4.580453238781462e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9827367452978</v>
+        <v>0.98988244288752</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +9021,7 @@
         <v>60.125</v>
       </c>
       <c r="C22" t="n">
-        <v>1687.030197632929</v>
+        <v>202.7118652611399</v>
       </c>
       <c r="D22" t="n">
         <v>1.47365e-07</v>
@@ -9398,16 +9054,13 @@
         <v>-27301.23258940838</v>
       </c>
       <c r="Y22" t="n">
-        <v>367.7975938516235</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>800821460.7859757</v>
+        <v>218.1037054884314</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.645206086526355e-07</v>
+        <v>3.708158159960188e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9828374030987175</v>
+        <v>0.9983818513056532</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9217,7 @@
         <v>113.397</v>
       </c>
       <c r="C2" t="n">
-        <v>1916.963163801467</v>
+        <v>113.397</v>
       </c>
       <c r="D2" t="n">
         <v>1.55372e-07</v>
@@ -9596,11 +9249,10 @@
       <c r="X2" t="n">
         <v>-6441.185630714731</v>
       </c>
-      <c r="Y2" t="n">
-        <v>431.8804385697641</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>236325911.4878342</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.421535611000204e-07</v>
@@ -9617,7 +9269,7 @@
         <v>75.17099999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>3051.339869599293</v>
+        <v>229.0645816763079</v>
       </c>
       <c r="D3" t="n">
         <v>1.54859e-07</v>
@@ -9650,16 +9302,13 @@
         <v>-8801.431445806935</v>
       </c>
       <c r="Y3" t="n">
-        <v>388.8880946342742</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3286.19399190833</v>
+        <v>228.5941246877516</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.320028754645425e-06</v>
+        <v>3.130655124832358e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8835133387878162</v>
+        <v>0.9996202448795002</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9319,7 @@
         <v>67.47399999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>2113.865636293965</v>
+        <v>272.1528302238335</v>
       </c>
       <c r="D4" t="n">
         <v>1.53088e-07</v>
@@ -9703,16 +9352,13 @@
         <v>-11727.89934096327</v>
       </c>
       <c r="Y4" t="n">
-        <v>383.6039142069445</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3210.996368504371</v>
+        <v>161.4046901234984</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.203063429814494e-06</v>
+        <v>2.001967991831343e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6724951138049746</v>
+        <v>0.9995643237254113</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9369,7 @@
         <v>64.238</v>
       </c>
       <c r="C5" t="n">
-        <v>2252.779004659418</v>
+        <v>64.238</v>
       </c>
       <c r="D5" t="n">
         <v>1.51792e-07</v>
@@ -9755,11 +9401,10 @@
       <c r="X5" t="n">
         <v>-14433.98027306289</v>
       </c>
-      <c r="Y5" t="n">
-        <v>386.2083336826761</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>6380.724393138067</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>8.038272625164862e-07</v>
@@ -9776,7 +9421,7 @@
         <v>59.93599999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>1612.655629040645</v>
+        <v>202.804877145032</v>
       </c>
       <c r="D6" t="n">
         <v>1.50988e-07</v>
@@ -9809,16 +9454,13 @@
         <v>-15955.65087096711</v>
       </c>
       <c r="Y6" t="n">
-        <v>382.4736754823203</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>209185431.4402277</v>
+        <v>222.5568274334151</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.794745490306424e-07</v>
+        <v>3.198232041373851e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9732745673122102</v>
+        <v>0.9997318275058752</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9471,7 @@
         <v>57.58200000000005</v>
       </c>
       <c r="C7" t="n">
-        <v>1774.678971240392</v>
+        <v>199.0327841737207</v>
       </c>
       <c r="D7" t="n">
         <v>1.50524e-07</v>
@@ -9862,16 +9504,13 @@
         <v>-17405.51411385684</v>
       </c>
       <c r="Y7" t="n">
-        <v>377.2917233827275</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>307775388.5564924</v>
+        <v>228.1840931899332</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.761317038744865e-07</v>
+        <v>3.627383734864578e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9756615362415106</v>
+        <v>0.9990932847764759</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9521,7 @@
         <v>56.41200000000003</v>
       </c>
       <c r="C8" t="n">
-        <v>2253.832274003391</v>
+        <v>56.41200000000003</v>
       </c>
       <c r="D8" t="n">
         <v>1.50224e-07</v>
@@ -9914,11 +9553,10 @@
       <c r="X8" t="n">
         <v>-18921.75319589645</v>
       </c>
-      <c r="Y8" t="n">
-        <v>372.3037068619515</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>304006294.589339</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.73812905593134e-07</v>
@@ -9935,7 +9573,7 @@
         <v>54.548</v>
       </c>
       <c r="C9" t="n">
-        <v>3882.088128335772</v>
+        <v>256.2100650171334</v>
       </c>
       <c r="D9" t="n">
         <v>1.50088e-07</v>
@@ -9968,16 +9606,13 @@
         <v>-20167.59559117172</v>
       </c>
       <c r="Y9" t="n">
-        <v>367.5314693890718</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>38393525.61343922</v>
+        <v>159.9893498241421</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.720479364240339e-07</v>
+        <v>2.398932455918836e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9788022244373353</v>
+        <v>0.9997616556204083</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9623,7 @@
         <v>53.39799999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>4170.860138173474</v>
+        <v>53.39799999999997</v>
       </c>
       <c r="D10" t="n">
         <v>1.50031e-07</v>
@@ -10020,11 +9655,10 @@
       <c r="X10" t="n">
         <v>-21028.19098596118</v>
       </c>
-      <c r="Y10" t="n">
-        <v>363.1266844353947</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>148258672.0502665</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.709239146154232e-07</v>
@@ -10041,7 +9675,7 @@
         <v>51.69199999999995</v>
       </c>
       <c r="C11" t="n">
-        <v>6008.259011873782</v>
+        <v>211.7564062082713</v>
       </c>
       <c r="D11" t="n">
         <v>1.50046e-07</v>
@@ -10074,16 +9708,13 @@
         <v>-21600.45072945064</v>
       </c>
       <c r="Y11" t="n">
-        <v>351.5106155674105</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5898.008891584643</v>
+        <v>202.413414098264</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.235512271654899e-06</v>
+        <v>3.742161832806621e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7930270991523264</v>
+        <v>0.9968396660540553</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 48.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>2.162356193760762e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9993911230584693</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97.28100000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1432.901734792091</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.5369e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.914</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2785191139918084</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8892966623409297</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.899770046115609</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.545052544910743</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17.59692457140864</v>
+      </c>
+      <c r="M12" t="n">
+        <v>86.56603481257713</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16.66503770425023</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8204.891919915419</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-815.9505587833364</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.228960720397941e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9431952925240271</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92.44900000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9503294579619864</v>
+      </c>
+      <c r="D13" t="n">
+        <v>327.1735300719598</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2283293558294362</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.50123e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-84.77500000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1975051182707226</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9346805205780346</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.752465745704763</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.497089253516159</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.82244741267145</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.30161957723325</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>21.21769492893483</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-10274.91400160013</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>157.1277484218515</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.671042003626162e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9994527181932028</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87.62200000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9007103134219427</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1599.006660243159</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.115922063193795</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.48329e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.27200000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.08309429603688401</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6385647022010473</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.780933521589282</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.698020984226417</v>
+      </c>
+      <c r="L14" t="n">
+        <v>27.40069509148915</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.68508427257339</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24.73722866194396</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-11761.52385783254</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-982.4687397163422</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.938977506697763e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9588141492459019</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>88.428</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9089955900946741</v>
+      </c>
+      <c r="D15" t="n">
+        <v>303.8111877194315</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2120251377625092</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.47135e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.61799999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7439905342003544</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.719694749076641</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.565945310021589</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.125897675567046</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31.59376441137767</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.03375180799974</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29.12820758641326</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-13739.04637824691</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>170.1077779460336</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.902290096057767e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.999104330417934</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84.20600000000002</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8655955428089762</v>
+      </c>
+      <c r="D16" t="n">
+        <v>315.8458042441073</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2204239108482449</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.46258e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6228190897135595</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.173026524571004</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.235963805513922</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.128728747136414</v>
+      </c>
+      <c r="L16" t="n">
+        <v>35.76462183950861</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.22545674805478</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>32.27729620983263</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14992.52478000839</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>154.1037054379253</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.815953656076665e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9995721699112194</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78.577</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8077322395945765</v>
+      </c>
+      <c r="D17" t="n">
+        <v>265.5081306421471</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1852940255394913</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.45626e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.108</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3137097772139661</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.820794075833813</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.408307774974133</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.825903441310532</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40.31971103848736</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.3652592097021</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>35.03933574510697</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16004.11879585791</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>201.4352652547699</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.440057999867442e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9990746625798433</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>76.40300000000002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7853846074773082</v>
+      </c>
+      <c r="D18" t="n">
+        <v>264.9243434706683</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1848866094848492</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.45096e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.283</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2476589464368071</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8629026124045522</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.255831732782069</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.27828465846257</v>
+      </c>
+      <c r="L18" t="n">
+        <v>45.09585069468846</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.48841713881001</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>37.89569692670363</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-17093.42473464095</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>196.2806475636547</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.390386500916465e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9993780192629763</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>73.80000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7586270700342308</v>
+      </c>
+      <c r="D19" t="n">
+        <v>305.0517612286749</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2128909148630048</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.44661e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.429</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2578187686538379</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9907504140241142</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.087084290957009</v>
+      </c>
+      <c r="K19" t="n">
+        <v>37.67098400262385</v>
+      </c>
+      <c r="L19" t="n">
+        <v>49.33138541099138</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.5885531646659</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>40.58543868891009</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-18100.59079228311</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>149.6577730926533</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.839224918288388e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9999355477542364</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>73.86100000000005</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7592541195094628</v>
+      </c>
+      <c r="D20" t="n">
+        <v>288.9241535643721</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.201635706447305</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.44317e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.574</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4573048808325964</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.195093895634331</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.344799995336352</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25.40769635172419</v>
+      </c>
+      <c r="L20" t="n">
+        <v>54.72323278274322</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.73948548702943</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>45.44694630504332</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-20143.10255451971</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>169.2679054610318</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.154930817398146e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9999451433867904</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>70.34899999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7231525169354754</v>
+      </c>
+      <c r="D21" t="n">
+        <v>285.1555891610266</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1990056835281881</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.43999e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.676</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2825786075686996</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.016218396030067</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.104335840771005</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26.1678314033804</v>
+      </c>
+      <c r="L21" t="n">
+        <v>58.98666517192155</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.77140104859826</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>46.62790695293129</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-20407.89935235872</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>166.0526291732602</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.162356193760762e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9993911230584693</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>3.43726826127944e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9999115871440918</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>102.808</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>302.0808069289747</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.52874e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.753</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2696636606650077</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9458056496175236</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.975931199999464</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.382345947683587</v>
+      </c>
+      <c r="L23" t="n">
+        <v>41.26996032494195</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.2343794523108</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>32.44051619648437</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-16105.91496641924</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>185.7148149929809</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.940925286281776e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9982916922972535</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>89.36900000000003</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.869280600731461</v>
+      </c>
+      <c r="D24" t="n">
+        <v>269.198291389822</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8911466243968156</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.51864e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-86.194</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.229347628314319</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9524649153600583</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.096320048765808</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.785509851517824</v>
+      </c>
+      <c r="L24" t="n">
+        <v>53.16962857414322</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.51704152719303</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>38.62750425171154</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-18438.47981940698</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>219.338914453536</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.147277280129455e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9829001782162861</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>84.33500000000004</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8203155396467205</v>
+      </c>
+      <c r="D25" t="n">
+        <v>282.8867625922326</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9364605632119651</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.51232e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.414</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1240006760837866</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6636793936162532</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.984553600201311</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.693141499371841</v>
+      </c>
+      <c r="L25" t="n">
+        <v>62.43819918072323</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.63173771670471</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>41.86689066823836</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-19638.79252253433</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>198.2669212976955</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.681377745920006e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.987542643019433</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>82.63200000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8037506808808654</v>
+      </c>
+      <c r="D26" t="n">
+        <v>262.3742070832591</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8685563632811287</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.50798e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.556</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3380097135004396</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.056556217023782</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.158548300650653</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.870069208000045</v>
+      </c>
+      <c r="L26" t="n">
+        <v>70.01049461869066</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.75344427271543</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>45.95601924830282</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21341.5930482217</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>209.844562498416</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.499187417156764e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.998707139828021</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80.65300000000002</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7845012061318188</v>
+      </c>
+      <c r="D27" t="n">
+        <v>360.7041820009157</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.194065209464713</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.50537e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.657</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2100806654701562</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.026511182952121</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.26223883386594</v>
+      </c>
+      <c r="K27" t="n">
+        <v>24.18793284944645</v>
+      </c>
+      <c r="L27" t="n">
+        <v>76.6313612243556</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.82438455887657</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>48.72999853220286</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-22379.84733407621</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>99.66626169458365</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.420834044135358e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.999438773684526</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>76.928</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7482686172282313</v>
+      </c>
+      <c r="D28" t="n">
+        <v>254.243844401594</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8416418341380154</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.5037e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.748</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1833774597281363</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7778709796599224</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.03883812893056</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.697095144141651</v>
+      </c>
+      <c r="L28" t="n">
+        <v>81.24013916264497</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.81374997364514</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>48.29301691202554</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21849.67980895728</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>210.6077219947007</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.75661414324168e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9965592843310509</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>76.46300000000002</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7437456229087234</v>
+      </c>
+      <c r="D29" t="n">
+        <v>266.1573950070119</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8810801245959029</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.50231e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.812</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2614877646672792</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.113166877173368</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.280960377016453</v>
+      </c>
+      <c r="K29" t="n">
+        <v>30.74926624145304</v>
+      </c>
+      <c r="L29" t="n">
+        <v>87.27206229238766</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.91345318528198</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>52.72567202186245</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-23681.33456379035</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>187.6467997577255</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.219294871637259e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9998933930290794</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7215391798303635</v>
+      </c>
+      <c r="D30" t="n">
+        <v>248.3060747169789</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8219856045848044</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.50176e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.881</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3206493379548573</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.015220060371274</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.084853166688043</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25.43408753814591</v>
+      </c>
+      <c r="L30" t="n">
+        <v>91.42927357425376</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.92842992015298</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>53.4627646988959</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-23736.44190164505</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>207.1137547001761</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.654276268790771e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9996948349284364</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>71.96299999999997</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6999747101392885</v>
+      </c>
+      <c r="D31" t="n">
+        <v>247.8692580407463</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.82053957866653</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.50105e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.923</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2978506581875404</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.044156552647077</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.121535501014364</v>
+      </c>
+      <c r="K31" t="n">
+        <v>24.61629948078551</v>
+      </c>
+      <c r="L31" t="n">
+        <v>94.9368022083093</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.9251467226117</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>53.29942164382769</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-23408.91966239561</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>209.0649379250879</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.83026466901215e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9997528844243019</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>70.26400000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6834487588514514</v>
+      </c>
+      <c r="D32" t="n">
+        <v>359.81033543625</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.191106244366093</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.50078e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.97199999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2137437464084619</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.037070547304311</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.162719463258724</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20.2050340351472</v>
+      </c>
+      <c r="L32" t="n">
+        <v>98.81668570612396</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.95413911794064</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>54.77728131786293</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-23837.61526272434</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>79.76588927675938</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.373068469893434e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9998284119826942</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>69.63499999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6773305579332347</v>
+      </c>
+      <c r="D33" t="n">
+        <v>355.19686296422</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.175833931904631</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.50054e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-87.015</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1988034368267566</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.132717307688328</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.23356486320051</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20.52677283187985</v>
+      </c>
+      <c r="L33" t="n">
+        <v>101.60450815865</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.97330415228687</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>55.80001806650652</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-24053.49785526302</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>80.65462608721339</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.390117113637715e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9999095533534819</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>69.911</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6800151739164269</v>
+      </c>
+      <c r="D34" t="n">
+        <v>237.0559286062417</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7847434301311911</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.50039e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-87.054</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.670079027072413</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.249726827230075</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.512717680857185</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6.753610657823997</v>
+      </c>
+      <c r="L34" t="n">
+        <v>104.7355091822837</v>
+      </c>
+      <c r="M34" t="n">
+        <v>89.05634127267498</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>60.71114173928162</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-26034.30608589084</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>200.8629523066157</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.710467316230492e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9987103315910405</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>66.96699999999998</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6513792700957123</v>
+      </c>
+      <c r="D35" t="n">
+        <v>234.5000593863414</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7762825509184934</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.50045e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-87.084</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2502710190124335</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8986334283192537</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.869112672557594</v>
+      </c>
+      <c r="K35" t="n">
+        <v>17.08394057978147</v>
+      </c>
+      <c r="L35" t="n">
+        <v>104.8937579522922</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.98416076772514</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>56.39649862448768</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-23863.41449898794</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>202.1894667159897</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.848981238297262e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9981758816939407</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>66.23099999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6442202941405338</v>
+      </c>
+      <c r="D36" t="n">
+        <v>234.7138962583606</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7769904306219183</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.5005e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-87.127</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3648011505785648</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.162540493258979</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.289031284553619</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.61590745313985</v>
+      </c>
+      <c r="L36" t="n">
+        <v>111.1543498405293</v>
+      </c>
+      <c r="M36" t="n">
+        <v>89.03575403470118</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>59.41468493358725</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-24961.21932336222</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>210.1553197391842</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.616931627405246e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9900758583921691</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>63.53700000000003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6180161076958995</v>
+      </c>
+      <c r="D37" t="n">
+        <v>231.9173994198526</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.767732984354683</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.50046e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-87.158</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1596009830547203</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8772304227963224</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.99464212323835</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.530132835311278</v>
+      </c>
+      <c r="L37" t="n">
+        <v>112.8762218567926</v>
+      </c>
+      <c r="M37" t="n">
+        <v>89.00221894496224</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>57.4173934577143</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-23863.70018466999</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>198.8914687692244</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.930079833374285e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9987675859404354</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>63.39699999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6166543459652944</v>
+      </c>
+      <c r="D38" t="n">
+        <v>229.9879156209014</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.761345674222117</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.50041e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-87.187</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3281822149982813</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9912454880045429</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.064203467877868</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>112.4437319603085</v>
+      </c>
+      <c r="M38" t="n">
+        <v>89.03097801498369</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>59.12179227429597</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-24377.9248764107</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>219.6079925445396</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.629995180516827e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9551066968414988</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>63.50899999999996</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6177437553497779</v>
+      </c>
+      <c r="D39" t="n">
+        <v>227.6343841834354</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7535546084427562</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.50048e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-87.211</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4441947042709506</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.255803127973852</v>
+      </c>
+      <c r="J39" t="n">
+        <v>55.00818467122109</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9.67962964093946</v>
+      </c>
+      <c r="L39" t="n">
+        <v>114.7526237705915</v>
+      </c>
+      <c r="M39" t="n">
+        <v>89.10550813941626</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>64.04879359737185</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-26268.55606877112</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>200.296845388964</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.973865275378797e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9998776576760682</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>61.73399999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6004785619796124</v>
+      </c>
+      <c r="D40" t="n">
+        <v>211.0146684141716</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6985371581842517</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.50077e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-87.254</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4747856971071805</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.042027925832634</v>
+      </c>
+      <c r="J40" t="n">
+        <v>42.78042843151687</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6.891717298405903</v>
+      </c>
+      <c r="L40" t="n">
+        <v>119.9015352564753</v>
+      </c>
+      <c r="M40" t="n">
+        <v>89.08940839896985</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>62.91619141931726</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-25535.82191588283</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>213.1225465351649</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.515370221670425e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9986622725726273</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>59.654</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5802466734106295</v>
+      </c>
+      <c r="D41" t="n">
+        <v>208.8157850328546</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6912580350791746</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.50097e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-87.276</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2040193429260758</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9919577877974927</v>
+      </c>
+      <c r="J41" t="n">
+        <v>36.1502654965991</v>
+      </c>
+      <c r="K41" t="n">
+        <v>66.19346428790335</v>
+      </c>
+      <c r="L41" t="n">
+        <v>122.6586426665235</v>
+      </c>
+      <c r="M41" t="n">
+        <v>89.05474568298867</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>60.60864275585362</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-24340.3247656731</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>209.6388141425477</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.213652509960925e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9995944081903956</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>60.66199999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5900513578709826</v>
+      </c>
+      <c r="D42" t="n">
+        <v>204.4035955807233</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6766520443941435</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.50091e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-87.315</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5260021767871218</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.330083738778998</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.401578942904233</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39.04956925063428</v>
+      </c>
+      <c r="L42" t="n">
+        <v>128.5799767080835</v>
+      </c>
+      <c r="M42" t="n">
+        <v>89.1488362482192</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>67.30968568500788</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-26900.50165895274</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>230.1141800703865</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>6.732830979713932e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9654047524846984</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58.286</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5669403159287215</v>
+      </c>
+      <c r="D43" t="n">
+        <v>201.231562947208</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6661514347534221</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.50118e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-87.33199999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4389141470815144</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8739192901444751</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7.011982921052152</v>
+      </c>
+      <c r="K43" t="n">
+        <v>60.23869870532217</v>
+      </c>
+      <c r="L43" t="n">
+        <v>126.3151734182323</v>
+      </c>
+      <c r="M43" t="n">
+        <v>89.10539835048284</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>64.04093200722461</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-25303.80680019316</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>212.6762244239966</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.43726826127944e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9999115871440918</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>3.90770989591692e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9999544805896312</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>111.569</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>310.0888555458832</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.4458e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.70699999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3607406132644139</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.03234437970366</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.082609677607008</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.249067598662565</v>
+      </c>
+      <c r="L23" t="n">
+        <v>37.26974350700457</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.18517492560989</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>31.56040640467317</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-16088.81420677342</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>185.7949663973179</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.795939960486342e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9995920556496446</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92.62700000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8302216565533437</v>
+      </c>
+      <c r="D24" t="n">
+        <v>310.8722716663597</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.002526424624637</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.44701e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-86.08</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3606668270657946</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.014285812524864</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.160191964629171</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.151778607673752</v>
+      </c>
+      <c r="L24" t="n">
+        <v>43.56101720680282</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.43713032555434</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>36.65153243247671</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-17721.49634677437</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>174.9898242530357</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.91025757128371e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9991508247994448</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>84.10599999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.753847394885676</v>
+      </c>
+      <c r="D25" t="n">
+        <v>315.6327239240202</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.017878321903499</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.44392e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.297</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.07433704226585361</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5154553816086164</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.644026512101666</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.371633975759122</v>
+      </c>
+      <c r="L25" t="n">
+        <v>49.59152434380715</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.53373275930893</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>39.06741522660464</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-18470.5222536253</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>163.3215712579876</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.836786490894029e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9992115828990913</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>85.24400000000003</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7640473608260361</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1525.629145158901</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.919974123136963</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.44064e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.446</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3879423674139348</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.321138573306015</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.484484522982701</v>
+      </c>
+      <c r="K26" t="n">
+        <v>35.02126843830591</v>
+      </c>
+      <c r="L26" t="n">
+        <v>55.78664500530981</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.72532217965134</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>44.94180848117169</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21133.16091644632</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-932.6113921505529</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.723974774484817e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9721783028520264</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>81.00900000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7260887881042225</v>
+      </c>
+      <c r="D27" t="n">
+        <v>340.3874674963857</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.097709451367301</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.438e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.58199999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09471439571052782</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9432058198692791</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.054031358628662</v>
+      </c>
+      <c r="K27" t="n">
+        <v>30.98208550230149</v>
+      </c>
+      <c r="L27" t="n">
+        <v>61.06147280806506</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.76879421157902</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>46.52915119437498</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-21547.56147767845</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>165.7588881287487</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.988594928495843e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8355354172667996</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79.471</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7123035968772687</v>
+      </c>
+      <c r="D28" t="n">
+        <v>269.0271761684735</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8675809251347508</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.43573e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.68300000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1428568968535594</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8993657744343769</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.994454079773701</v>
+      </c>
+      <c r="K28" t="n">
+        <v>37.66387194752814</v>
+      </c>
+      <c r="L28" t="n">
+        <v>66.2705917233327</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.84376734030843</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>49.54712289458529</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-22702.57419919123</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>195.5602495041686</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.22115860339817e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9998656692785385</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>76.327</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6841237261246402</v>
+      </c>
+      <c r="D29" t="n">
+        <v>259.2807418031464</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8361498234004775</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.43369e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.782</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2142710672691781</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9156098085717993</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.043763660906011</v>
+      </c>
+      <c r="K29" t="n">
+        <v>19.46081359100852</v>
+      </c>
+      <c r="L29" t="n">
+        <v>72.02293229990379</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.88027298043149</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>51.16290317173809</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-23160.91605284272</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>201.8127652165605</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.420385874137379e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9986285993514818</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74.90300000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.671360324104366</v>
+      </c>
+      <c r="D30" t="n">
+        <v>256.5700748781208</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.827408242151923</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.43237e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.855</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2230673548169933</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9928664383075485</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.431619955252782</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.403966145058472</v>
+      </c>
+      <c r="L30" t="n">
+        <v>76.83572165323311</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.9374410821389</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>53.91626756947566</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-24186.02289824299</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>201.2964353720747</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.466400525135444e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9984057112929668</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>74.71899999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6697111204725326</v>
+      </c>
+      <c r="D31" t="n">
+        <v>251.0527976284598</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8096156735026937</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.43113e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.93300000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4718952694591041</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.099263689411906</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.407490499757435</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>82.43393516974481</v>
+      </c>
+      <c r="M31" t="n">
+        <v>89.02204433206558</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>58.58160772475124</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-26103.31153531824</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>203.5944863506237</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.493936170793275e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9997670932683376</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>71.50599999999997</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6409127983579664</v>
+      </c>
+      <c r="D32" t="n">
+        <v>249.1182313078403</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8033769252019403</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.43053e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.997</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2366661892358034</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9800102674151965</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.219615326585745</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>87.50521049502312</v>
+      </c>
+      <c r="M32" t="n">
+        <v>89.00696568856972</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>57.6919062531543</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-25393.93913333458</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>212.3416845813411</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.870593303514115e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9994735644289109</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>71.74599999999998</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.643063933529923</v>
+      </c>
+      <c r="D33" t="n">
+        <v>248.4481792839254</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8012160864232123</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.42966e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-87.053</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4483214437894611</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.233166158226024</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.83031508077826</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.318654377395548</v>
+      </c>
+      <c r="L33" t="n">
+        <v>92.70791309757264</v>
+      </c>
+      <c r="M33" t="n">
+        <v>89.08710479955295</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>62.75740195408181</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-27463.06474505195</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>202.8001575796897</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.775777760675794e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9979717856154389</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>70.08499999999998</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6281762855273415</v>
+      </c>
+      <c r="D34" t="n">
+        <v>250.6382087094215</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8082786731183735</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.42916e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-87.11499999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4451871291190626</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.263405927147861</v>
+      </c>
+      <c r="J34" t="n">
+        <v>48.85694213831647</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.323086967196212</v>
+      </c>
+      <c r="L34" t="n">
+        <v>98.75776030446136</v>
+      </c>
+      <c r="M34" t="n">
+        <v>89.12278836452018</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>65.3106962503746</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-28329.992125253</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>197.5407477945222</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.655353461958467e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9994014319779001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>68.21199999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6113884681228655</v>
+      </c>
+      <c r="D35" t="n">
+        <v>242.9201288982287</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.783388775680409</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.42854e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-87.161</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4296553433693044</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.095843051671861</v>
+      </c>
+      <c r="J35" t="n">
+        <v>16.38514662091575</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>103.1579367081166</v>
+      </c>
+      <c r="M35" t="n">
+        <v>89.11322531876897</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>64.60627004950472</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-27727.52163474765</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>224.5850668231283</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.274830042532587e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9545410082855696</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>67.95099999999996</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6090491086233627</v>
+      </c>
+      <c r="D36" t="n">
+        <v>240.1611754074034</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7744914759500836</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.42828e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-87.197</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5464686076555584</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.291373861205821</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10.63488624931479</v>
+      </c>
+      <c r="L36" t="n">
+        <v>105.5865994965467</v>
+      </c>
+      <c r="M36" t="n">
+        <v>89.1650016430421</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>68.61297714370748</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-29245.62761920104</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>204.9182044822032</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.837849329653783e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9998996563786251</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>65.00800000000004</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5826708135772484</v>
+      </c>
+      <c r="D37" t="n">
+        <v>237.2570638442114</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7651260585503529</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.42802e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-87.23699999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2617129184509353</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.106646789018974</v>
+      </c>
+      <c r="J37" t="n">
+        <v>30.95825897632223</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.410231164184812</v>
+      </c>
+      <c r="L37" t="n">
+        <v>108.3046587895985</v>
+      </c>
+      <c r="M37" t="n">
+        <v>89.12779420332863</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>65.68559145130547</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-27662.5367367368</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>206.2806398823837</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.04859866647148e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.99755419704073</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>64.149</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5749715422742876</v>
+      </c>
+      <c r="D38" t="n">
+        <v>234.3145421561315</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7556367730263703</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.42778e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-87.282</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2187397352297945</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.071962052064052</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>13.56497065075459</v>
+      </c>
+      <c r="L38" t="n">
+        <v>113.2701893536862</v>
+      </c>
+      <c r="M38" t="n">
+        <v>89.14943303210345</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>67.35691917241277</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-28123.08245496312</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>205.0780738453774</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.956790757059985e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9998302965306569</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>63.66700000000003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5706513458039422</v>
+      </c>
+      <c r="D39" t="n">
+        <v>213.4125900894725</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6882304419285854</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.42772e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-87.325</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3581881191898013</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.250298229896885</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7.491851142777003</v>
+      </c>
+      <c r="L39" t="n">
+        <v>118.6683724647427</v>
+      </c>
+      <c r="M39" t="n">
+        <v>89.19919001883319</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>71.54262546588316</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-29665.81517515678</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>238.5629575764631</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.688398341481341e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9648337455444731</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>63.09300000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5655065475176797</v>
+      </c>
+      <c r="D40" t="n">
+        <v>202.6409849358399</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6534932852685366</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.42793e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-87.371</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4640323302785433</v>
+      </c>
+      <c r="I40" t="n">
+        <v>42.75605392963757</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>73.94917913957804</v>
+      </c>
+      <c r="L40" t="n">
+        <v>129.1541052059849</v>
+      </c>
+      <c r="M40" t="n">
+        <v>89.23578150019959</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>74.96858783113515</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-30852.6232540144</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>230.8063187801345</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.635483051003357e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9999503057725476</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>59.72399999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.535309987541342</v>
+      </c>
+      <c r="D41" t="n">
+        <v>198.0625116015227</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6387282485623408</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.42774e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-87.401</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>55.55029812630103</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>64.83841105431515</v>
+      </c>
+      <c r="L41" t="n">
+        <v>131.1443200943292</v>
+      </c>
+      <c r="M41" t="n">
+        <v>89.14549169996715</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>67.04619651680511</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-27211.05566833534</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>229.0799472618826</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.842400251398738e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9943129967803334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>60.34000000000003</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.540831234482697</v>
+      </c>
+      <c r="D42" t="n">
+        <v>193.1942752392436</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6230287602537107</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.42781e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-87.428</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4271466358948189</v>
+      </c>
+      <c r="I42" t="n">
+        <v>15.67132988896301</v>
+      </c>
+      <c r="J42" t="n">
+        <v>24.82036928695099</v>
+      </c>
+      <c r="K42" t="n">
+        <v>11.75334142518138</v>
+      </c>
+      <c r="L42" t="n">
+        <v>135.2538130901161</v>
+      </c>
+      <c r="M42" t="n">
+        <v>89.24036593942184</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>75.42108146753357</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-30491.36332095984</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>231.709686596693</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.878995616051365e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9996370042721919</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>60.12399999999997</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5388952128279357</v>
+      </c>
+      <c r="D43" t="n">
+        <v>187.5113027491251</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6047018439892931</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.42815e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-87.461</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.615237403643917</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>39.36634948581876</v>
+      </c>
+      <c r="K43" t="n">
+        <v>40.41685682396033</v>
+      </c>
+      <c r="L43" t="n">
+        <v>138.396966705116</v>
+      </c>
+      <c r="M43" t="n">
+        <v>89.2594148876689</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>77.36124812118389</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-31030.1220791261</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>233.7932939942067</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.90770989591692e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9999544805896312</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>4.073067754415299e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9646357305701903</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>269.4039876300928</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.44567e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-84.624</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1932201611715378</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8282660769631874</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.50892068625401</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.110258333208687</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.99935931064937</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.19793351182348</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>20.43138299841736</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-10804.47260449541</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>238.1116452093167</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25960991467633e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9989744797076745</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>85.50400000000002</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6577736748980691</v>
+      </c>
+      <c r="D13" t="n">
+        <v>323.3622188285124</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.2002874258584</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.46029e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-85.343</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.04681824688339607</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6514626612367653</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.866814762570976</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.659625920032692</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27.30058811349939</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.68962738094933</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24.78592478400139</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-11630.28770275351</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>147.5056133252461</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.642945248370354e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9997883603506084</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>77.54300000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5965305023463343</v>
+      </c>
+      <c r="D14" t="n">
+        <v>300.2336642437897</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.114436600901498</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.45557e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.767</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3148555314555037</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8217435698194462</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.925040907165875</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.810523464519012</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.51110441032063</v>
+      </c>
+      <c r="M14" t="n">
+        <v>88.03664702988991</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>29.17119467278279</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-13296.59635142475</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>165.5217311956595</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.973322362407135e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9987568830356022</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>73.39400000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.564612662512501</v>
+      </c>
+      <c r="D15" t="n">
+        <v>227.4148239989399</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8441405266472656</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.44921e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-86.07299999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1347412486345415</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8639631439455213</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.941048867293506</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.878700243864679</v>
+      </c>
+      <c r="L15" t="n">
+        <v>37.95561996195787</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.28014656513224</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>33.30433220507999</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-14939.02966586925</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>240.9143653052786</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.250445342716278e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9974711727769503</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>71.78499999999997</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5522347872913298</v>
+      </c>
+      <c r="D16" t="n">
+        <v>226.6298459381427</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8412267685113799</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.44382e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.297</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4642302347336944</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.034733779351052</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.302090190429891</v>
+      </c>
+      <c r="K16" t="n">
+        <v>42.50426549670706</v>
+      </c>
+      <c r="L16" t="n">
+        <v>43.59100676048639</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.46697743725498</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>37.36546844546758</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-16558.87633341621</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>231.0936176368125</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.139242071615511e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9955605933966244</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>69.63799999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5357181321640124</v>
+      </c>
+      <c r="D17" t="n">
+        <v>237.3418652632969</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.880988686734589</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.43966e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.476</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3484248521515291</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.272318903749826</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.073765109404044</v>
+      </c>
+      <c r="K17" t="n">
+        <v>51.70685708765008</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48.58758612244542</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.60767135371988</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>41.14294496942372</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-17995.61827354145</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>216.2502155485615</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.939482865584448e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9972100962473501</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>67.887</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5222478652204016</v>
+      </c>
+      <c r="D18" t="n">
+        <v>215.3625670600274</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7994037837173096</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.43633e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.624</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.430249316114006</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.179586645343728</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.438375833633839</v>
+      </c>
+      <c r="K18" t="n">
+        <v>34.47260734172169</v>
+      </c>
+      <c r="L18" t="n">
+        <v>53.83833662679709</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.72244516517623</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>44.84056746076497</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-19367.25000866836</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>249.0950567968178</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.603167188134894e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9740866539093019</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>63.94400000000002</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4919147626740519</v>
+      </c>
+      <c r="D19" t="n">
+        <v>285.7207344917549</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.060566092600181</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.43368e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.754</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1211278767167347</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8575363153693312</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.248319701926778</v>
+      </c>
+      <c r="K19" t="n">
+        <v>24.59997745335877</v>
+      </c>
+      <c r="L19" t="n">
+        <v>58.84212245370388</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.77241592232483</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>46.66646719615327</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-19817.1919479509</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>152.3496864065575</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.99069007762569e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9999683979653243</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>62.01099999999997</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4770443880298482</v>
+      </c>
+      <c r="D20" t="n">
+        <v>296.2345579681313</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.099592328139101</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.43162e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.863</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1603822997649117</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8848762452763849</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.062226087585731</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14.39674161085175</v>
+      </c>
+      <c r="L20" t="n">
+        <v>63.65532405535298</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.84041693729746</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>49.40392662251721</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-20694.79226048642</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>136.0238053193072</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.854862673629728e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9999747873922931</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>62.42699999999996</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4802446342026306</v>
+      </c>
+      <c r="D21" t="n">
+        <v>269.9749219144816</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.002119249567949</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.43006e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.955</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6452256822340328</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.443121094046478</v>
+      </c>
+      <c r="J21" t="n">
+        <v>39.68419032078065</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>68.5835508410199</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.95390704849997</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>54.76512660680767</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-22756.50704360376</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>176.2845162334381</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.073067754415299e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9646357305701903</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>7.149229435143403e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9871464169076573</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106.705</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>293.2546290745512</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.46314e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.242</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2059864383734093</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.86868901378242</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.845211220641163</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.428998334951572</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28.17510476110219</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.76498880630163</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>25.62256305199043</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-12826.70080709606</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>201.7904556659632</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.046577140946956e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9996772920320494</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>89.92000000000002</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8426971557096671</v>
+      </c>
+      <c r="D24" t="n">
+        <v>304.7782054152098</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.039295462707697</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.45624e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.831</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1533933466527184</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6183815582476688</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.782174170631141</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.463221784909456</v>
+      </c>
+      <c r="L24" t="n">
+        <v>36.23805081436807</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.19650747490451</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>31.75885383049608</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-15183.47037551354</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>182.9754801086265</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.02976220376825e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9999941565406726</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>86.75099999999998</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8129984536807084</v>
+      </c>
+      <c r="D25" t="n">
+        <v>305.8352333355332</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.042899934097149</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.44916e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.179</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2705555679152608</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.01210002301506</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.482200100315166</v>
+      </c>
+      <c r="K25" t="n">
+        <v>30.82422203876305</v>
+      </c>
+      <c r="L25" t="n">
+        <v>44.94538629382376</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.49949242872881</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>38.17553551956504</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-17996.41734846085</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>170.6875169611787</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.930661947361007e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9993475535750741</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83.63099999999997</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7837589616231665</v>
+      </c>
+      <c r="D26" t="n">
+        <v>343.2677661395488</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.170545089851875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.44353e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.414</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2707273831914636</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8999759155717224</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.184741674272713</v>
+      </c>
+      <c r="K26" t="n">
+        <v>22.6341276390077</v>
+      </c>
+      <c r="L26" t="n">
+        <v>52.87542163232857</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.6738344489425</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>43.19637718867707</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20102.8191344386</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>125.159973486184</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.554459812310296e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9997526767273479</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>81.73200000000003</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7659622323227594</v>
+      </c>
+      <c r="D27" t="n">
+        <v>269.1671651378492</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9178616071203483</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.43943e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.58499999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2448698978735633</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9297276202254495</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.083110923611488</v>
+      </c>
+      <c r="K27" t="n">
+        <v>9.680965533797732</v>
+      </c>
+      <c r="L27" t="n">
+        <v>59.9148325463306</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.80615247011848</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>47.98559777798011</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-22072.28940661754</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>199.9365915232861</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.410996477277386e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9988335977968016</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79.34900000000005</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.743629633100605</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1602.863302368509</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.46577323408944</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.43615e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.726</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3219977293189288</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.178421286101475</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.47936003148988</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>67.64333315961575</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.89680133452164</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>51.92963029835049</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-23590.42694492583</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-1015.986702566714</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.679803956322664e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9756979943363299</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>77.149</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7230120425472097</v>
+      </c>
+      <c r="D29" t="n">
+        <v>257.2869694352985</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8773500703032076</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.43417e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.84399999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2192921871439489</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.063379702293585</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.282844245367996</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>75.15281033102391</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.96059567111276</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>55.11762121378192</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-24738.50326950821</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>199.8584779675226</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.452871375116573e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9984306832324656</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>73.39099999999996</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6877934492291831</v>
+      </c>
+      <c r="D30" t="n">
+        <v>251.0691455371995</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8561472544509187</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.43228e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.944</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.05118988029425977</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.969596873840784</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.839921183871087</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>82.0414138919255</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.97844311556345</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>56.08078117214754</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-24829.51235185706</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>205.808493495103</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.666382843830977e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9986994122857512</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>72.53700000000003</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6797900754416386</v>
+      </c>
+      <c r="D31" t="n">
+        <v>248.3607063981081</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8469114611485632</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.43116e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-87.02</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1742507461667912</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.062165249780565</v>
+      </c>
+      <c r="J31" t="n">
+        <v>42.60515217841277</v>
+      </c>
+      <c r="K31" t="n">
+        <v>16.85627625961427</v>
+      </c>
+      <c r="L31" t="n">
+        <v>89.14077185931664</v>
+      </c>
+      <c r="M31" t="n">
+        <v>89.04388766450577</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>59.92021959529691</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-26313.31105928323</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>202.0075203345557</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.614532037959664e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9981278330532738</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>72.33399999999995</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6778876341314836</v>
+      </c>
+      <c r="D32" t="n">
+        <v>364.7651605422383</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.243851330474677</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.43021e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-87.07899999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5395662438290054</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.236436662336845</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.4296171345155942</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6.253989809740849</v>
+      </c>
+      <c r="L32" t="n">
+        <v>93.30280411486554</v>
+      </c>
+      <c r="M32" t="n">
+        <v>89.12237823926489</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>65.28017085281029</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-28470.45822842</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>77.88022350298743</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.387939804216694e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9996805370942213</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>71.02100000000002</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6655826812239354</v>
+      </c>
+      <c r="D33" t="n">
+        <v>242.3875251067854</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8265428780159705</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.42966e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-87.14700000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4541478536429603</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.260172077986908</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>63.21899903588657</v>
+      </c>
+      <c r="L33" t="n">
+        <v>103.7831074796338</v>
+      </c>
+      <c r="M33" t="n">
+        <v>89.14996582156013</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>67.39914374254423</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-29121.17547699118</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>198.2849072670195</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.570579836371147e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9995785722118899</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>68.92000000000002</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6458928822454433</v>
+      </c>
+      <c r="D34" t="n">
+        <v>242.2771403458611</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8261664653357249</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.42903e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-87.19499999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3018321585745657</v>
+      </c>
+      <c r="I34" t="n">
+        <v>82.32831890833661</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8.005005775968096</v>
+      </c>
+      <c r="K34" t="n">
+        <v>77.14292714228635</v>
+      </c>
+      <c r="L34" t="n">
+        <v>108.0719001161687</v>
+      </c>
+      <c r="M34" t="n">
+        <v>89.16134179986844</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>68.31351262685321</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-29230.2190850054</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>201.0148819714799</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.846933705082984e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9983688255702891</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>68.77800000000002</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6445621104915424</v>
+      </c>
+      <c r="D35" t="n">
+        <v>239.3322013356098</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8161242060897417</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.42868e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-87.249</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5066352048371567</v>
+      </c>
+      <c r="I35" t="n">
+        <v>15.94403999700256</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>57.07998708018266</v>
+      </c>
+      <c r="L35" t="n">
+        <v>114.7237880779391</v>
+      </c>
+      <c r="M35" t="n">
+        <v>89.20508838239715</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>72.07355137642995</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-30606.60289461131</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>211.6338366294502</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.626669434144762e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9896962979684972</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>66.82499999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6262593130593693</v>
+      </c>
+      <c r="D36" t="n">
+        <v>217.6996840339342</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7423571955912436</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.42845e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-87.29300000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.4212676031016663</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>121.5435319611368</v>
+      </c>
+      <c r="M36" t="n">
+        <v>89.1878417462287</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>70.54283052890734</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-29635.20413203444</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>243.8275687341049</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.039332748715568e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9506938576182017</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>64.565</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.605079424581791</v>
+      </c>
+      <c r="D37" t="n">
+        <v>207.5566077620917</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7077692461909157</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.42846e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-87.334</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2648942239331119</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9.112252316526112</v>
+      </c>
+      <c r="L37" t="n">
+        <v>125.6699085567055</v>
+      </c>
+      <c r="M37" t="n">
+        <v>89.18097761505307</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>69.95153975064504</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-29097.28831433077</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>224.8154737608533</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.445594278495454e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9986173664264046</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>64.21700000000004</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6018180966215271</v>
+      </c>
+      <c r="D38" t="n">
+        <v>199.4041384916333</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6799692783057171</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.42851e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-87.374</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3114374268644638</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>27.13985504973357</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>132.9781427317299</v>
+      </c>
+      <c r="M38" t="n">
+        <v>89.20381774901686</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>71.95851386817088</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-29700.81025677378</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>232.3886044149088</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.932128714187444e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9927565592281482</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>64.08499999999998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6005810411883229</v>
+      </c>
+      <c r="D39" t="n">
+        <v>194.1149799203761</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6619332166484853</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.42865e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-87.40900000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>43.99454425808437</v>
+      </c>
+      <c r="I39" t="n">
+        <v>23.18359254647</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27.52088045515272</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>137.7744023930748</v>
+      </c>
+      <c r="M39" t="n">
+        <v>89.24646638241214</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>76.03174528134205</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-31154.69381519698</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>226.5036853957153</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.598303779029738e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9988112655382395</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>62.55700000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5862611873857835</v>
+      </c>
+      <c r="D40" t="n">
+        <v>188.8564794105574</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6440016991600372</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.42879e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-87.43899999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>21.59470286553895</v>
+      </c>
+      <c r="J40" t="n">
+        <v>24.56384967748641</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>140.8590334000464</v>
+      </c>
+      <c r="M40" t="n">
+        <v>89.24863645460839</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>76.25136383642679</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-30964.85902371214</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>239.4495495668397</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.067580511860567e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9991901375553539</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>60.09100000000001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5631507427018417</v>
+      </c>
+      <c r="D41" t="n">
+        <v>182.3496340088545</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.621813318290357</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.42897e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-87.476</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12.44478804006545</v>
+      </c>
+      <c r="I41" t="n">
+        <v>15.73351564673546</v>
+      </c>
+      <c r="J41" t="n">
+        <v>17.30098360183226</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>147.9102010569628</v>
+      </c>
+      <c r="M41" t="n">
+        <v>89.20082965421912</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>71.68942656224965</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-28783.94244058224</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>241.0362336495347</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.130287454776442e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9999010312556399</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>59.94599999999997</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5617918560517312</v>
+      </c>
+      <c r="D42" t="n">
+        <v>176.0280569302203</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6002567034857289</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.42901e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-87.506</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>119.1564960831399</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.90623181058468</v>
+      </c>
+      <c r="L42" t="n">
+        <v>151.2264079338039</v>
+      </c>
+      <c r="M42" t="n">
+        <v>89.22789773890457</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>74.20300929673849</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-29563.8603020616</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>247.2571882175293</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.604324978974212e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9983571105529503</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58.75299999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5506114989925495</v>
+      </c>
+      <c r="D43" t="n">
+        <v>169.4403819028988</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5777926931200246</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.42914e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-87.544</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1176760841413539</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>23.42304300595208</v>
+      </c>
+      <c r="K43" t="n">
+        <v>7.807477104156312</v>
+      </c>
+      <c r="L43" t="n">
+        <v>162.4989948078652</v>
+      </c>
+      <c r="M43" t="n">
+        <v>89.24567236948779</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>75.95170426001862</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-30011.96598531417</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>262.1284471106711</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.149229435143403e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9871464169076573</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>2.248908705432753e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.998983161837647</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>137.544</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>387.4534038306677</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.46552e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.50700000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1925491804141725</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8744031192422377</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.061046529614885</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.66126614381116</v>
+      </c>
+      <c r="M12" t="n">
+        <v>86.10449652226727</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14.68551327358024</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-7984.234650369973</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>128.9522613124877</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.312359387818177e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9969231243837424</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90.36699999999996</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6570043040772403</v>
+      </c>
+      <c r="D13" t="n">
+        <v>272.3025897117579</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7028008710713631</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.48235e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-84.629</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2284996415826582</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7266619909554093</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.761101557097582</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.369580172889659</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20.91215541130907</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.07975860361393</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19.60322807675627</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9314.38895203223</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>210.7731358136587</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.455248028313882e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.996480938122416</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79.47200000000004</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5777932879660328</v>
+      </c>
+      <c r="D14" t="n">
+        <v>323.823164974972</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8357731840097483</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.47334e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.30800000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2143156944160017</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8092714297959385</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.792694903214924</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.434349116589851</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26.3283097717079</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.63522719125206</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24.21511351682594</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-11088.53596514757</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>140.016998396451</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.681190011920777e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9993049411608173</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>76.82999999999998</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5585848891990923</v>
+      </c>
+      <c r="D15" t="n">
+        <v>539.9716375954924</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.393642776800797</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.46346e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.771</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2925773793764858</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.08152617807323</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.313638347615063</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.027492724142349</v>
+      </c>
+      <c r="L15" t="n">
+        <v>32.2230618559198</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.04764426360474</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29.33563858171446</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-13231.08512810853</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.6946890043136505</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.372216951617967e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.6446633361164164</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>74.733</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.543338858837899</v>
+      </c>
+      <c r="D16" t="n">
+        <v>223.7864516217042</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.577582876828997</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.45553e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.116</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5493934765802965</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.410188971512364</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.34181537244983</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.872209861731851</v>
+      </c>
+      <c r="L16" t="n">
+        <v>38.54666385935315</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.35315008012894</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>34.781554475208</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-15489.98017282409</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>241.7106168739188</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.358402521305719e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9990501234434463</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>71.06799999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5166928401093466</v>
+      </c>
+      <c r="D17" t="n">
+        <v>235.4628808662749</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6077192213006894</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.44965e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.36499999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5074132763959316</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.155739487157557</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.290057272069526</v>
+      </c>
+      <c r="K17" t="n">
+        <v>19.62736838107926</v>
+      </c>
+      <c r="L17" t="n">
+        <v>44.84446357357221</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.52520479587945</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>38.84141000421531</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-17009.14249155791</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>210.983833774033</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.749348799264973e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9980783971590791</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>68.54599999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4983568894317453</v>
+      </c>
+      <c r="D18" t="n">
+        <v>214.3904622401751</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5533322462018481</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.44513e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.56100000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4537020212548949</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.051677884267775</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.403075732523242</v>
+      </c>
+      <c r="K18" t="n">
+        <v>52.71086676115873</v>
+      </c>
+      <c r="L18" t="n">
+        <v>51.25480753216245</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.65921782205136</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>42.72529982653244</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-18422.55495118479</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>230.454446275409</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.170393650990506e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9992727644469968</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>63.29699999999997</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4601945559239222</v>
+      </c>
+      <c r="D19" t="n">
+        <v>252.3527179896063</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.651311139596787</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.44184e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.729</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.02545865638593039</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6785801560275218</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.063260045783374</v>
+      </c>
+      <c r="K19" t="n">
+        <v>30.70849064733947</v>
+      </c>
+      <c r="L19" t="n">
+        <v>57.90919636980156</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.72436859326332</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>44.90820155836985</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-19002.98295864273</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>186.9734102975081</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.485896136148834e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9990046874481924</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>63.92100000000005</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4647312859884839</v>
+      </c>
+      <c r="D20" t="n">
+        <v>291.4616797767105</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7522496302654516</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.43944e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.839</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5841831652325623</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.113043009863059</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.411604419681786</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10.28070185496962</v>
+      </c>
+      <c r="L20" t="n">
+        <v>62.64111663167108</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.85729932848511</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>50.1340238155891</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-21035.60011296409</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>139.6196627967131</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.89076493011693e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9999819802691742</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>60.53500000000003</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4401137090676439</v>
+      </c>
+      <c r="D21" t="n">
+        <v>267.9801386871702</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6916448172546912</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.43775e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.94799999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2279369343337856</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.162545917706498</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.331421121767884</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>68.69587973279077</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.89963523684352</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>52.06340396749443</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-21517.56347801927</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>162.4524184439602</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.248908705432753e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.998983161837647</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>7.557956078597764e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9683447653752802</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>281.0409288674729</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.48966e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.602</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1950795110801365</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8832796669262837</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.83941065869744</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.575998979197658</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.1678380711639</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.18653222989532</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20.34845453634298</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-10250.95867513279</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>215.7120628567772</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.138552558186012e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9996971898150299</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93.166</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8614516874711051</v>
+      </c>
+      <c r="D24" t="n">
+        <v>315.7450499762339</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.123484224339174</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.46983e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.67700000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3243019859946038</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9867661453656977</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.268661707157932</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.531952404968413</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33.95171831545183</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.10521808608657</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>30.22769567372829</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-14561.04227016276</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>215.8737570130483</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.987974887639155e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8513752827962794</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>84.99800000000005</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7859269533055947</v>
+      </c>
+      <c r="D25" t="n">
+        <v>305.5809651733679</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.0873183717574</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.45814e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.13500000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04973484883749691</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7417335734405835</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.212154208197443</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.993358272928293</v>
+      </c>
+      <c r="L25" t="n">
+        <v>44.15111167618797</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.42475046954964</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>36.36334524389967</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-17150.11455124067</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>172.9230421845877</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.957654486844113e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.999158029430076</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83.40699999999998</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.771215903837263</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1464.607258943138</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.211366418568113</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.4504e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.407</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1765171855787109</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8173243094259266</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.033987566480522</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.145366021340354</v>
+      </c>
+      <c r="L26" t="n">
+        <v>53.41866753661562</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.64437714473877</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>42.25739298285365</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-19714.39747457574</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-880.4201650369066</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.740383282684285e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9717846255995866</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>82.41899999999998</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7620804438280167</v>
+      </c>
+      <c r="D27" t="n">
+        <v>274.8772560205911</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9780684156157615</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.44557e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.59699999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5134047949762769</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.249166310547523</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.500535000286332</v>
+      </c>
+      <c r="K27" t="n">
+        <v>28.87007287994195</v>
+      </c>
+      <c r="L27" t="n">
+        <v>63.05085311496209</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.82450896285805</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>48.73515714877987</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-22545.27319824054</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>197.797181227365</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.547863361240342e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9937009562178335</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78.279</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7238002773925105</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1623.193854982974</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.775649338777996</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.44212e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.72799999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2714925078547025</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.967604981890549</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.038417045439191</v>
+      </c>
+      <c r="K28" t="n">
+        <v>50.89110683042671</v>
+      </c>
+      <c r="L28" t="n">
+        <v>70.0346869879685</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.85921148358472</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>50.2180792139989</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-22886.24164235841</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-1033.691006249136</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.689034763179671e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9754734755785102</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>76.28500000000003</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7053629218677766</v>
+      </c>
+      <c r="D29" t="n">
+        <v>258.4547523666612</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9196338533614001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.43979e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.825</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2852091473322986</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9413860218299669</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.934828154734594</v>
+      </c>
+      <c r="K29" t="n">
+        <v>43.40849476679223</v>
+      </c>
+      <c r="L29" t="n">
+        <v>75.8719893605862</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.91292527282339</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>52.70006088901937</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-23744.98673057721</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>200.8296659418979</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.46755963144936e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.998322827495478</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74.70000000000005</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6907073509015262</v>
+      </c>
+      <c r="D30" t="n">
+        <v>252.1536928203679</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8972134195417244</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.43841e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.91200000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2687994240041698</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9695587177550111</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.967428379470031</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30.42269536762668</v>
+      </c>
+      <c r="L30" t="n">
+        <v>82.30315231334518</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.9661537017887</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>55.41400228333963</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-24730.50644335342</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>203.3103995299852</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.506957320154795e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.999577645628526</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>75.37799999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6969764216366158</v>
+      </c>
+      <c r="D31" t="n">
+        <v>249.8240601280796</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8889241191125089</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.43722e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.982</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5642957837302314</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.537330056319824</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.765818925248256</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>89.3369242063621</v>
+      </c>
+      <c r="M31" t="n">
+        <v>89.06871706157064</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>61.51807510217653</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-27316.27022963938</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>211.3956404098765</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.275607928972657e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9888528806407042</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>70.90499999999997</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6556171983356448</v>
+      </c>
+      <c r="D32" t="n">
+        <v>249.7643994824821</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8887118345679127</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.43611e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-87.035</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.08347917902598105</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8886899371652173</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.983320566520368</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.513208850372214</v>
+      </c>
+      <c r="L32" t="n">
+        <v>92.31452673024421</v>
+      </c>
+      <c r="M32" t="n">
+        <v>89.00823369920913</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>57.7656822962722</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-25295.6471690317</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>197.8123440137912</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.471276929346483e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9994610263215388</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>70.32599999999996</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6502635228848819</v>
+      </c>
+      <c r="D33" t="n">
+        <v>363.8213930126107</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.294549496682647</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.43544e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-87.08199999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3333113356562042</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.08970173429023</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.213284585796286</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>97.46096450505657</v>
+      </c>
+      <c r="M33" t="n">
+        <v>89.05655104008662</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>60.72464275806209</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-26418.90728981206</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>79.21279092878714</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.397245194359139e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.999641595218358</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>70.27800000000002</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6498196948682389</v>
+      </c>
+      <c r="D34" t="n">
+        <v>242.1240917332349</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.861526086997138</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.4353e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-87.131</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5597341464822598</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.381217285494777</v>
+      </c>
+      <c r="J34" t="n">
+        <v>57.70506455825574</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.410382448788007</v>
+      </c>
+      <c r="L34" t="n">
+        <v>102.4531845583565</v>
+      </c>
+      <c r="M34" t="n">
+        <v>89.1296181681449</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>65.82326286770892</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-28499.84257358155</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>198.7494040832594</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.55882536354243e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9996167138923566</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>69.04499999999996</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6384188626907071</v>
+      </c>
+      <c r="D35" t="n">
+        <v>242.4460326830121</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8626716174758284</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.43474e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-87.16800000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.419576051462992</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.275070550830177</v>
+      </c>
+      <c r="J35" t="n">
+        <v>43.1558444238731</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>105.7101513331248</v>
+      </c>
+      <c r="M35" t="n">
+        <v>89.13147266081205</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>65.96383129253033</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-28311.08958908441</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>201.9339685273287</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.838513567334731e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.998377126155088</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>68.36199999999997</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.63210355987055</v>
+      </c>
+      <c r="D36" t="n">
+        <v>239.3863579690577</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8517846810915656</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.43446e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-87.214</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5356623742648906</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.280961405844801</v>
+      </c>
+      <c r="J36" t="n">
+        <v>44.6081907936746</v>
+      </c>
+      <c r="K36" t="n">
+        <v>16.84501800489797</v>
+      </c>
+      <c r="L36" t="n">
+        <v>111.4458634800138</v>
+      </c>
+      <c r="M36" t="n">
+        <v>89.15968101814754</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>68.17848050415313</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-29049.59931635962</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>202.1053660856297</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.885871208544202e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9984823978559318</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>65.73099999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6077762367082756</v>
+      </c>
+      <c r="D37" t="n">
+        <v>236.7164446238284</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8422845938409702</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.43442e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-87.246</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3413539175300419</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.055185355829462</v>
+      </c>
+      <c r="J37" t="n">
+        <v>29.57353170918867</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>112.8557175783032</v>
+      </c>
+      <c r="M37" t="n">
+        <v>89.11445303669798</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>64.69585415819186</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-27259.19356633699</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>202.2447988351698</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.938110053130199e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.998488141207048</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>65.62799999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6068238557558946</v>
+      </c>
+      <c r="D38" t="n">
+        <v>217.9475878740918</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7755012366076641</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.43441e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-87.28100000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4591734488888983</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.084635221674765</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.432010133908</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>116.8060187004285</v>
+      </c>
+      <c r="M38" t="n">
+        <v>89.16896176629569</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>68.93998283402046</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-28880.54549330903</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>225.3907037881557</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.627376490498228e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9992777482776589</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>63.923</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5910587147480353</v>
+      </c>
+      <c r="D39" t="n">
+        <v>213.3970545498981</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7593095262310607</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.43414e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-87.315</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4211131216884566</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.144760675858397</v>
+      </c>
+      <c r="J39" t="n">
+        <v>24.13379308222178</v>
+      </c>
+      <c r="K39" t="n">
+        <v>87.14393014824773</v>
+      </c>
+      <c r="L39" t="n">
+        <v>123.3406603157688</v>
+      </c>
+      <c r="M39" t="n">
+        <v>89.16317318030586</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>68.46303685303937</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-28425.14716559185</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>226.7337835239295</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.703415275189223e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9995217145723566</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>63.81099999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5900231160425334</v>
+      </c>
+      <c r="D40" t="n">
+        <v>210.8321130899101</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7501829500048716</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.43426e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-87.34399999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3520642412077271</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.185567329385985</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>95.06359465549689</v>
+      </c>
+      <c r="L40" t="n">
+        <v>124.8685987512335</v>
+      </c>
+      <c r="M40" t="n">
+        <v>89.19079324006958</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>70.80016225361923</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-29184.06750991363</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>225.9155600313929</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.645165962900131e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9999576555815921</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>62.517</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5780582524271846</v>
+      </c>
+      <c r="D41" t="n">
+        <v>201.5523275437778</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7171636115635722</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.43445e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-87.377</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.303949794740728</v>
+      </c>
+      <c r="I41" t="n">
+        <v>77.00186893994545</v>
+      </c>
+      <c r="J41" t="n">
+        <v>10.53686433003766</v>
+      </c>
+      <c r="K41" t="n">
+        <v>69.51125562032557</v>
+      </c>
+      <c r="L41" t="n">
+        <v>130.9732848146434</v>
+      </c>
+      <c r="M41" t="n">
+        <v>89.19279528563034</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>70.97578558132599</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-28988.99657579932</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>247.1943208717368</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>6.482556023868355e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9738197606982245</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>62.59499999999997</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.57877947295423</v>
+      </c>
+      <c r="D42" t="n">
+        <v>198.6038854352282</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7066724631019189</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.43491e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-87.40300000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6120557306531654</v>
+      </c>
+      <c r="I42" t="n">
+        <v>28.17592677371058</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>66.41478437562661</v>
+      </c>
+      <c r="L42" t="n">
+        <v>132.0586861027249</v>
+      </c>
+      <c r="M42" t="n">
+        <v>89.25410106462239</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>76.81006093117836</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-31198.96571073774</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>237.6493530192578</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>5.630143071229247e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9800656710548841</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>60.60300000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5603606102635231</v>
+      </c>
+      <c r="D43" t="n">
+        <v>193.6944901105853</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6892038497421972</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.43515e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-87.43300000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5888094392421295</v>
+      </c>
+      <c r="I43" t="n">
+        <v>32.85695096432471</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.17967565383666</v>
+      </c>
+      <c r="L43" t="n">
+        <v>137.8713027085747</v>
+      </c>
+      <c r="M43" t="n">
+        <v>89.21795392947773</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>73.25939417993858</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-29436.65716876552</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>248.6706116690359</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.557956078597764e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9683447653752802</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>2.573585113307562e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9994754130573339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>114.597</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>334.1603570585748</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.57293e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-81.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1458071414842707</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5894388043392587</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.332665507107203</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.731630894249228</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.25412374512587</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.69387133424055</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.76715063313547</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5387.805928715256</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>153.8207859995344</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.536830668752766e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9997696140965543</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83.63999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7298620382732532</v>
+      </c>
+      <c r="D13" t="n">
+        <v>244.5965487384973</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.731973567695291</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.55133e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.959</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3297100366831963</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9001482719099967</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.946329377916797</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.760178550018705</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.92208242469651</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.45393516384725</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.13693137386896</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7388.069706441625</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>225.8257225352453</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.746384160694846e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9987911239344199</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75.69200000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6605059469270576</v>
+      </c>
+      <c r="D14" t="n">
+        <v>335.6640305703018</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.004499856071986</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.52503e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.056</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2578768724022593</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9800379232129497</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.097206780106089</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.968178675168363</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.90934423252638</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.41118647874454</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>22.11699813021316</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9881.900400862911</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>117.4211516145785</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.53441897296202e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9999314139343761</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>71.43200000000002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6233321989231833</v>
+      </c>
+      <c r="D15" t="n">
+        <v>242.4492357892748</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7255475721998225</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.50662e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.69799999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1978888461933131</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7397775158056628</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.079130682926888</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.543063266820791</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31.45434620358342</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.94948734474607</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>27.93024266086277</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-12292.18184384115</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>207.7983503621808</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.665295921145765e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9970066901960255</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>70.99099999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6194839306439086</v>
+      </c>
+      <c r="D16" t="n">
+        <v>218.1066684759337</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6527006087610263</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.49432e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.10899999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6726147200026024</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.258241451334412</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.240244151311418</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.200094581817688</v>
+      </c>
+      <c r="L16" t="n">
+        <v>39.15809653791465</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.31136112682967</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>33.92033080645216</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14767.62845276563</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>235.2074617793962</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.334800953967796e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9982737197722613</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>68.19499999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5950853861793939</v>
+      </c>
+      <c r="D17" t="n">
+        <v>230.1895516275676</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6888595453206851</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.48639e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.399</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3182167828106994</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.158970684605528</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.257108827089283</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.329277694670078</v>
+      </c>
+      <c r="L17" t="n">
+        <v>46.83510260689462</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.52341347472644</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>38.79426870998044</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16633.02655156043</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>217.4423866276217</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.012551837423615e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9999950500448639</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>64.32899999999995</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5613497735542812</v>
+      </c>
+      <c r="D18" t="n">
+        <v>210.1083239547866</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.628764961242715</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.48072e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2569360457607195</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9909652539684836</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.197119503204801</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.242127832209206</v>
+      </c>
+      <c r="L18" t="n">
+        <v>53.87317226550037</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.64962108815162</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>42.42155278758862</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-17889.92606714007</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>244.2394356649057</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.361914432378412e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9778663228361385</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>63.42499999999995</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5534612598933651</v>
+      </c>
+      <c r="D19" t="n">
+        <v>283.3015846854587</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.847801298691451</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.47724e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.77</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3719344938100666</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.302471527137695</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.140956709185947</v>
+      </c>
+      <c r="K19" t="n">
+        <v>22.29657807805067</v>
+      </c>
+      <c r="L19" t="n">
+        <v>61.21485024353517</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.7830010822081</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>47.07248445762566</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-19597.34089013432</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>147.2275517749384</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.067321373286448e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9997862543218264</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>59.10699999999997</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5157813904377949</v>
+      </c>
+      <c r="D20" t="n">
+        <v>264.9204048920089</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7927942357494285</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.475e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.896</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.09361332141376247</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7860254070705663</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.801789865981753</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.633897319915755</v>
+      </c>
+      <c r="L20" t="n">
+        <v>67.01401299143372</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.82390532328188</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>48.71013643486328</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-19947.20813040185</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>156.4788618016251</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.163828103296893e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9996554499098295</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>59.40999999999997</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5184254387113099</v>
+      </c>
+      <c r="D21" t="n">
+        <v>231.6163981110363</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6931294907326078</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.47335e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3920894475119457</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.147704848237603</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.072365186816426</v>
+      </c>
+      <c r="K21" t="n">
+        <v>38.68604571496671</v>
+      </c>
+      <c r="L21" t="n">
+        <v>74.33755334938022</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.92454085184558</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>53.2693878287027</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-21601.1652768092</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>185.2287740787792</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.573585113307562e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9994754130573339</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>3.708158159960188e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9983818513056532</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106.311</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>311.3144118042566</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.51399e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2292053978879659</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8759101704768288</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.868902380930953</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.334426381536433</v>
+      </c>
+      <c r="L23" t="n">
+        <v>31.19174442467736</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.82290876471947</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>26.30491608296539</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-13183.64591278973</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>178.4544504937477</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.801037887453986e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9989189390021618</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92.39400000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8690916273950953</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1414.440304306464</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.543446273845536</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.49834e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-86.002</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4069915713887124</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.382722875312195</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.086461376278661</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.678044039904082</v>
+      </c>
+      <c r="L24" t="n">
+        <v>43.98562631472151</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.4011402363483</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>35.82609793986977</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-17219.7122207606</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-819.2073969883706</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.824848398905355e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.7294442315509895</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>88.21699999999998</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8298012435213661</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1362.678318775706</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.377177114538821</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.48879e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.319</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6832747166325229</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.309178561605427</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.301456991374557</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.253608215286931</v>
+      </c>
+      <c r="L25" t="n">
+        <v>54.5446183790102</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.65591714947475</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>42.620340682535</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-20167.68347234795</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-785.6113216431905</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.799402542672796e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9706712931760222</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>82.83100000000002</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7791385651531826</v>
+      </c>
+      <c r="D26" t="n">
+        <v>265.8312635846895</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8538996381312236</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.48296e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.52</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3377967277484958</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8685864998310625</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.087956972862759</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.967804344001123</v>
+      </c>
+      <c r="L26" t="n">
+        <v>63.8596371918139</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.7299404691602</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>45.10528322733751</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20992.34145579227</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>202.3163981180456</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.269225935213186e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.999515755718297</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80.47500000000002</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7569771707537319</v>
+      </c>
+      <c r="D27" t="n">
+        <v>260.0923029307649</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8354650252886514</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.47905e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.64400000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2056940400910255</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9785322360228204</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.160506119185388</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29.58168384987797</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70.96386325177357</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.80509088880189</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>47.94295405932738</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-22050.59842642148</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>212.0401719370243</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.547038235313572e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9999799532050987</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78.49499999999995</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7383525693484204</v>
+      </c>
+      <c r="D28" t="n">
+        <v>364.4510880228202</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.17068492239278</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.47673e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.745</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1228651537141657</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.829782113657682</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.87546524546391</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.428990491449566</v>
+      </c>
+      <c r="L28" t="n">
+        <v>76.3039613099418</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.85215892479286</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>49.90944775667173</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-22692.49838129308</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>91.67988971608844</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.356809998327137e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9999124228055719</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>75.005</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.705524357780474</v>
+      </c>
+      <c r="D29" t="n">
+        <v>254.6404933317845</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.817952795233564</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.47524e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.827</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1360267418209382</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7268598203902856</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.67278878622605</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.398334593052569</v>
+      </c>
+      <c r="L29" t="n">
+        <v>81.56281243102093</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.8574131229344</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>50.13901817247561</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-22513.85403880199</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>205.3631218205746</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.601643424338193e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9990039297998735</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>76.15599999999995</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7163510831428538</v>
+      </c>
+      <c r="D30" t="n">
+        <v>250.8280244275861</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8057064334859568</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.47422e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.898</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3673627027089082</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.215447472850204</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.506819302244316</v>
+      </c>
+      <c r="K30" t="n">
+        <v>38.39684851266294</v>
+      </c>
+      <c r="L30" t="n">
+        <v>89.32171975412756</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.99057701950217</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>56.75504974144478</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-25371.29466502148</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>212.6367243441501</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.803522940076049e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9997846977550818</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>73.93399999999997</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6954501415657829</v>
+      </c>
+      <c r="D31" t="n">
+        <v>251.1398740450863</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8067081526665525</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.47345e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.95</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3410251925219966</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.397413500147951</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.266369216354575</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8.430005299430585</v>
+      </c>
+      <c r="L31" t="n">
+        <v>93.7724216068379</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.99394217515265</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>56.94492852542965</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-25198.54161031957</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>206.4870183321702</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.709774740409917e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9995594937847865</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>71.91399999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6764492855866275</v>
+      </c>
+      <c r="D32" t="n">
+        <v>363.7297336281568</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.168367797430647</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.47276e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.997</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4065955793458744</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9820423473630473</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.923855963719443</v>
+      </c>
+      <c r="K32" t="n">
+        <v>36.10224791246267</v>
+      </c>
+      <c r="L32" t="n">
+        <v>95.83319170819763</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.99417310334179</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>56.95800522115</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-24938.71876990232</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>78.33851247403648</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.354272589580053e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9998945764566022</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>70.46300000000002</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6628006509204127</v>
+      </c>
+      <c r="D33" t="n">
+        <v>359.2714532842356</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.154046968792864</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.47245e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-87.041</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2279642236486098</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.03879488990274</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.054022985831914</v>
+      </c>
+      <c r="K33" t="n">
+        <v>29.5582845439287</v>
+      </c>
+      <c r="L33" t="n">
+        <v>99.35020959134143</v>
+      </c>
+      <c r="M33" t="n">
+        <v>89.0113552010319</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>57.94810539584014</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-25150.24252877807</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>80.9569532501279</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.396878671339473e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9997469384688852</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>70.36800000000005</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6619070463075319</v>
+      </c>
+      <c r="D34" t="n">
+        <v>239.9137352993731</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7706476995681855</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.47247e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-87.08499999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3891483258136423</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.340505896964026</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.449927819187408</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.4957955112764292</v>
+      </c>
+      <c r="L34" t="n">
+        <v>105.021041843762</v>
+      </c>
+      <c r="M34" t="n">
+        <v>89.06915122590496</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>61.54677327370452</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-26531.69042211393</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>202.4525849168638</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.751351175824226e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9982758452100803</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>68.02999999999997</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6399149664663106</v>
+      </c>
+      <c r="D35" t="n">
+        <v>237.0066604736441</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7613096325995516</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.47216e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-87.134</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2617647120249922</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9509140517004793</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.01633400268642</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.007675167515963</v>
+      </c>
+      <c r="L35" t="n">
+        <v>109.5307017111447</v>
+      </c>
+      <c r="M35" t="n">
+        <v>89.03403213158484</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>59.30875421748169</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-25280.49402069625</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>203.3380287112363</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.847868807366486e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9979757146289749</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>66.863</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6289377392743929</v>
+      </c>
+      <c r="D36" t="n">
+        <v>237.6009582766221</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7632186280730785</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.47205e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-87.161</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.239777436988743</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9633272914733254</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.975382731945476</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5.523147131837248</v>
+      </c>
+      <c r="L36" t="n">
+        <v>110.7282543408883</v>
+      </c>
+      <c r="M36" t="n">
+        <v>89.04748147753429</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>60.14633800435683</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-25419.83934485272</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>203.6335644772842</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.861493679864437e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9998487864587822</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>66.55400000000003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6260311726914431</v>
+      </c>
+      <c r="D37" t="n">
+        <v>234.920246964464</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7546076829625652</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.47199e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-87.191</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5105954516420155</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.16399332589215</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.206331608491171</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>112.6208813698807</v>
+      </c>
+      <c r="M37" t="n">
+        <v>89.09557239948225</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>63.34505993899006</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-26595.58197902434</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>199.4732819602494</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.908707535842557e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.99869446240015</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6173396920356311</v>
+      </c>
+      <c r="D38" t="n">
+        <v>214.3332962934971</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6884785546910763</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.47301e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-87.252</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3633071108191505</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.243313126023183</v>
+      </c>
+      <c r="J38" t="n">
+        <v>46.77429937829264</v>
+      </c>
+      <c r="K38" t="n">
+        <v>8.558191734369867</v>
+      </c>
+      <c r="L38" t="n">
+        <v>123.5526502796577</v>
+      </c>
+      <c r="M38" t="n">
+        <v>89.1260787236988</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>65.55663278592131</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-27301.21563522803</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>241.3738366666283</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.137759202835225e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9503544145827506</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>64.55500000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6072278503635559</v>
+      </c>
+      <c r="D39" t="n">
+        <v>229.350867611809</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7367177969133555</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.47247e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-87.259</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5018124156540074</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.11493532627462</v>
+      </c>
+      <c r="J39" t="n">
+        <v>36.52464859101643</v>
+      </c>
+      <c r="K39" t="n">
+        <v>61.37418987871618</v>
+      </c>
+      <c r="L39" t="n">
+        <v>122.2383678319495</v>
+      </c>
+      <c r="M39" t="n">
+        <v>89.11289757595712</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>64.58239724468777</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-26639.03816144041</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>199.4261808713246</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.018911084878908e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9987293519791896</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>63.72699999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.599439380684971</v>
+      </c>
+      <c r="D40" t="n">
+        <v>211.08590072232</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6780473139645179</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.47271e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-87.291</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4116587596975646</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.218825373800666</v>
+      </c>
+      <c r="J40" t="n">
+        <v>32.0943230244362</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.015664136821234</v>
+      </c>
+      <c r="L40" t="n">
+        <v>121.8892906166401</v>
+      </c>
+      <c r="M40" t="n">
+        <v>89.14182050853864</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>66.75933810862095</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-27314.91109448129</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>233.7420151784868</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.836273111869968e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9636842278339329</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>61.61199999999997</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5795449200929343</v>
+      </c>
+      <c r="D41" t="n">
+        <v>206.9435169408619</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6647412040499449</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.47275e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-87.322</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4066497606996921</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.088027152078596</v>
+      </c>
+      <c r="J41" t="n">
+        <v>11.41361968853344</v>
+      </c>
+      <c r="K41" t="n">
+        <v>51.45684682116918</v>
+      </c>
+      <c r="L41" t="n">
+        <v>128.0449417670068</v>
+      </c>
+      <c r="M41" t="n">
+        <v>89.13020675648549</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>65.86781226420273</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-26689.19248452581</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>217.7231070823523</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.425139114818643e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9999898975400129</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>59.72899999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.561832736029197</v>
+      </c>
+      <c r="D42" t="n">
+        <v>205.2907660705783</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6594322597556381</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.47295e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-87.345</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2760811216853171</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9130168825225143</v>
+      </c>
+      <c r="J42" t="n">
+        <v>24.30310778615464</v>
+      </c>
+      <c r="K42" t="n">
+        <v>61.73107249312272</v>
+      </c>
+      <c r="L42" t="n">
+        <v>127.0583295218604</v>
+      </c>
+      <c r="M42" t="n">
+        <v>89.09339115417504</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>63.19263025762518</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-25320.88127509539</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>223.4743097609033</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.580453238781462e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.98988244288752</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>60.125</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5655576563102593</v>
+      </c>
+      <c r="D43" t="n">
+        <v>202.7118652611399</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6511483489835925</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.47365e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-87.369</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6714070932454794</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.131874686963183</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>42.88351096776944</v>
+      </c>
+      <c r="L43" t="n">
+        <v>129.0660872073018</v>
+      </c>
+      <c r="M43" t="n">
+        <v>89.16389312927488</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>68.52199689964934</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-27301.23258940838</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>218.1037054884314</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.708158159960188e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9983818513056532</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.9968396660540553</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>113.397</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>232.1086627409731</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.55372e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.039</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.04738333586731697</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3206346233204299</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.034171585156763</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.148366429471708</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.316667755847</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.59107526851361</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.969748643155</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6441.185630714731</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>250.4992617490558</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.661063285288665e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9997597964646688</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>75.17099999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6629011349506597</v>
+      </c>
+      <c r="D13" t="n">
+        <v>229.0645816763079</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9868851036031244</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.54859e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-84.804</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1385832825640608</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7841302783169236</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.871968014347045</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.056646001154741</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.7712597562457</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.13674553142994</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19.9940581085279</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8801.431445806935</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>228.5941246877516</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.130655124832358e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9996202448795002</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>67.47399999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5950245597326205</v>
+      </c>
+      <c r="D14" t="n">
+        <v>272.1528302238335</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.172523364746402</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.53088e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.688</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3841822320281821</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.112043713403548</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.035832029625437</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.977970272417165</v>
+      </c>
+      <c r="L14" t="n">
+        <v>30.83619877757449</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.91102970620548</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>27.41560753252618</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-11727.89934096327</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>161.4046901234984</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.001967991831343e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9995643237254113</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>64.238</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5664876495850858</v>
+      </c>
+      <c r="D15" t="n">
+        <v>220.8338506401014</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9514244235104055</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.51792e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-86.191</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3824815865688868</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.343763967973147</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.279785239723245</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.37593002576943</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40.48580457419422</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.32852274969719</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>34.26880306046514</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-14433.98027306289</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>213.5265580872823</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.982173463783532e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9981977899244293</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>59.93599999999998</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5285501380107054</v>
+      </c>
+      <c r="D16" t="n">
+        <v>202.804877145032</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8737497116656807</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.50988e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.506</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.04114586801431521</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7574590820279299</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.879624447070336</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.789237764879073</v>
+      </c>
+      <c r="L16" t="n">
+        <v>49.85538818688924</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.51560631152049</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>38.59013978514398</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-15955.65087096711</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>222.5568274334151</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.198232041373851e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9997318275058752</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57.58200000000005</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5077912114077094</v>
+      </c>
+      <c r="D17" t="n">
+        <v>199.0327841737207</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.857498301973485</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.50524e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.724</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1982195727913589</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.000100437336305</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.959561973003111</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.810803984085168</v>
+      </c>
+      <c r="L17" t="n">
+        <v>58.74190409315504</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.65957793641439</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>42.73678248728942</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-17405.51411385684</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>228.1840931899332</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.627383734864578e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9990932847764759</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56.41200000000003</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4974734781343423</v>
+      </c>
+      <c r="D18" t="n">
+        <v>270.1715480679762</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.163987353498651</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.50224e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.877</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2569265832587139</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.008061290595036</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.970472738356537</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.601342300409536</v>
+      </c>
+      <c r="L18" t="n">
+        <v>66.32953090142806</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.78294966683336</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>47.07049524034769</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-18921.75319589645</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>149.252410168033</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.209172834264025e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9996862645962195</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>54.548</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4810356535005333</v>
+      </c>
+      <c r="D19" t="n">
+        <v>256.2100650171334</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.103836720230718</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.50088e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.99299999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5275591011210629</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.230899185061016</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.145109127991847</v>
+      </c>
+      <c r="K19" t="n">
+        <v>37.18397857259151</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74.42598544950813</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.87275466523322</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>50.82157807793389</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-20167.59559117172</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>159.9893498241421</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.398932455918836e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9997616556204083</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>53.39799999999997</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4708942917361125</v>
+      </c>
+      <c r="D20" t="n">
+        <v>226.4984183299594</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9758292329775106</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.50031e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-87.089</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5394665844542564</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.357673898660345</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.362572431479899</v>
+      </c>
+      <c r="K20" t="n">
+        <v>29.91690095219927</v>
+      </c>
+      <c r="L20" t="n">
+        <v>81.0801175697478</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.93311863277523</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>53.69777665278218</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-21028.19098596118</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>178.2429499295173</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.597201897172871e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9999271281936198</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>51.69199999999995</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4558498020229806</v>
+      </c>
+      <c r="D21" t="n">
+        <v>211.7564062082713</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9123158253019865</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.50046e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-87.16200000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4734379631402365</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.316103757860133</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.232374486206331</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26.57226962424973</v>
+      </c>
+      <c r="L21" t="n">
+        <v>86.60120843249781</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.9737992355857</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>55.82694415265196</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-21600.45072945064</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>202.413414098264</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.742161832806621e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9968396660540553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
